--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -21,7 +21,7 @@
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Equipements!$A$5:$R$112</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Obligations legales'!$A$5:$N$26</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Plaques par marque'!$A$5:$J$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Questionnaire!$A$5:$L$78</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Questionnaire!$A$5:$L$80</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Taches!$A$5:$O$159</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="2322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5193" uniqueCount="2330">
   <si>
     <t xml:space="preserve">Referentiel d'entretien des equipements du logement - France</t>
   </si>
@@ -5247,7 +5247,7 @@
     <t xml:space="preserve">Questionnaire d'accueil : premiere utilisation et nouveau lieu</t>
   </si>
   <si>
-    <t xml:space="preserve">Une ligne = une reponse possible. Pour chaque obligation créée : date approximative du dernier entretien, ramonage, contrôle ou vidange (mois et année). « Je ne sais pas » la classe « à planifier ».</t>
+    <t xml:space="preserve">Une ligne = une reponse possible. Pour chaque obligation créée, la date du dernier passage (entretien, ramonage, contrôle ou vidange) se donne en chiffres (MM/AAAA). Réponses graduées : date précise → calcul normal ; fait récemment, sans date exacte → à confirmer (orange), avec un rappel pour la préciser ; plus ancien que le délai légal → en retard (rouge) ; jamais réalisé ou je ne sais pas → en retard (rouge), prioritaire.</t>
   </si>
   <si>
     <t xml:space="preserve">Bloc</t>
@@ -5481,7 +5481,7 @@
     <t xml:space="preserve">CUIS-03, CUIS-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Date de péremption imprimée sur le tuyau flexible (une photo suffit).</t>
+    <t xml:space="preserve">Date de péremption imprimée sur le tuyau flexible (MM/AAAA).</t>
   </si>
   <si>
     <t xml:space="preserve">Indice : des brûleurs à flamme signalent une cuisson au gaz.</t>
@@ -5532,7 +5532,7 @@
     <t xml:space="preserve">Voiture</t>
   </si>
   <si>
-    <t xml:space="preserve">Date de première immatriculation et du dernier contrôle technique (photo de la carte grise possible).</t>
+    <t xml:space="preserve">Date de première immatriculation (sur la carte grise) et du dernier contrôle technique (MM/AAAA).</t>
   </si>
   <si>
     <t xml:space="preserve">Moto, scooter ou quadricycle</t>
@@ -5553,7 +5553,7 @@
     <t xml:space="preserve">Ajouté d'office</t>
   </si>
   <si>
-    <t xml:space="preserve">Est-il installé ? Photographiez la date imprimée au dos pour le rappel de remplacement à 10 ans.</t>
+    <t xml:space="preserve">Est-il installé ? Si oui, notez la date de fabrication imprimée au dos (MM/AAAA) : elle fixe son remplacement, 10 ans après.</t>
   </si>
   <si>
     <t xml:space="preserve">Obligatoire dans tout logement : il n'y a pas de question à poser.</t>
@@ -5571,7 +5571,7 @@
     <t xml:space="preserve">Pour chaque obligation créée</t>
   </si>
   <si>
-    <t xml:space="preserve">Pour chaque obligation créée : date approximative du dernier entretien, ramonage, contrôle ou vidange (mois et année). « Je ne sais pas » la classe « à planifier ».</t>
+    <t xml:space="preserve">Pour chaque obligation créée, la date du dernier passage (entretien, ramonage, contrôle ou vidange) se donne en chiffres (MM/AAAA). Réponses graduées : date précise → calcul normal ; fait récemment, sans date exacte → à confirmer (orange), avec un rappel pour la préciser ; plus ancien que le délai légal → en retard (rouge) ; jamais réalisé ou je ne sais pas → en retard (rouge), prioritaire.</t>
   </si>
   <si>
     <t xml:space="preserve">REGLE-02</t>
@@ -5584,6 +5584,30 @@
   </si>
   <si>
     <t xml:space="preserve">« Je ne sais pas » ne bloque jamais la progression : la réponse ajoute un point « à vérifier » sur l'écran d'accueil, avec l'aide associée pour trouver la réponse. Même règle pour les questions de suivi. À l'écran, c'est un choix discret, sous les autres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appareil et conduit de fumée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour chaque réponse créant un appareil et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand une réponse crée un appareil à combustion et son conduit de fumée (poêle, insert, chaudière), une seule question de date couvre les deux : l'entretien et le ramonage se font au même passage. Un lien « faits séparément ? » permet de donner deux dates, ou d'indiquer que seul l'un des deux a été fait.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type de logement déjà connu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour la question Q01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La question Q01 n'est pas posée si le type de logement a déjà été renseigné à la création du lieu.</t>
   </si>
   <si>
     <t xml:space="preserve">Q20</t>
@@ -22014,7 +22038,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:L78"/>
+  <dimension ref="A2:L80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -23940,7 +23964,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
         <v>1841</v>
       </c>
@@ -24016,103 +24040,103 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="24" t="s">
+    <row r="57" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="16" t="s">
         <v>1850</v>
       </c>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D57" s="18" t="s">
         <v>1851</v>
       </c>
-      <c r="C57" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D57" s="26" t="s">
+      <c r="E57" s="16" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F57" s="18" t="s">
         <v>1852</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="G57" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H57" s="19" t="s">
         <v>1853</v>
       </c>
-      <c r="F57" s="26" t="s">
+      <c r="I57" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J57" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L57" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="16" t="s">
         <v>1854</v>
       </c>
-      <c r="G57" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="H57" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I57" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J57" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K57" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L57" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="24" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B58" s="24" t="s">
-        <v>1851</v>
-      </c>
-      <c r="C58" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>1852</v>
-      </c>
-      <c r="E58" s="24" t="s">
-        <v>1853</v>
-      </c>
-      <c r="F58" s="26" t="s">
+      <c r="B58" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D58" s="18" t="s">
         <v>1855</v>
       </c>
-      <c r="G58" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="H58" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I58" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J58" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K58" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L58" s="25" t="s">
+      <c r="E58" s="16" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>1857</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J58" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L58" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C59" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>384</v>
+        <v>1862</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="H59" s="25" t="s">
         <v>153</v>
@@ -24132,25 +24156,25 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C60" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>1856</v>
+        <v>1863</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="H60" s="25" t="s">
         <v>153</v>
@@ -24170,25 +24194,25 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C61" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="H61" s="25" t="s">
         <v>153</v>
@@ -24208,25 +24232,25 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C62" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>1857</v>
+        <v>1864</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="H62" s="25" t="s">
         <v>153</v>
@@ -24246,25 +24270,25 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C63" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>1858</v>
+        <v>398</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="H63" s="25" t="s">
         <v>153</v>
@@ -24284,25 +24308,25 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C64" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>334</v>
+        <v>409</v>
       </c>
       <c r="H64" s="25" t="s">
         <v>153</v>
@@ -24322,25 +24346,25 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C65" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="H65" s="25" t="s">
         <v>153</v>
@@ -24360,25 +24384,25 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C66" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>446</v>
+        <v>334</v>
       </c>
       <c r="H66" s="25" t="s">
         <v>153</v>
@@ -24398,25 +24422,25 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C67" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="H67" s="25" t="s">
         <v>153</v>
@@ -24436,25 +24460,25 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C68" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>461</v>
+        <v>1869</v>
       </c>
       <c r="G68" s="25" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="H68" s="25" t="s">
         <v>153</v>
@@ -24474,31 +24498,31 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C69" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>1863</v>
+        <v>1870</v>
       </c>
       <c r="G69" s="25" t="s">
-        <v>316</v>
+        <v>453</v>
       </c>
       <c r="H69" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I69" s="25" t="s">
-        <v>1864</v>
+        <v>153</v>
       </c>
       <c r="J69" s="25" t="s">
         <v>153</v>
@@ -24512,25 +24536,25 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C70" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>289</v>
+        <v>461</v>
       </c>
       <c r="G70" s="25" t="s">
-        <v>288</v>
+        <v>460</v>
       </c>
       <c r="H70" s="25" t="s">
         <v>153</v>
@@ -24550,31 +24574,31 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C71" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>1865</v>
+        <v>1871</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>647</v>
+        <v>316</v>
       </c>
       <c r="H71" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I71" s="25" t="s">
-        <v>1866</v>
+        <v>1872</v>
       </c>
       <c r="J71" s="25" t="s">
         <v>153</v>
@@ -24588,25 +24612,25 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C72" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>714</v>
+        <v>289</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>713</v>
+        <v>288</v>
       </c>
       <c r="H72" s="25" t="s">
         <v>153</v>
@@ -24626,31 +24650,31 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C73" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E73" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>1867</v>
+        <v>1873</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>694</v>
+        <v>647</v>
       </c>
       <c r="H73" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I73" s="25" t="s">
-        <v>153</v>
+        <v>1874</v>
       </c>
       <c r="J73" s="25" t="s">
         <v>153</v>
@@ -24664,25 +24688,25 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C74" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>1868</v>
+        <v>714</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>789</v>
+        <v>713</v>
       </c>
       <c r="H74" s="25" t="s">
         <v>153</v>
@@ -24702,25 +24726,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C75" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>799</v>
+        <v>1875</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>798</v>
+        <v>694</v>
       </c>
       <c r="H75" s="25" t="s">
         <v>153</v>
@@ -24740,31 +24764,31 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C76" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>1869</v>
+        <v>1876</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>1870</v>
+        <v>789</v>
       </c>
       <c r="H76" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I76" s="25" t="s">
-        <v>1871</v>
+        <v>153</v>
       </c>
       <c r="J76" s="25" t="s">
         <v>153</v>
@@ -24778,25 +24802,25 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C77" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>1872</v>
+        <v>799</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>603</v>
+        <v>798</v>
       </c>
       <c r="H77" s="25" t="s">
         <v>153</v>
@@ -24816,44 +24840,120 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C78" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="G78" s="25" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H78" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I78" s="25" t="s">
+        <v>1879</v>
+      </c>
+      <c r="J78" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K78" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L78" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="24" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B79" s="24" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C79" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D79" s="26" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E79" s="24" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F79" s="26" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G79" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="H79" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I79" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J79" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K79" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L79" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="24" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B80" s="24" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C80" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E80" s="24" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F80" s="26" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G80" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="H78" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I78" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J78" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K78" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L78" s="25" t="s">
+      <c r="H80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L80" s="25" t="s">
         <v>153</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L78"/>
+  <autoFilter ref="A5:L80"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -24886,349 +24986,349 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1874</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1875</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>1876</v>
+        <v>1884</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1877</v>
+        <v>1885</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1878</v>
+        <v>1886</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1879</v>
+        <v>1887</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1880</v>
+        <v>1888</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1881</v>
+        <v>1889</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1882</v>
+        <v>1890</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1883</v>
+        <v>1891</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>1885</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1886</v>
+        <v>1894</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1887</v>
+        <v>1895</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1888</v>
+        <v>1896</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>1889</v>
+        <v>1897</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1890</v>
+        <v>1898</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>1891</v>
+        <v>1899</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>1892</v>
+        <v>1900</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>1893</v>
+        <v>1901</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>1894</v>
+        <v>1902</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1897</v>
+        <v>1905</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1898</v>
+        <v>1906</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1899</v>
+        <v>1907</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>1901</v>
+        <v>1909</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>1902</v>
+        <v>1910</v>
       </c>
       <c r="I7" s="15" t="s">
+        <v>1911</v>
+      </c>
+      <c r="J7" s="26" t="s">
         <v>1903</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1904</v>
+        <v>1912</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>1904</v>
+        <v>1912</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1905</v>
+        <v>1913</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>1906</v>
+        <v>1914</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>1907</v>
+        <v>1915</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>1908</v>
+        <v>1916</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>1909</v>
+        <v>1917</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>1910</v>
+        <v>1918</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1911</v>
+        <v>1919</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>1911</v>
+        <v>1919</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1912</v>
+        <v>1920</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1913</v>
+        <v>1921</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>1916</v>
+        <v>1924</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>1917</v>
+        <v>1925</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1918</v>
+        <v>1926</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>1918</v>
+        <v>1926</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1912</v>
+        <v>1920</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>1919</v>
+        <v>1927</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1920</v>
+        <v>1928</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>153</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1923</v>
+        <v>1931</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>1924</v>
+        <v>1932</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1926</v>
+        <v>1934</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1927</v>
+        <v>1935</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>1930</v>
+        <v>1938</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>1931</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1932</v>
+        <v>1940</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>1933</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>1925</v>
-      </c>
       <c r="D12" s="15" t="s">
-        <v>1934</v>
+        <v>1942</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>1935</v>
+        <v>1943</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>1936</v>
+        <v>1944</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>1938</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>1940</v>
+        <v>1948</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1941</v>
+        <v>1949</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>1942</v>
+        <v>1950</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>1943</v>
+        <v>1951</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>1944</v>
+        <v>1952</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>1945</v>
+        <v>1953</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>1946</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1947</v>
+        <v>1955</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>1948</v>
+        <v>1956</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1949</v>
+        <v>1957</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>1950</v>
+        <v>1958</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>1951</v>
+        <v>1959</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>1955</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1956</v>
+        <v>1964</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>1957</v>
+        <v>1965</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1958</v>
+        <v>1966</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>1959</v>
+        <v>1967</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>153</v>
@@ -25237,36 +25337,36 @@
         <v>181</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>1963</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1964</v>
+        <v>1972</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>1965</v>
+        <v>1973</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>1966</v>
+        <v>1974</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>153</v>
@@ -25275,30 +25375,30 @@
         <v>153</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1967</v>
+        <v>1975</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>1966</v>
+        <v>1974</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>153</v>
@@ -25307,30 +25407,30 @@
         <v>153</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1969</v>
+        <v>1977</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>1966</v>
+        <v>1974</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>153</v>
@@ -25339,30 +25439,30 @@
         <v>153</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1973</v>
+        <v>1981</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>153</v>
@@ -25371,59 +25471,59 @@
         <v>153</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1975</v>
+        <v>1983</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>1976</v>
+        <v>1984</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1977</v>
+        <v>1985</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>1979</v>
+        <v>1987</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>153</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>304</v>
@@ -25435,7 +25535,7 @@
         <v>153</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25443,22 +25543,22 @@
         <v>44</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>153</v>
@@ -25467,7 +25567,7 @@
         <v>153</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
   </sheetData>
@@ -25507,12 +25607,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1986</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1987</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25520,78 +25620,78 @@
         <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1988</v>
+        <v>1996</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1993</v>
+        <v>2001</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>1999</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>915</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="J6" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="L6" s="28" t="s">
         <v>153</v>
@@ -25600,92 +25700,92 @@
         <v>1592</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>2009</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>2019</v>
+        <v>2027</v>
       </c>
       <c r="K7" s="28" t="s">
-        <v>2020</v>
+        <v>2028</v>
       </c>
       <c r="L7" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>2021</v>
+        <v>2029</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>2024</v>
+        <v>2032</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>2026</v>
+        <v>2034</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>2027</v>
+        <v>2035</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>2028</v>
+        <v>2036</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>112</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>2029</v>
+        <v>2037</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="J8" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>2030</v>
+        <v>2038</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>2031</v>
+        <v>2039</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>153</v>
@@ -25693,31 +25793,31 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>2032</v>
+        <v>2040</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>2033</v>
+        <v>2041</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>2034</v>
+        <v>2042</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>2035</v>
+        <v>2043</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>2037</v>
+        <v>2045</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>112</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>2038</v>
+        <v>2046</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>2039</v>
+        <v>2047</v>
       </c>
       <c r="J9" s="28" t="s">
         <v>153</v>
@@ -25732,37 +25832,37 @@
         <v>153</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>2040</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>2041</v>
+        <v>2049</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>2042</v>
+        <v>2050</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>2043</v>
+        <v>2051</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>2044</v>
+        <v>2052</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>2045</v>
+        <v>2053</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>2046</v>
+        <v>2054</v>
       </c>
       <c r="G10" s="15" t="s">
+        <v>2055</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>2056</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>2047</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>2048</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>2039</v>
-      </c>
       <c r="J10" s="28" t="s">
         <v>153</v>
       </c>
@@ -25776,39 +25876,39 @@
         <v>153</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>2049</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>2050</v>
+        <v>2058</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>2052</v>
+        <v>2060</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>2053</v>
+        <v>2061</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>2054</v>
+        <v>2062</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>2055</v>
+        <v>2063</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>2056</v>
+        <v>2064</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>2057</v>
+        <v>2065</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>2058</v>
+        <v>2066</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>2059</v>
+        <v>2067</v>
       </c>
       <c r="K11" s="28" t="s">
         <v>153</v>
@@ -25820,48 +25920,48 @@
         <v>153</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>2060</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>2061</v>
+        <v>2069</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>2062</v>
+        <v>2070</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>2063</v>
+        <v>2071</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>2064</v>
+        <v>2072</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>2065</v>
+        <v>2073</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>2066</v>
+        <v>2074</v>
       </c>
       <c r="G12" s="15" t="s">
         <v>642</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>2067</v>
+        <v>2075</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>2068</v>
+        <v>2076</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>2069</v>
+        <v>2077</v>
       </c>
       <c r="L12" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>2070</v>
+        <v>2078</v>
       </c>
       <c r="N12" s="28" t="s">
         <v>153</v>
@@ -25869,43 +25969,43 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>2071</v>
+        <v>2079</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>2072</v>
+        <v>2080</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>2073</v>
+        <v>2081</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>2074</v>
+        <v>2082</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>2075</v>
+        <v>2083</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>2077</v>
+        <v>2085</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>2078</v>
+        <v>2086</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>2079</v>
+        <v>2087</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>2080</v>
+        <v>2088</v>
       </c>
       <c r="K13" s="28" t="s">
         <v>153</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>2082</v>
+        <v>2090</v>
       </c>
       <c r="N13" s="28" t="s">
         <v>153</v>
@@ -25913,31 +26013,31 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>2083</v>
+        <v>2091</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>2084</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>2085</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>2086</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>2087</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>2076</v>
-      </c>
       <c r="G14" s="15" t="s">
-        <v>2088</v>
+        <v>2096</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>2089</v>
+        <v>2097</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>2090</v>
+        <v>2098</v>
       </c>
       <c r="J14" s="28" t="s">
         <v>153</v>
@@ -25952,39 +26052,39 @@
         <v>153</v>
       </c>
       <c r="N14" s="28" t="s">
-        <v>2091</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>2092</v>
+        <v>2100</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>2093</v>
+        <v>2101</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>2094</v>
+        <v>2102</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>2095</v>
+        <v>2103</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>2096</v>
+        <v>2104</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>2097</v>
+        <v>2105</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>2098</v>
+        <v>2106</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>2099</v>
+        <v>2107</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>2100</v>
+        <v>2108</v>
       </c>
       <c r="K15" s="28" t="s">
         <v>153</v>
@@ -25996,36 +26096,36 @@
         <v>153</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>2101</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>1669</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2103</v>
+        <v>2111</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2104</v>
+        <v>2112</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>2105</v>
+        <v>2113</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>2106</v>
+        <v>2114</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>2107</v>
+        <v>2115</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>2108</v>
+        <v>2116</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>2109</v>
+        <v>2117</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>153</v>
@@ -26034,42 +26134,42 @@
         <v>153</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>2110</v>
+        <v>2118</v>
       </c>
       <c r="M16" s="28" t="s">
         <v>153</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>2111</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>2112</v>
+        <v>2120</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>2113</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="F17" s="15" t="s">
         <v>2114</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="G17" s="15" t="s">
         <v>2115</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>2105</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>2106</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>2107</v>
-      </c>
       <c r="H17" s="15" t="s">
-        <v>2116</v>
+        <v>2124</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>2109</v>
+        <v>2117</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>153</v>
@@ -26078,42 +26178,42 @@
         <v>153</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>2110</v>
+        <v>2118</v>
       </c>
       <c r="M17" s="28" t="s">
         <v>153</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>2111</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>2117</v>
+        <v>2125</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>2118</v>
+        <v>2126</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2119</v>
+        <v>2127</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2120</v>
+        <v>2128</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>2121</v>
+        <v>2129</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>2046</v>
+        <v>2054</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>2123</v>
+        <v>2131</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>2124</v>
+        <v>2132</v>
       </c>
       <c r="J18" s="28" t="s">
         <v>153</v>
@@ -26122,54 +26222,54 @@
         <v>153</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>2125</v>
+        <v>2133</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>2126</v>
+        <v>2134</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>2127</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>2128</v>
+        <v>2136</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>2129</v>
+        <v>2137</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2130</v>
+        <v>2138</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2131</v>
+        <v>2139</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>2132</v>
+        <v>2140</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>2028</v>
+        <v>2036</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>2133</v>
+        <v>2141</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>2134</v>
+        <v>2142</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>2135</v>
+        <v>2143</v>
       </c>
       <c r="J19" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>2136</v>
+        <v>2144</v>
       </c>
       <c r="L19" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>2137</v>
+        <v>2145</v>
       </c>
       <c r="N19" s="28" t="s">
         <v>153</v>
@@ -26177,31 +26277,31 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>2138</v>
+        <v>2146</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>2139</v>
+        <v>2147</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2140</v>
+        <v>2148</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2141</v>
+        <v>2149</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>2142</v>
+        <v>2150</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>2046</v>
+        <v>2054</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>2143</v>
+        <v>2151</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>2144</v>
+        <v>2152</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>2145</v>
+        <v>2153</v>
       </c>
       <c r="J20" s="28" t="s">
         <v>153</v>
@@ -26210,42 +26310,42 @@
         <v>153</v>
       </c>
       <c r="L20" s="28" t="s">
-        <v>2146</v>
+        <v>2154</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>2147</v>
+        <v>2155</v>
       </c>
       <c r="N20" s="28" t="s">
-        <v>2148</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>2149</v>
+        <v>2157</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>2150</v>
+        <v>2158</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2151</v>
+        <v>2159</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>2152</v>
+        <v>2160</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>2153</v>
+        <v>2161</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>847</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>2154</v>
+        <v>2162</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>2155</v>
+        <v>2163</v>
       </c>
       <c r="J21" s="28" t="s">
         <v>153</v>
@@ -26260,36 +26360,36 @@
         <v>153</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>2156</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>2157</v>
+        <v>2165</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>2158</v>
+        <v>2166</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2159</v>
+        <v>2167</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2160</v>
+        <v>2168</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>2161</v>
+        <v>2169</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>2162</v>
+        <v>2170</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>2163</v>
+        <v>2171</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>2164</v>
+        <v>2172</v>
       </c>
       <c r="J22" s="28" t="s">
         <v>153</v>
@@ -26301,39 +26401,39 @@
         <v>153</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>2165</v>
+        <v>2173</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>2166</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>2167</v>
+        <v>2175</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>2168</v>
+        <v>2176</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2169</v>
+        <v>2177</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>2170</v>
+        <v>2178</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>2171</v>
+        <v>2179</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>2172</v>
+        <v>2180</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>227</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>2173</v>
+        <v>2181</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>2164</v>
+        <v>2172</v>
       </c>
       <c r="J23" s="28" t="s">
         <v>153</v>
@@ -26342,10 +26442,10 @@
         <v>153</v>
       </c>
       <c r="L23" s="28" t="s">
-        <v>2174</v>
+        <v>2182</v>
       </c>
       <c r="M23" s="28" t="s">
-        <v>2175</v>
+        <v>2183</v>
       </c>
       <c r="N23" s="28" t="s">
         <v>153</v>
@@ -26353,31 +26453,31 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>2176</v>
+        <v>2184</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>2177</v>
+        <v>2185</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2178</v>
+        <v>2186</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>2179</v>
+        <v>2187</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>2180</v>
+        <v>2188</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>2181</v>
+        <v>2189</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>2182</v>
+        <v>2190</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>2183</v>
+        <v>2191</v>
       </c>
       <c r="J24" s="28" t="s">
         <v>153</v>
@@ -26389,42 +26489,42 @@
         <v>153</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>2184</v>
+        <v>2192</v>
       </c>
       <c r="N24" s="28" t="s">
-        <v>2185</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>2186</v>
+        <v>2194</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>2187</v>
+        <v>2195</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2188</v>
+        <v>2196</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>872</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>2189</v>
+        <v>2197</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>2190</v>
+        <v>2198</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>875</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>2191</v>
+        <v>2199</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>2192</v>
+        <v>2200</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>2193</v>
+        <v>2201</v>
       </c>
       <c r="K25" s="28" t="s">
         <v>153</v>
@@ -26436,27 +26536,27 @@
         <v>153</v>
       </c>
       <c r="N25" s="28" t="s">
-        <v>2194</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>2195</v>
+        <v>2203</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>2196</v>
+        <v>2204</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2197</v>
+        <v>2205</v>
       </c>
       <c r="D26" s="15" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F26" s="15" t="s">
         <v>2198</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>2199</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>2190</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>875</v>
@@ -26465,10 +26565,10 @@
         <v>887</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>2200</v>
+        <v>2208</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>2193</v>
+        <v>2201</v>
       </c>
       <c r="K26" s="28" t="s">
         <v>153</v>
@@ -26512,26 +26612,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2201</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2202</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>2203</v>
+        <v>2211</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2204</v>
+        <v>2212</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2205</v>
+        <v>2213</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2206</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26539,7 +26639,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>2207</v>
+        <v>2215</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>41</v>
@@ -26551,7 +26651,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>2208</v>
+        <v>2216</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>42</v>
@@ -26563,7 +26663,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>2209</v>
+        <v>2217</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>43</v>
@@ -26575,7 +26675,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>2210</v>
+        <v>2218</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>44</v>
@@ -26587,13 +26687,13 @@
         <v>35</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>2211</v>
+        <v>2219</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>2212</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26601,7 +26701,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>2213</v>
+        <v>2221</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>46</v>
@@ -26613,7 +26713,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>2214</v>
+        <v>2222</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>47</v>
@@ -26625,7 +26725,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>2215</v>
+        <v>2223</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>48</v>
@@ -26637,13 +26737,13 @@
         <v>35</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>2216</v>
+        <v>2224</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>2217</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26651,191 +26751,191 @@
         <v>35</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>2218</v>
+        <v>2226</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2212</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>2219</v>
+        <v>2227</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>2220</v>
+        <v>2228</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2221</v>
+        <v>2229</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2222</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>2219</v>
+        <v>2227</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>2223</v>
+        <v>2231</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>2224</v>
+        <v>2232</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>2225</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>2219</v>
+        <v>2227</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>2226</v>
+        <v>2234</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2227</v>
+        <v>2235</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2228</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>2229</v>
+        <v>2237</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>2230</v>
+        <v>2238</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2231</v>
+        <v>2239</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2232</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>2229</v>
+        <v>2237</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>2233</v>
+        <v>2241</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2234</v>
+        <v>2242</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2235</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>2229</v>
+        <v>2237</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2236</v>
+        <v>2244</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2237</v>
+        <v>2245</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>2238</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>2229</v>
+        <v>2237</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2239</v>
+        <v>2247</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2240</v>
+        <v>2248</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2241</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>2242</v>
+        <v>2250</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2243</v>
+        <v>2251</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2244</v>
+        <v>2252</v>
       </c>
       <c r="D23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>2242</v>
+        <v>2250</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2245</v>
+        <v>2253</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2246</v>
+        <v>2254</v>
       </c>
       <c r="D24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>2242</v>
+        <v>2250</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>2247</v>
+        <v>2255</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2248</v>
+        <v>2256</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>2249</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>2242</v>
+        <v>2250</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>2250</v>
+        <v>2258</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2251</v>
+        <v>2259</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>2252</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>2242</v>
+        <v>2250</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>2253</v>
+        <v>2261</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>2254</v>
+        <v>2262</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>2255</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>2242</v>
+        <v>2250</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>2256</v>
+        <v>2264</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>2257</v>
+        <v>2265</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>2258</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26843,13 +26943,13 @@
         <v>53</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>2259</v>
+        <v>2267</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>56</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>2260</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26857,13 +26957,13 @@
         <v>53</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2261</v>
+        <v>2269</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>2262</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26871,317 +26971,317 @@
         <v>53</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>2263</v>
+        <v>2271</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>60</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>2264</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2266</v>
+        <v>2274</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>112</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>2267</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2268</v>
+        <v>2276</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>2269</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>2270</v>
+        <v>2278</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>2271</v>
+        <v>2279</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>2272</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>2273</v>
+        <v>2281</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>2274</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>2275</v>
+        <v>2283</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>2276</v>
+        <v>2284</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>2277</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>2278</v>
+        <v>2286</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>581</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>2279</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>2265</v>
+        <v>2273</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>2280</v>
+        <v>2288</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>779</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>2281</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>2282</v>
+        <v>2290</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>2283</v>
+        <v>2291</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>2284</v>
+        <v>2292</v>
       </c>
       <c r="D39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>2282</v>
+        <v>2290</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>2285</v>
+        <v>2293</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>2286</v>
+        <v>2294</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>2287</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>2282</v>
+        <v>2290</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>2288</v>
+        <v>2296</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>2289</v>
+        <v>2297</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>2290</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>2282</v>
+        <v>2290</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>2291</v>
+        <v>2299</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>2292</v>
+        <v>2300</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>2293</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>2294</v>
+        <v>2302</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>2295</v>
+        <v>2303</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>2296</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>2294</v>
+        <v>2302</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>2297</v>
+        <v>2305</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>2298</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>2294</v>
+        <v>2302</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>2299</v>
+        <v>2307</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>74</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>2300</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>2294</v>
+        <v>2302</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>2301</v>
+        <v>2309</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>75</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>2302</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>2294</v>
+        <v>2302</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>2303</v>
+        <v>2311</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>2304</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>2305</v>
+        <v>2313</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>2306</v>
+        <v>2314</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>2307</v>
+        <v>2315</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>2308</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>2305</v>
+        <v>2313</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>2309</v>
+        <v>2317</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>1955</v>
+        <v>1963</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>2310</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>2305</v>
+        <v>2313</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>2311</v>
+        <v>2319</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>2312</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>2313</v>
+        <v>2321</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>2314</v>
+        <v>2322</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>2315</v>
+        <v>2323</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>2316</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>2313</v>
+        <v>2321</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>2317</v>
+        <v>2325</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>2318</v>
+        <v>2326</v>
       </c>
       <c r="D52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>2313</v>
+        <v>2321</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>2319</v>
+        <v>2327</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>2320</v>
+        <v>2328</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>2321</v>
+        <v>2329</v>
       </c>
     </row>
   </sheetData>

--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -21,7 +21,7 @@
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Equipements!$A$5:$R$112</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Obligations legales'!$A$5:$N$26</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Plaques par marque'!$A$5:$J$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Questionnaire!$A$5:$L$80</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Questionnaire!$A$5:$L$81</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Taches!$A$5:$O$159</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5193" uniqueCount="2330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5204" uniqueCount="2336">
   <si>
     <t xml:space="preserve">Referentiel d'entretien des equipements du logement - France</t>
   </si>
@@ -5526,7 +5526,7 @@
     <t xml:space="preserve">Q10</t>
   </si>
   <si>
-    <t xml:space="preserve">Avez-vous un véhicule ?</t>
+    <t xml:space="preserve">Un véhicule est-il rattaché à {residence} ?</t>
   </si>
   <si>
     <t xml:space="preserve">Voiture</t>
@@ -5535,6 +5535,12 @@
     <t xml:space="preserve">Date de première immatriculation (sur la carte grise) et du dernier contrôle technique (MM/AAAA).</t>
   </si>
   <si>
+    <t xml:space="preserve">Rattachez chaque véhicule à un seul logement, celui où il est principalement garé, pour ne pas le compter deux fois.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q01 = Un logement loué à l'année ; Q01 = Un logement loué en courte durée</t>
+  </si>
+  <si>
     <t xml:space="preserve">Moto, scooter ou quadricycle</t>
   </si>
   <si>
@@ -5607,7 +5613,19 @@
     <t xml:space="preserve">Pour la question Q01</t>
   </si>
   <si>
-    <t xml:space="preserve">La question Q01 n'est pas posée si le type de logement a déjà été renseigné à la création du lieu.</t>
+    <t xml:space="preserve">La question Q01 n'est pas posée si le type de logement a déjà été renseigné à la création du lieu. Sa réponse est alors déduite du type du lieu, et les conditions qui en dépendent (skip_if) s'appliquent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom du logement dans les questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour les textes contenant {residence}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans les textes, {residence} se remplace par « votre résidence principale » ou « votre résidence secondaire », selon le type du lieu.</t>
   </si>
   <si>
     <t xml:space="preserve">Q20</t>
@@ -22038,7 +22056,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:L80"/>
+  <dimension ref="A2:L81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -23762,13 +23780,13 @@
         <v>1832</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>153</v>
+        <v>1833</v>
       </c>
       <c r="J49" s="19" t="s">
         <v>153</v>
       </c>
       <c r="K49" s="19" t="s">
-        <v>153</v>
+        <v>1834</v>
       </c>
       <c r="L49" s="19" t="s">
         <v>153</v>
@@ -23791,7 +23809,7 @@
         <v>1793</v>
       </c>
       <c r="F50" s="18" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="G50" s="19" t="s">
         <v>881</v>
@@ -23806,13 +23824,13 @@
         <v>153</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>153</v>
+        <v>1834</v>
       </c>
       <c r="L50" s="19" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="16" t="s">
         <v>1829</v>
       </c>
@@ -23829,7 +23847,7 @@
         <v>1793</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="G51" s="19" t="s">
         <v>889</v>
@@ -23844,13 +23862,13 @@
         <v>153</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>153</v>
+        <v>1834</v>
       </c>
       <c r="L51" s="19" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="16" t="s">
         <v>1829</v>
       </c>
@@ -23882,13 +23900,13 @@
         <v>153</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>153</v>
+        <v>1834</v>
       </c>
       <c r="L52" s="19" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="16" t="s">
         <v>1829</v>
       </c>
@@ -23920,7 +23938,7 @@
         <v>153</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>153</v>
+        <v>1834</v>
       </c>
       <c r="L53" s="19" t="s">
         <v>153</v>
@@ -23928,7 +23946,7 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>1766</v>
@@ -23937,22 +23955,22 @@
         <v>11</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="G54" s="19" t="s">
         <v>636</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="J54" s="19" t="s">
         <v>153</v>
@@ -23966,7 +23984,7 @@
     </row>
     <row r="55" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>1766</v>
@@ -23975,19 +23993,19 @@
         <v>12</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="G55" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="I55" s="19" t="s">
         <v>153</v>
@@ -24004,7 +24022,7 @@
     </row>
     <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="16" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>1766</v>
@@ -24013,19 +24031,19 @@
         <v>13</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="G56" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="I56" s="19" t="s">
         <v>153</v>
@@ -24042,7 +24060,7 @@
     </row>
     <row r="57" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="16" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>1766</v>
@@ -24051,19 +24069,19 @@
         <v>14</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="G57" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="I57" s="19" t="s">
         <v>153</v>
@@ -24078,9 +24096,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="16" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>1766</v>
@@ -24089,19 +24107,19 @@
         <v>15</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="F58" s="18" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="G58" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="I58" s="19" t="s">
         <v>153</v>
@@ -24116,65 +24134,65 @@
         <v>153</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="24" t="s">
-        <v>1858</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>1859</v>
-      </c>
-      <c r="C59" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D59" s="26" t="s">
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="16" t="s">
         <v>1860</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="B59" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>1861</v>
       </c>
-      <c r="F59" s="26" t="s">
+      <c r="E59" s="16" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F59" s="18" t="s">
         <v>1862</v>
       </c>
-      <c r="G59" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="H59" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I59" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J59" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K59" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L59" s="25" t="s">
+      <c r="G59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>1863</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L59" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C60" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>1863</v>
+        <v>1868</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="H60" s="25" t="s">
         <v>153</v>
@@ -24194,25 +24212,25 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C61" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>384</v>
+        <v>1869</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="H61" s="25" t="s">
         <v>153</v>
@@ -24232,25 +24250,25 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C62" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>1864</v>
+        <v>384</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="H62" s="25" t="s">
         <v>153</v>
@@ -24270,25 +24288,25 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C63" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>398</v>
+        <v>1870</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H63" s="25" t="s">
         <v>153</v>
@@ -24308,25 +24326,25 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C64" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>1865</v>
+        <v>398</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="H64" s="25" t="s">
         <v>153</v>
@@ -24346,25 +24364,25 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C65" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>1866</v>
+        <v>1871</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="H65" s="25" t="s">
         <v>153</v>
@@ -24384,25 +24402,25 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C66" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>1867</v>
+        <v>1872</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>334</v>
+        <v>416</v>
       </c>
       <c r="H66" s="25" t="s">
         <v>153</v>
@@ -24422,25 +24440,25 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C67" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>1868</v>
+        <v>1873</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>441</v>
+        <v>334</v>
       </c>
       <c r="H67" s="25" t="s">
         <v>153</v>
@@ -24460,25 +24478,25 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C68" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>1869</v>
+        <v>1874</v>
       </c>
       <c r="G68" s="25" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H68" s="25" t="s">
         <v>153</v>
@@ -24498,25 +24516,25 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C69" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="G69" s="25" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="H69" s="25" t="s">
         <v>153</v>
@@ -24536,25 +24554,25 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C70" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>461</v>
+        <v>1876</v>
       </c>
       <c r="G70" s="25" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="H70" s="25" t="s">
         <v>153</v>
@@ -24574,31 +24592,31 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C71" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>1871</v>
+        <v>461</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>316</v>
+        <v>460</v>
       </c>
       <c r="H71" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I71" s="25" t="s">
-        <v>1872</v>
+        <v>153</v>
       </c>
       <c r="J71" s="25" t="s">
         <v>153</v>
@@ -24612,31 +24630,31 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C72" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>289</v>
+        <v>1877</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="H72" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I72" s="25" t="s">
-        <v>153</v>
+        <v>1878</v>
       </c>
       <c r="J72" s="25" t="s">
         <v>153</v>
@@ -24650,31 +24668,31 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C73" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E73" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>1873</v>
+        <v>289</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>647</v>
+        <v>288</v>
       </c>
       <c r="H73" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I73" s="25" t="s">
-        <v>1874</v>
+        <v>153</v>
       </c>
       <c r="J73" s="25" t="s">
         <v>153</v>
@@ -24688,31 +24706,31 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C74" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>714</v>
+        <v>1879</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>713</v>
+        <v>647</v>
       </c>
       <c r="H74" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I74" s="25" t="s">
-        <v>153</v>
+        <v>1880</v>
       </c>
       <c r="J74" s="25" t="s">
         <v>153</v>
@@ -24726,25 +24744,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C75" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>1875</v>
+        <v>714</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
       <c r="H75" s="25" t="s">
         <v>153</v>
@@ -24764,25 +24782,25 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C76" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>1876</v>
+        <v>1881</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>789</v>
+        <v>694</v>
       </c>
       <c r="H76" s="25" t="s">
         <v>153</v>
@@ -24802,25 +24820,25 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C77" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>799</v>
+        <v>1882</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="H77" s="25" t="s">
         <v>153</v>
@@ -24840,31 +24858,31 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C78" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>1877</v>
+        <v>799</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>1878</v>
+        <v>798</v>
       </c>
       <c r="H78" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I78" s="25" t="s">
-        <v>1879</v>
+        <v>153</v>
       </c>
       <c r="J78" s="25" t="s">
         <v>153</v>
@@ -24878,31 +24896,31 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B79" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C79" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>603</v>
+        <v>1884</v>
       </c>
       <c r="H79" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I79" s="25" t="s">
-        <v>153</v>
+        <v>1885</v>
       </c>
       <c r="J79" s="25" t="s">
         <v>153</v>
@@ -24916,44 +24934,82 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="24" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C80" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>1881</v>
+        <v>1886</v>
       </c>
       <c r="G80" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="H80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L80" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="24" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C81" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E81" s="24" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F81" s="26" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G81" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="H80" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I80" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J80" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K80" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L80" s="25" t="s">
+      <c r="H81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L81" s="25" t="s">
         <v>153</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L80"/>
+  <autoFilter ref="A5:L81"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -24986,349 +25042,349 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1882</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1883</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>1884</v>
+        <v>1890</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1885</v>
+        <v>1891</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1886</v>
+        <v>1892</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1887</v>
+        <v>1893</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1888</v>
+        <v>1894</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1890</v>
+        <v>1896</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1891</v>
+        <v>1897</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>1893</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1894</v>
+        <v>1900</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1895</v>
+        <v>1901</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1896</v>
+        <v>1902</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>1897</v>
+        <v>1903</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1898</v>
+        <v>1904</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>1899</v>
+        <v>1905</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>1900</v>
+        <v>1906</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>1901</v>
+        <v>1907</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>1902</v>
+        <v>1908</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1904</v>
+        <v>1910</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1904</v>
+        <v>1910</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1905</v>
+        <v>1911</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1907</v>
+        <v>1913</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G7" s="15" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>1916</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>1917</v>
+      </c>
+      <c r="J7" s="26" t="s">
         <v>1909</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>1910</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>1911</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1913</v>
+        <v>1919</v>
       </c>
       <c r="D8" s="15" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>1914</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>1908</v>
-      </c>
       <c r="G8" s="15" t="s">
-        <v>1916</v>
+        <v>1922</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>1917</v>
+        <v>1923</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>1918</v>
+        <v>1924</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1920</v>
+        <v>1926</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1921</v>
+        <v>1927</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>1923</v>
+        <v>1929</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>1924</v>
+        <v>1930</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>1925</v>
+        <v>1931</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>1926</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>1926</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>1920</v>
-      </c>
       <c r="D10" s="15" t="s">
-        <v>1927</v>
+        <v>1933</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>1929</v>
+        <v>1935</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>153</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>1930</v>
+        <v>1936</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1931</v>
+        <v>1937</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>1932</v>
+        <v>1938</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1934</v>
+        <v>1940</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1935</v>
+        <v>1941</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>1936</v>
+        <v>1942</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>1937</v>
+        <v>1943</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>1939</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1940</v>
+        <v>1946</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>1941</v>
+        <v>1947</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D12" s="15" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>1914</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>1942</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>1908</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>1936</v>
-      </c>
       <c r="H12" s="15" t="s">
-        <v>1944</v>
+        <v>1950</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>1945</v>
+        <v>1951</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1947</v>
+        <v>1953</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>1948</v>
+        <v>1954</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1949</v>
+        <v>1955</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>1950</v>
+        <v>1956</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>1953</v>
+        <v>1959</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>1954</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1955</v>
+        <v>1961</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>1956</v>
+        <v>1962</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1957</v>
+        <v>1963</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>1960</v>
+        <v>1966</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>1967</v>
+        <v>1973</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1968</v>
+        <v>1974</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>153</v>
@@ -25337,36 +25393,36 @@
         <v>181</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>1971</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>153</v>
@@ -25375,30 +25431,30 @@
         <v>153</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>153</v>
@@ -25407,30 +25463,30 @@
         <v>153</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>153</v>
@@ -25439,30 +25495,30 @@
         <v>153</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>153</v>
@@ -25471,59 +25527,59 @@
         <v>153</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1983</v>
+        <v>1989</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1985</v>
+        <v>1991</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>1986</v>
+        <v>1992</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>153</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1988</v>
+        <v>1994</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1990</v>
+        <v>1996</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>304</v>
@@ -25535,7 +25591,7 @@
         <v>153</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25543,22 +25599,22 @@
         <v>44</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>153</v>
@@ -25567,7 +25623,7 @@
         <v>153</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
     </row>
   </sheetData>
@@ -25607,12 +25663,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25620,78 +25676,78 @@
         <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>915</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="J6" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="L6" s="28" t="s">
         <v>153</v>
@@ -25700,92 +25756,92 @@
         <v>1592</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>2027</v>
+        <v>2033</v>
       </c>
       <c r="K7" s="28" t="s">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="L7" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>2029</v>
+        <v>2035</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>2033</v>
+        <v>2039</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>112</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>2037</v>
+        <v>2043</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="J8" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>2038</v>
+        <v>2044</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>2039</v>
+        <v>2045</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>153</v>
@@ -25793,31 +25849,31 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>2040</v>
+        <v>2046</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>2042</v>
+        <v>2048</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>2043</v>
+        <v>2049</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>112</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>2046</v>
+        <v>2052</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>2047</v>
+        <v>2053</v>
       </c>
       <c r="J9" s="28" t="s">
         <v>153</v>
@@ -25832,37 +25888,37 @@
         <v>153</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>2049</v>
+        <v>2055</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>2052</v>
+        <v>2058</v>
       </c>
       <c r="E10" s="15" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>2062</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>2053</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>2054</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>2055</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>2056</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>2047</v>
-      </c>
       <c r="J10" s="28" t="s">
         <v>153</v>
       </c>
@@ -25876,39 +25932,39 @@
         <v>153</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>2057</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>2064</v>
+        <v>2070</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>2067</v>
+        <v>2073</v>
       </c>
       <c r="K11" s="28" t="s">
         <v>153</v>
@@ -25920,48 +25976,48 @@
         <v>153</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>2069</v>
+        <v>2075</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>2070</v>
+        <v>2076</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>2072</v>
+        <v>2078</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="G12" s="15" t="s">
         <v>642</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>2075</v>
+        <v>2081</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="L12" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>2078</v>
+        <v>2084</v>
       </c>
       <c r="N12" s="28" t="s">
         <v>153</v>
@@ -25969,43 +26025,43 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>2079</v>
+        <v>2085</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>2080</v>
+        <v>2086</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>2081</v>
+        <v>2087</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>2082</v>
+        <v>2088</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>2087</v>
+        <v>2093</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>2088</v>
+        <v>2094</v>
       </c>
       <c r="K13" s="28" t="s">
         <v>153</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>2090</v>
+        <v>2096</v>
       </c>
       <c r="N13" s="28" t="s">
         <v>153</v>
@@ -26013,31 +26069,31 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>2091</v>
+        <v>2097</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>2092</v>
+        <v>2098</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>2093</v>
+        <v>2099</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>2094</v>
+        <v>2100</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>2095</v>
+        <v>2101</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>2096</v>
+        <v>2102</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>2097</v>
+        <v>2103</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>2098</v>
+        <v>2104</v>
       </c>
       <c r="J14" s="28" t="s">
         <v>153</v>
@@ -26052,39 +26108,39 @@
         <v>153</v>
       </c>
       <c r="N14" s="28" t="s">
-        <v>2099</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>2100</v>
+        <v>2106</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>2101</v>
+        <v>2107</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>2102</v>
+        <v>2108</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>2103</v>
+        <v>2109</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>2104</v>
+        <v>2110</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>2105</v>
+        <v>2111</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>2106</v>
+        <v>2112</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>2108</v>
+        <v>2114</v>
       </c>
       <c r="K15" s="28" t="s">
         <v>153</v>
@@ -26096,36 +26152,36 @@
         <v>153</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>2109</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>2110</v>
+        <v>2116</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>1669</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2111</v>
+        <v>2117</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2112</v>
+        <v>2118</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>153</v>
@@ -26134,86 +26190,86 @@
         <v>153</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="M16" s="28" t="s">
         <v>153</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>2120</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="G17" s="15" t="s">
         <v>2121</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>2122</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="H17" s="15" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I17" s="15" t="s">
         <v>2123</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>2113</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>2114</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>2115</v>
-      </c>
-      <c r="H17" s="15" t="s">
+      <c r="J17" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" s="28" t="s">
         <v>2124</v>
       </c>
-      <c r="I17" s="15" t="s">
-        <v>2117</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="L17" s="28" t="s">
-        <v>2118</v>
-      </c>
       <c r="M17" s="28" t="s">
         <v>153</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>2126</v>
+        <v>2132</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2128</v>
+        <v>2134</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>2129</v>
+        <v>2135</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>2054</v>
+        <v>2060</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>2130</v>
+        <v>2136</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>2131</v>
+        <v>2137</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>2132</v>
+        <v>2138</v>
       </c>
       <c r="J18" s="28" t="s">
         <v>153</v>
@@ -26222,54 +26278,54 @@
         <v>153</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>2133</v>
+        <v>2139</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>2134</v>
+        <v>2140</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>2135</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>2136</v>
+        <v>2142</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2138</v>
+        <v>2144</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2139</v>
+        <v>2145</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>2140</v>
+        <v>2146</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>2141</v>
+        <v>2147</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>2142</v>
+        <v>2148</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>2143</v>
+        <v>2149</v>
       </c>
       <c r="J19" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>2144</v>
+        <v>2150</v>
       </c>
       <c r="L19" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>2145</v>
+        <v>2151</v>
       </c>
       <c r="N19" s="28" t="s">
         <v>153</v>
@@ -26277,31 +26333,31 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>2146</v>
+        <v>2152</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>2147</v>
+        <v>2153</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>2054</v>
+        <v>2060</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>2151</v>
+        <v>2157</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>2152</v>
+        <v>2158</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>2153</v>
+        <v>2159</v>
       </c>
       <c r="J20" s="28" t="s">
         <v>153</v>
@@ -26310,42 +26366,42 @@
         <v>153</v>
       </c>
       <c r="L20" s="28" t="s">
-        <v>2154</v>
+        <v>2160</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="N20" s="28" t="s">
-        <v>2156</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>2157</v>
+        <v>2163</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>2158</v>
+        <v>2164</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2159</v>
+        <v>2165</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>2160</v>
+        <v>2166</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>2161</v>
+        <v>2167</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>847</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>2162</v>
+        <v>2168</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>2163</v>
+        <v>2169</v>
       </c>
       <c r="J21" s="28" t="s">
         <v>153</v>
@@ -26360,36 +26416,36 @@
         <v>153</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>2164</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>2165</v>
+        <v>2171</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>2166</v>
+        <v>2172</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2167</v>
+        <v>2173</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2168</v>
+        <v>2174</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>2169</v>
+        <v>2175</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>2170</v>
+        <v>2176</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>2171</v>
+        <v>2177</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>2172</v>
+        <v>2178</v>
       </c>
       <c r="J22" s="28" t="s">
         <v>153</v>
@@ -26401,39 +26457,39 @@
         <v>153</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>2173</v>
+        <v>2179</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>2174</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>2175</v>
+        <v>2181</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>2176</v>
+        <v>2182</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2177</v>
+        <v>2183</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>2179</v>
+        <v>2185</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>2180</v>
+        <v>2186</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>227</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>2181</v>
+        <v>2187</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>2172</v>
+        <v>2178</v>
       </c>
       <c r="J23" s="28" t="s">
         <v>153</v>
@@ -26442,10 +26498,10 @@
         <v>153</v>
       </c>
       <c r="L23" s="28" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="M23" s="28" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="N23" s="28" t="s">
         <v>153</v>
@@ -26453,31 +26509,31 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>2185</v>
+        <v>2191</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2186</v>
+        <v>2192</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>2187</v>
+        <v>2193</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>2188</v>
+        <v>2194</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>2189</v>
+        <v>2195</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>2190</v>
+        <v>2196</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>2191</v>
+        <v>2197</v>
       </c>
       <c r="J24" s="28" t="s">
         <v>153</v>
@@ -26489,42 +26545,42 @@
         <v>153</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>2192</v>
+        <v>2198</v>
       </c>
       <c r="N24" s="28" t="s">
-        <v>2193</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>2194</v>
+        <v>2200</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>2195</v>
+        <v>2201</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2196</v>
+        <v>2202</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>872</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>2197</v>
+        <v>2203</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>2198</v>
+        <v>2204</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>875</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>2199</v>
+        <v>2205</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>2201</v>
+        <v>2207</v>
       </c>
       <c r="K25" s="28" t="s">
         <v>153</v>
@@ -26536,27 +26592,27 @@
         <v>153</v>
       </c>
       <c r="N25" s="28" t="s">
-        <v>2202</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>2203</v>
+        <v>2209</v>
       </c>
       <c r="B26" s="18" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>2213</v>
+      </c>
+      <c r="F26" s="15" t="s">
         <v>2204</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>2205</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>2206</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>2207</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>2198</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>875</v>
@@ -26565,10 +26621,10 @@
         <v>887</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>2208</v>
+        <v>2214</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>2201</v>
+        <v>2207</v>
       </c>
       <c r="K26" s="28" t="s">
         <v>153</v>
@@ -26612,26 +26668,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2209</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2210</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>2211</v>
+        <v>2217</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2212</v>
+        <v>2218</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2213</v>
+        <v>2219</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2214</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26639,7 +26695,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>2215</v>
+        <v>2221</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>41</v>
@@ -26651,7 +26707,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>2216</v>
+        <v>2222</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>42</v>
@@ -26663,7 +26719,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>2217</v>
+        <v>2223</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>43</v>
@@ -26675,7 +26731,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>2218</v>
+        <v>2224</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>44</v>
@@ -26687,13 +26743,13 @@
         <v>35</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>2219</v>
+        <v>2225</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>2220</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26701,7 +26757,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>2221</v>
+        <v>2227</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>46</v>
@@ -26713,7 +26769,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>2222</v>
+        <v>2228</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>47</v>
@@ -26725,7 +26781,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>2223</v>
+        <v>2229</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>48</v>
@@ -26737,13 +26793,13 @@
         <v>35</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>2224</v>
+        <v>2230</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>2225</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26751,191 +26807,191 @@
         <v>35</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>2226</v>
+        <v>2232</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2220</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>2227</v>
+        <v>2233</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>2228</v>
+        <v>2234</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2229</v>
+        <v>2235</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2230</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>2227</v>
+        <v>2233</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>2231</v>
+        <v>2237</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>2232</v>
+        <v>2238</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>2233</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>2227</v>
+        <v>2233</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>2234</v>
+        <v>2240</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2235</v>
+        <v>2241</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2236</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>2237</v>
+        <v>2243</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>2238</v>
+        <v>2244</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2240</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>2237</v>
+        <v>2243</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>2241</v>
+        <v>2247</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2242</v>
+        <v>2248</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2243</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>2237</v>
+        <v>2243</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>2246</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>2237</v>
+        <v>2243</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2247</v>
+        <v>2253</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2248</v>
+        <v>2254</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2249</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2251</v>
+        <v>2257</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2252</v>
+        <v>2258</v>
       </c>
       <c r="D23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2253</v>
+        <v>2259</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2254</v>
+        <v>2260</v>
       </c>
       <c r="D24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>2255</v>
+        <v>2261</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2256</v>
+        <v>2262</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>2257</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>2258</v>
+        <v>2264</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2259</v>
+        <v>2265</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>2260</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>2261</v>
+        <v>2267</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>2262</v>
+        <v>2268</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>2263</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>2264</v>
+        <v>2270</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>2265</v>
+        <v>2271</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>2266</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26943,13 +26999,13 @@
         <v>53</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>2267</v>
+        <v>2273</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>56</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>2268</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26957,13 +27013,13 @@
         <v>53</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2269</v>
+        <v>2275</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>2270</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26971,317 +27027,317 @@
         <v>53</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>2271</v>
+        <v>2277</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>60</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>2272</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2274</v>
+        <v>2280</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>112</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>2275</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2276</v>
+        <v>2282</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>2277</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>2278</v>
+        <v>2284</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>2279</v>
+        <v>2285</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>2280</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>2281</v>
+        <v>2287</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>2282</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>2283</v>
+        <v>2289</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>2284</v>
+        <v>2290</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>2285</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>2286</v>
+        <v>2292</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>581</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>2287</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>2288</v>
+        <v>2294</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>779</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>2289</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>2291</v>
+        <v>2297</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>2292</v>
+        <v>2298</v>
       </c>
       <c r="D39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>2293</v>
+        <v>2299</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>2294</v>
+        <v>2300</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>2295</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>2296</v>
+        <v>2302</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>2297</v>
+        <v>2303</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>2298</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>2299</v>
+        <v>2305</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>2300</v>
+        <v>2306</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>2301</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>2303</v>
+        <v>2309</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>2304</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>2305</v>
+        <v>2311</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>2306</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>2307</v>
+        <v>2313</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>74</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>2308</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>2309</v>
+        <v>2315</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>75</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>2310</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>2311</v>
+        <v>2317</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>2312</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>2313</v>
+        <v>2319</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>2314</v>
+        <v>2320</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>2315</v>
+        <v>2321</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>2316</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>2313</v>
+        <v>2319</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>2317</v>
+        <v>2323</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>2318</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>2313</v>
+        <v>2319</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>2319</v>
+        <v>2325</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1908</v>
+        <v>1914</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>2320</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>2321</v>
+        <v>2327</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>2322</v>
+        <v>2328</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>2323</v>
+        <v>2329</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>2324</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>2321</v>
+        <v>2327</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>2325</v>
+        <v>2331</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>2326</v>
+        <v>2332</v>
       </c>
       <c r="D52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>2321</v>
+        <v>2327</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>2327</v>
+        <v>2333</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>2328</v>
+        <v>2334</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>2329</v>
+        <v>2335</v>
       </c>
     </row>
   </sheetData>

--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -13,15 +13,17 @@
     <sheet name="Equipements" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Taches" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Questionnaire" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Plaques par marque" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Obligations legales" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Referentiel" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Questions de date" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Plaques par marque" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Obligations legales" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Referentiel" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Equipements!$A$5:$R$112</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Obligations legales'!$A$5:$N$26</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Plaques par marque'!$A$5:$J$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Questionnaire!$A$5:$L$81</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Obligations legales'!$A$5:$N$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Plaques par marque'!$A$5:$J$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Questionnaire!$A$5:$M$87</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Questions de date'!$A$5:$G$41</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Taches!$A$5:$O$159</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5204" uniqueCount="2336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5614" uniqueCount="2431">
   <si>
     <t xml:space="preserve">Referentiel d'entretien des equipements du logement - France</t>
   </si>
@@ -4116,19 +4118,19 @@
     <t xml:space="preserve">T-083</t>
   </si>
   <si>
-    <t xml:space="preserve">Remplacement de la pile et controle de la date limite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tous les ans (pile) / 10 ans (appareil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meme mois chaque annee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pile 9V ou lithium selon modele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remplacer la pile meme sans signal de defaut. Verifier la date de fabrication imprimee au dos : un DAAF se remplace integralement au bout de 10 ans.</t>
+    <t xml:space="preserve">Remplacement du detecteur de fumee (10 ans apres fabrication)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 ans apres la date de fabrication imprimee au dos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selon echeance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detecteur neuf certifie NF EN 14604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remplacer l'appareil complet 10 ans apres sa date de fabrication, ou des qu'il signale sa fin de vie. Les modeles recents ont une pile scellee de 10 ans : rien a changer entre-temps. Sur un ancien modele a pile remplacable, changer la pile chaque annee.</t>
   </si>
   <si>
     <t xml:space="preserve">Detecteur hors service sans que personne ne s'en apercoive</t>
@@ -4185,9 +4187,6 @@
     <t xml:space="preserve">Controle technique quinquennal</t>
   </si>
   <si>
-    <t xml:space="preserve">Selon echeance</t>
-  </si>
-  <si>
     <t xml:space="preserve">Organisme de controle agree</t>
   </si>
   <si>
@@ -5247,7 +5246,7 @@
     <t xml:space="preserve">Questionnaire d'accueil : premiere utilisation et nouveau lieu</t>
   </si>
   <si>
-    <t xml:space="preserve">Une ligne = une reponse possible. Pour chaque obligation créée, la date du dernier passage (entretien, ramonage, contrôle ou vidange) se donne en chiffres (MM/AAAA). Réponses graduées : date précise → calcul normal ; fait récemment, sans date exacte → à confirmer (orange), avec un rappel pour la préciser ; plus ancien que le délai légal → en retard (rouge) ; jamais réalisé ou je ne sais pas → en retard (rouge), prioritaire.</t>
+    <t xml:space="preserve">Une ligne = une reponse possible. Chaque obligation a sa propre question de date (onglet Questions de date, seed/date_questions.json), qui nomme l'appareil et l'intervention. Réponses graduées avec le vrai délai de l'obligation : mois et année → calcul normal ; « Il y a moins de {délai} », sans date précise → à confirmer (orange) ; « Il y a plus de {délai} » → en retard (rouge) ; « Jamais » ou « Je ne sais pas » → en retard, prioritaire. Les dates se choisissent dans deux listes (mois en toutes lettres, année) et s'affichent « septembre 2026 », jamais avec un jour.</t>
   </si>
   <si>
     <t xml:space="preserve">Bloc</t>
@@ -5283,6 +5282,9 @@
     <t xml:space="preserve">Renseigne</t>
   </si>
   <si>
+    <t xml:space="preserve">Statut initial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q01</t>
   </si>
   <si>
@@ -5343,7 +5345,7 @@
     <t xml:space="preserve">Chaudière au gaz de ville</t>
   </si>
   <si>
-    <t xml:space="preserve">Évacue-t-elle ses fumées par un conduit de cheminée, et non par une ventouse murale ?</t>
+    <t xml:space="preserve">Est-elle raccordée à un conduit de cheminée, et non à une ventouse (un tuyau qui sort directement du mur) ?</t>
   </si>
   <si>
     <t xml:space="preserve">Chaudière au propane (citerne)</t>
@@ -5481,9 +5483,6 @@
     <t xml:space="preserve">CUIS-03, CUIS-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Date de péremption imprimée sur le tuyau flexible (MM/AAAA).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Indice : des brûleurs à flamme signalent une cuisson au gaz.</t>
   </si>
   <si>
@@ -5496,9 +5495,6 @@
     <t xml:space="preserve">Non, fosse septique ou fosse toutes eaux</t>
   </si>
   <si>
-    <t xml:space="preserve">Date du dernier contrôle du SPANC et de la dernière vidange.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Non, micro-station d'épuration</t>
   </si>
   <si>
@@ -5511,7 +5507,25 @@
     <t xml:space="preserve">Avez-vous une piscine enterrée ou semi-enterrée ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Le dispositif de sécurité est-il une alarme ? (Sinon : barrière, couverture ou abri.)</t>
+    <t xml:space="preserve">Oui, protégée par une barrière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui, protégée par une alarme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIS-01, PIS-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui, protégée par une couverture ou un abri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui, sans dispositif de sécurité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un dispositif de sécurité est obligatoire : l'obligation apparaîtra en retard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-093 = jamais</t>
   </si>
   <si>
     <t xml:space="preserve">Q09</t>
@@ -5520,9 +5534,6 @@
     <t xml:space="preserve">Avez-vous un puits ou un forage ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Est-il déclaré en mairie ?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q10</t>
   </si>
   <si>
@@ -5532,9 +5543,6 @@
     <t xml:space="preserve">Voiture</t>
   </si>
   <si>
-    <t xml:space="preserve">Date de première immatriculation (sur la carte grise) et du dernier contrôle technique (MM/AAAA).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rattachez chaque véhicule à un seul logement, celui où il est principalement garé, pour ne pas le compter deux fois.</t>
   </si>
   <si>
@@ -5547,157 +5555,439 @@
     <t xml:space="preserve">Vélo électrique</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO-01</t>
+    <t xml:space="preserve">Q11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avez-vous un détecteur de fumée installé ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obligatoire dans tout logement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obligatoire dans tout logement : l'installation apparaîtra en retard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-082 = jamais ; T-083 = jamais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indice : il se trouve en général au plafond d'un couloir ou d'un palier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-083 = jamais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date du dernier passage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour chaque obligation créée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaque obligation a sa propre question de date (onglet Questions de date, seed/date_questions.json), qui nomme l'appareil et l'intervention. Réponses graduées avec le vrai délai de l'obligation : mois et année → calcul normal ; « Il y a moins de {délai} », sans date précise → à confirmer (orange) ; « Il y a plus de {délai} » → en retard (rouge) ; « Jamais » ou « Je ne sais pas » → en retard, prioritaire. Les dates se choisissent dans deux listes (mois en toutes lettres, année) et s'affichent « septembre 2026 », jamais avec un jour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réponse « Je ne sais pas »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour chaque question d'obligation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« Je ne sais pas » ne bloque jamais la progression : la réponse ajoute un point « à vérifier » sur l'écran d'accueil, avec l'aide associée pour trouver la réponse. Même règle pour les questions de suivi. À l'écran, c'est un choix discret, sous les autres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appareil et conduit de fumée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour chaque réponse créant un appareil et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand une réponse crée un appareil à combustion et son conduit de fumée (poêle, insert, chaudière), une seule question de date couvre les deux : l'entretien et le ramonage se font au même passage. Un lien « faits séparément ? » permet de donner deux dates, ou d'indiquer que seul l'un des deux a été fait.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type de logement déjà connu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour la question Q01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La question Q01 n'est pas posée si le type de logement a déjà été renseigné à la création du lieu. Sa réponse est alors déduite du type du lieu, et les conditions qui en dépendent (skip_if) s'appliquent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom du logement dans les questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour les textes contenant {residence}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans les textes, {residence} se remplace par « votre résidence principale » ou « votre résidence secondaire », selon le type du lieu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGLE-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statut initial fixé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour les réponses qui fixent un statut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si une réponse fixe le statut initial d'une tâche (colonne Statut initial), sa question de date n'est pas posée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entretien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quels appareils avez-vous ? (facultatif)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cases a cocher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réfrigérateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congélateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sèche-linge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaque à induction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micro-ondes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine à café</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspirateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple flux par défaut ; double flux à préciser ensuite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Détecteur de monoxyde de carbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommandé dès qu'un appareil à combustion est présent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portail motorisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tondeuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panneaux solaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENE-01, ENE-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crée aussi l'onduleur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borne de recharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gouttières</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une question de date par obligation, avec le vrai delai legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mois gradue : mois et annee | Il y a moins de {delai} | Il y a plus de {delai} | Jamais | Je ne sais pas. Affichage des dates : septembre 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appareil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaudière au gaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la chaudière a-t-elle été entretenue pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mois gradué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un an</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le poêle à granulés a-t-il été entretenu pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le poêle ou l'insert a-t-il été entretenu pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduit de fumée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le conduit de fumée a-t-il été ramoné pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posée seule quand l'appareil et le conduit ont été faits à des dates différentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la cheminée a-t-elle été ramonée pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-001+T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-001, T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaudière au gaz et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la chaudière a-t-elle été entretenue et son conduit ramoné pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question commune à l'appareil et à son conduit (REGLE-03).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-004+T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-004, T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaudière au fioul et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-006+T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-006, T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaudière bois ou granulés et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-010+T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-010, T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poêle à granulés et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le poêle à granulés a-t-il été entretenu et son conduit ramoné pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-013+T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-013, T-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poêle ou insert à bois et son conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le poêle ou l'insert a-t-il été entretenu et son conduit ramoné pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pompe à chaleur air/eau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la pompe à chaleur a-t-elle été entretenue pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 ans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pompe à chaleur air/air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pompe à chaleur géothermique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la pompe à chaleur géothermique a-t-elle été entretenue pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le chauffe-eau thermodynamique a-t-il été entretenu pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le chauffe-eau au gaz a-t-il été entretenu pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la climatisation a-t-elle été entretenue pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pompe à chaleur de piscine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la pompe à chaleur de la piscine a-t-elle été entretenue pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circuit de climatisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand l'étanchéité du circuit de climatisation a-t-elle été contrôlée pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citerne de propane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand votre fournisseur de gaz a-t-il contrôlé la citerne pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 ans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selon le contrat du fournisseur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosse septique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la fosse a-t-elle été vidangée pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 ans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Délai indicatif : la vidange dépend du niveau de boues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le SPANC est-il venu contrôler l'installation pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La commune peut fixer un délai plus court.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micro-station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la micro-station a-t-elle été entretenue pour la dernière fois ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascenseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand l'ascenseur a-t-il passé son dernier contrôle technique ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation de gaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le diagnostic de l'installation de gaz a-t-il été réalisé ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 ans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exigé à la vente (valable 3 ans) ou à la mise en location (6 ans).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuyau de gaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle date de péremption est imprimée sur le tuyau de gaz de la cuisinière ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Péremption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mois et année, ou « Je ne trouve pas la date » (à confirmer). La date donnée devient l'échéance.</t>
   </si>
   <si>
     <t xml:space="preserve">Détecteur de fumée</t>
   </si>
   <si>
-    <t xml:space="preserve">Automatique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajouté d'office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est-il installé ? Si oui, notez la date de fabrication imprimée au dos (MM/AAAA) : elle fixe son remplacement, 10 ans après.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obligatoire dans tout logement : il n'y a pas de question à poser.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGLE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date du dernier passage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour chaque obligation créée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour chaque obligation créée, la date du dernier passage (entretien, ramonage, contrôle ou vidange) se donne en chiffres (MM/AAAA). Réponses graduées : date précise → calcul normal ; fait récemment, sans date exacte → à confirmer (orange), avec un rappel pour la préciser ; plus ancien que le délai légal → en retard (rouge) ; jamais réalisé ou je ne sais pas → en retard (rouge), prioritaire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGLE-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réponse « Je ne sais pas »</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour chaque question d'obligation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">« Je ne sais pas » ne bloque jamais la progression : la réponse ajoute un point « à vérifier » sur l'écran d'accueil, avec l'aide associée pour trouver la réponse. Même règle pour les questions de suivi. À l'écran, c'est un choix discret, sous les autres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGLE-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appareil et conduit de fumée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour chaque réponse créant un appareil et son conduit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quand une réponse crée un appareil à combustion et son conduit de fumée (poêle, insert, chaudière), une seule question de date couvre les deux : l'entretien et le ramonage se font au même passage. Un lien « faits séparément ? » permet de donner deux dates, ou d'indiquer que seul l'un des deux a été fait.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGLE-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type de logement déjà connu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour la question Q01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La question Q01 n'est pas posée si le type de logement a déjà été renseigné à la création du lieu. Sa réponse est alors déduite du type du lieu, et les conditions qui en dépendent (skip_if) s'appliquent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGLE-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nom du logement dans les questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour les textes contenant {residence}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dans les textes, {residence} se remplace par « votre résidence principale » ou « votre résidence secondaire », selon le type du lieu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entretien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quels appareils avez-vous ? (facultatif)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cases a cocher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réfrigérateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congélateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sèche-linge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Four</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaque à induction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micro-ondes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine à café</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspirateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple flux par défaut ; double flux à préciser ensuite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Détecteur de monoxyde de carbone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommandé dès qu'un appareil à combustion est présent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portail motorisé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tondeuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panneaux solaires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENE-01, ENE-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crée aussi l'onduleur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borne de recharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gouttières</t>
+    <t xml:space="preserve">Quelle date est imprimée au dos du détecteur ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabrication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explication affichée : un détecteur se remplace 10 ans après sa fabrication. Mois et année, ou « Je ne la trouve pas » (à confirmer). Échéance = date + 10 ans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand la voiture a-t-elle passé son dernier contrôle technique ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôle véhicule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option en plus : « Jamais, elle a moins de 4 ans ». On demande alors la date de première immatriculation ; échéance = cette date + 4 ans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quand le véhicule a-t-il passé son dernier contrôle technique ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option en plus : « Jamais, il a moins de 5 ans ». Échéance = date de première immatriculation + 5 ans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puits ou forage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le puits est-il déclaré en mairie ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui / non</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui → à jour ; Non → en retard (à déclarer) ; Je ne sais pas → à confirmer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test mensuel : démarre à la création.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visite toutes les 6 semaines : démarre à la création.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôle mensuel du dispositif : démarre à la création, sauf statut initial fixé par le questionnaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non générée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second ramonage : seulement au-delà de 6 m³ de bois ou 2,5 t de granulés par an.</t>
   </si>
   <si>
     <t xml:space="preserve">Aide adaptative a la marque : ou lire la plaque et quel identifiant valider</t>
@@ -6688,9 +6978,6 @@
   </si>
   <si>
     <t xml:space="preserve">Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cle</t>
   </si>
   <si>
     <t xml:space="preserve">Libelle</t>
@@ -7482,6 +7769,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -8258,7 +8549,7 @@
       </c>
       <c r="C31" s="16" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Taches!$F$6:$F$250="DIY")*(Taches!$G$6:$G$250&gt;0)*Taches!$J$6:$J$250*(12/IF(Taches!$G$6:$G$250=0,1,Taches!$G$6:$G$250)))/60,0)</f>
-        <v>199.805555555556</v>
+        <v>199.663888888889</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18582,7 +18873,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="17" t="s">
         <v>1359</v>
       </c>
@@ -18603,7 +18894,7 @@
         <v>922</v>
       </c>
       <c r="G88" s="16" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="H88" s="19" t="s">
         <v>1361</v>
@@ -18612,7 +18903,7 @@
         <v>1362</v>
       </c>
       <c r="J88" s="16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K88" s="19" t="s">
         <v>1363</v>
@@ -18801,19 +19092,19 @@
         <v>1191</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>1383</v>
+        <v>1362</v>
       </c>
       <c r="J92" s="16" t="n">
         <v>180</v>
       </c>
       <c r="K92" s="19" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L92" s="19" t="s">
         <v>1384</v>
       </c>
-      <c r="L92" s="19" t="s">
+      <c r="M92" s="19" t="s">
         <v>1385</v>
-      </c>
-      <c r="M92" s="19" t="s">
-        <v>1386</v>
       </c>
       <c r="N92" s="17" t="s">
         <v>97</v>
@@ -18824,7 +19115,7 @@
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="23" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B93" s="24" t="s">
         <v>694</v>
@@ -18837,7 +19128,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F93" s="24" t="s">
         <v>922</v>
@@ -18855,13 +19146,13 @@
         <v>30</v>
       </c>
       <c r="K93" s="25" t="s">
+        <v>1388</v>
+      </c>
+      <c r="L93" s="25" t="s">
         <v>1389</v>
       </c>
-      <c r="L93" s="25" t="s">
+      <c r="M93" s="25" t="s">
         <v>1390</v>
-      </c>
-      <c r="M93" s="25" t="s">
-        <v>1391</v>
       </c>
       <c r="N93" s="24" t="s">
         <v>191</v>
@@ -18872,7 +19163,7 @@
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="23" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B94" s="24" t="s">
         <v>694</v>
@@ -18885,7 +19176,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="F94" s="24" t="s">
         <v>922</v>
@@ -18903,13 +19194,13 @@
         <v>10</v>
       </c>
       <c r="K94" s="25" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L94" s="25" t="s">
         <v>1394</v>
       </c>
-      <c r="L94" s="25" t="s">
+      <c r="M94" s="25" t="s">
         <v>1395</v>
-      </c>
-      <c r="M94" s="25" t="s">
-        <v>1396</v>
       </c>
       <c r="N94" s="24" t="s">
         <v>191</v>
@@ -18920,7 +19211,7 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="23" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B95" s="24" t="s">
         <v>706</v>
@@ -18933,7 +19224,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="F95" s="24" t="s">
         <v>922</v>
@@ -18951,13 +19242,13 @@
         <v>20</v>
       </c>
       <c r="K95" s="25" t="s">
+        <v>1398</v>
+      </c>
+      <c r="L95" s="25" t="s">
         <v>1399</v>
       </c>
-      <c r="L95" s="25" t="s">
+      <c r="M95" s="25" t="s">
         <v>1400</v>
-      </c>
-      <c r="M95" s="25" t="s">
-        <v>1401</v>
       </c>
       <c r="N95" s="24" t="s">
         <v>191</v>
@@ -18968,7 +19259,7 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="23" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B96" s="24" t="s">
         <v>713</v>
@@ -18981,7 +19272,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="F96" s="24" t="s">
         <v>922</v>
@@ -18999,13 +19290,13 @@
         <v>30</v>
       </c>
       <c r="K96" s="25" t="s">
+        <v>1403</v>
+      </c>
+      <c r="L96" s="25" t="s">
         <v>1404</v>
       </c>
-      <c r="L96" s="25" t="s">
+      <c r="M96" s="25" t="s">
         <v>1405</v>
-      </c>
-      <c r="M96" s="25" t="s">
-        <v>1406</v>
       </c>
       <c r="N96" s="24" t="s">
         <v>191</v>
@@ -19016,7 +19307,7 @@
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="23" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B97" s="24" t="s">
         <v>721</v>
@@ -19029,7 +19320,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="F97" s="24" t="s">
         <v>922</v>
@@ -19047,13 +19338,13 @@
         <v>45</v>
       </c>
       <c r="K97" s="25" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L97" s="25" t="s">
         <v>1409</v>
       </c>
-      <c r="L97" s="25" t="s">
+      <c r="M97" s="25" t="s">
         <v>1410</v>
-      </c>
-      <c r="M97" s="25" t="s">
-        <v>1411</v>
       </c>
       <c r="N97" s="24" t="s">
         <v>191</v>
@@ -19064,7 +19355,7 @@
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="17" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B98" s="16" t="s">
         <v>734</v>
@@ -19077,7 +19368,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F98" s="16" t="s">
         <v>922</v>
@@ -19098,10 +19389,10 @@
         <v>1022</v>
       </c>
       <c r="L98" s="19" t="s">
+        <v>1413</v>
+      </c>
+      <c r="M98" s="19" t="s">
         <v>1414</v>
-      </c>
-      <c r="M98" s="19" t="s">
-        <v>1415</v>
       </c>
       <c r="N98" s="17" t="s">
         <v>97</v>
@@ -19112,7 +19403,7 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="23" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B99" s="24" t="s">
         <v>744</v>
@@ -19125,7 +19416,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F99" s="24" t="s">
         <v>922</v>
@@ -19137,19 +19428,19 @@
         <v>960</v>
       </c>
       <c r="I99" s="25" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="J99" s="24" t="n">
         <v>15</v>
       </c>
       <c r="K99" s="25" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L99" s="25" t="s">
         <v>1419</v>
       </c>
-      <c r="L99" s="25" t="s">
+      <c r="M99" s="25" t="s">
         <v>1420</v>
-      </c>
-      <c r="M99" s="25" t="s">
-        <v>1421</v>
       </c>
       <c r="N99" s="24" t="s">
         <v>191</v>
@@ -19160,7 +19451,7 @@
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B100" s="27" t="s">
         <v>744</v>
@@ -19173,7 +19464,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F100" s="27" t="s">
         <v>201</v>
@@ -19182,7 +19473,7 @@
         <v>72</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="I100" s="28" t="s">
         <v>1033</v>
@@ -19191,13 +19482,13 @@
         <v>180</v>
       </c>
       <c r="K100" s="28" t="s">
+        <v>1424</v>
+      </c>
+      <c r="L100" s="28" t="s">
         <v>1425</v>
       </c>
-      <c r="L100" s="28" t="s">
+      <c r="M100" s="28" t="s">
         <v>1426</v>
-      </c>
-      <c r="M100" s="28" t="s">
-        <v>1427</v>
       </c>
       <c r="N100" s="27" t="s">
         <v>191</v>
@@ -19208,7 +19499,7 @@
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="23" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B101" s="24" t="s">
         <v>752</v>
@@ -19221,7 +19512,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="F101" s="24" t="s">
         <v>922</v>
@@ -19233,7 +19524,7 @@
         <v>960</v>
       </c>
       <c r="I101" s="25" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="J101" s="24" t="n">
         <v>10</v>
@@ -19242,10 +19533,10 @@
         <v>1022</v>
       </c>
       <c r="L101" s="25" t="s">
+        <v>1429</v>
+      </c>
+      <c r="M101" s="25" t="s">
         <v>1430</v>
-      </c>
-      <c r="M101" s="25" t="s">
-        <v>1431</v>
       </c>
       <c r="N101" s="24" t="s">
         <v>191</v>
@@ -19256,7 +19547,7 @@
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="23" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B102" s="24" t="s">
         <v>752</v>
@@ -19269,7 +19560,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E102" s="26" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F102" s="24" t="s">
         <v>922</v>
@@ -19281,19 +19572,19 @@
         <v>1020</v>
       </c>
       <c r="I102" s="25" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="J102" s="24" t="n">
         <v>120</v>
       </c>
       <c r="K102" s="25" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L102" s="25" t="s">
         <v>1435</v>
       </c>
-      <c r="L102" s="25" t="s">
+      <c r="M102" s="25" t="s">
         <v>1436</v>
-      </c>
-      <c r="M102" s="25" t="s">
-        <v>1437</v>
       </c>
       <c r="N102" s="24" t="s">
         <v>191</v>
@@ -19304,7 +19595,7 @@
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="23" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B103" s="24" t="s">
         <v>752</v>
@@ -19317,7 +19608,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E103" s="26" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F103" s="24" t="s">
         <v>922</v>
@@ -19329,19 +19620,19 @@
         <v>1020</v>
       </c>
       <c r="I103" s="25" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="J103" s="24" t="n">
         <v>180</v>
       </c>
       <c r="K103" s="25" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L103" s="25" t="s">
         <v>1441</v>
       </c>
-      <c r="L103" s="25" t="s">
+      <c r="M103" s="25" t="s">
         <v>1442</v>
-      </c>
-      <c r="M103" s="25" t="s">
-        <v>1443</v>
       </c>
       <c r="N103" s="24" t="s">
         <v>191</v>
@@ -19352,7 +19643,7 @@
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="23" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B104" s="24" t="s">
         <v>758</v>
@@ -19365,7 +19656,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E104" s="26" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="F104" s="24" t="s">
         <v>922</v>
@@ -19374,22 +19665,22 @@
         <v>3</v>
       </c>
       <c r="H104" s="25" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="I104" s="25" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="J104" s="24" t="n">
         <v>30</v>
       </c>
       <c r="K104" s="25" t="s">
+        <v>1446</v>
+      </c>
+      <c r="L104" s="25" t="s">
         <v>1447</v>
       </c>
-      <c r="L104" s="25" t="s">
+      <c r="M104" s="25" t="s">
         <v>1448</v>
-      </c>
-      <c r="M104" s="25" t="s">
-        <v>1449</v>
       </c>
       <c r="N104" s="24" t="s">
         <v>191</v>
@@ -19400,7 +19691,7 @@
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="17" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B105" s="16" t="s">
         <v>775</v>
@@ -19413,7 +19704,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F105" s="16" t="s">
         <v>922</v>
@@ -19434,10 +19725,10 @@
         <v>1022</v>
       </c>
       <c r="L105" s="19" t="s">
+        <v>1451</v>
+      </c>
+      <c r="M105" s="19" t="s">
         <v>1452</v>
-      </c>
-      <c r="M105" s="19" t="s">
-        <v>1453</v>
       </c>
       <c r="N105" s="17" t="s">
         <v>97</v>
@@ -19448,7 +19739,7 @@
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="23" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B106" s="24" t="s">
         <v>783</v>
@@ -19461,7 +19752,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E106" s="26" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F106" s="24" t="s">
         <v>922</v>
@@ -19470,7 +19761,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="25" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="I106" s="25" t="s">
         <v>924</v>
@@ -19479,13 +19770,13 @@
         <v>90</v>
       </c>
       <c r="K106" s="25" t="s">
+        <v>1456</v>
+      </c>
+      <c r="L106" s="25" t="s">
         <v>1457</v>
       </c>
-      <c r="L106" s="25" t="s">
+      <c r="M106" s="25" t="s">
         <v>1458</v>
-      </c>
-      <c r="M106" s="25" t="s">
-        <v>1459</v>
       </c>
       <c r="N106" s="24" t="s">
         <v>191</v>
@@ -19496,7 +19787,7 @@
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="23" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B107" s="24" t="s">
         <v>789</v>
@@ -19509,7 +19800,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F107" s="24" t="s">
         <v>922</v>
@@ -19521,19 +19812,19 @@
         <v>1020</v>
       </c>
       <c r="I107" s="25" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="J107" s="24" t="n">
         <v>60</v>
       </c>
       <c r="K107" s="25" t="s">
+        <v>1462</v>
+      </c>
+      <c r="L107" s="25" t="s">
         <v>1463</v>
       </c>
-      <c r="L107" s="25" t="s">
+      <c r="M107" s="25" t="s">
         <v>1464</v>
-      </c>
-      <c r="M107" s="25" t="s">
-        <v>1465</v>
       </c>
       <c r="N107" s="24" t="s">
         <v>191</v>
@@ -19544,7 +19835,7 @@
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="23" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B108" s="24" t="s">
         <v>789</v>
@@ -19557,7 +19848,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F108" s="24" t="s">
         <v>922</v>
@@ -19575,13 +19866,13 @@
         <v>30</v>
       </c>
       <c r="K108" s="25" t="s">
+        <v>1467</v>
+      </c>
+      <c r="L108" s="25" t="s">
         <v>1468</v>
       </c>
-      <c r="L108" s="25" t="s">
+      <c r="M108" s="25" t="s">
         <v>1469</v>
-      </c>
-      <c r="M108" s="25" t="s">
-        <v>1470</v>
       </c>
       <c r="N108" s="24" t="s">
         <v>191</v>
@@ -19592,7 +19883,7 @@
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="23" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B109" s="24" t="s">
         <v>798</v>
@@ -19605,7 +19896,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F109" s="24" t="s">
         <v>922</v>
@@ -19614,22 +19905,22 @@
         <v>2.5</v>
       </c>
       <c r="H109" s="25" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I109" s="25" t="s">
         <v>1473</v>
-      </c>
-      <c r="I109" s="25" t="s">
-        <v>1474</v>
       </c>
       <c r="J109" s="24" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="25" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L109" s="25" t="s">
         <v>1475</v>
       </c>
-      <c r="L109" s="25" t="s">
+      <c r="M109" s="25" t="s">
         <v>1476</v>
-      </c>
-      <c r="M109" s="25" t="s">
-        <v>1477</v>
       </c>
       <c r="N109" s="24" t="s">
         <v>191</v>
@@ -19640,7 +19931,7 @@
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="23" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B110" s="24" t="s">
         <v>808</v>
@@ -19653,7 +19944,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E110" s="26" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F110" s="24" t="s">
         <v>922</v>
@@ -19671,13 +19962,13 @@
         <v>20</v>
       </c>
       <c r="K110" s="25" t="s">
+        <v>1479</v>
+      </c>
+      <c r="L110" s="25" t="s">
         <v>1480</v>
       </c>
-      <c r="L110" s="25" t="s">
+      <c r="M110" s="25" t="s">
         <v>1481</v>
-      </c>
-      <c r="M110" s="25" t="s">
-        <v>1482</v>
       </c>
       <c r="N110" s="24" t="s">
         <v>191</v>
@@ -19688,7 +19979,7 @@
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="23" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B111" s="24" t="s">
         <v>814</v>
@@ -19701,7 +19992,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F111" s="24" t="s">
         <v>922</v>
@@ -19719,13 +20010,13 @@
         <v>60</v>
       </c>
       <c r="K111" s="25" t="s">
+        <v>1484</v>
+      </c>
+      <c r="L111" s="25" t="s">
         <v>1485</v>
       </c>
-      <c r="L111" s="25" t="s">
+      <c r="M111" s="25" t="s">
         <v>1486</v>
-      </c>
-      <c r="M111" s="25" t="s">
-        <v>1487</v>
       </c>
       <c r="N111" s="24" t="s">
         <v>191</v>
@@ -19736,7 +20027,7 @@
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="23" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B112" s="24" t="s">
         <v>814</v>
@@ -19749,7 +20040,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="F112" s="24" t="s">
         <v>922</v>
@@ -19761,7 +20052,7 @@
         <v>1020</v>
       </c>
       <c r="I112" s="25" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="J112" s="24" t="n">
         <v>45</v>
@@ -19770,10 +20061,10 @@
         <v>1022</v>
       </c>
       <c r="L112" s="25" t="s">
+        <v>1490</v>
+      </c>
+      <c r="M112" s="25" t="s">
         <v>1491</v>
-      </c>
-      <c r="M112" s="25" t="s">
-        <v>1492</v>
       </c>
       <c r="N112" s="24" t="s">
         <v>191</v>
@@ -19784,7 +20075,7 @@
     </row>
     <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="23" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B113" s="24" t="s">
         <v>819</v>
@@ -19797,7 +20088,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E113" s="26" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="F113" s="24" t="s">
         <v>922</v>
@@ -19809,7 +20100,7 @@
         <v>1020</v>
       </c>
       <c r="I113" s="25" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="J113" s="24" t="n">
         <v>20</v>
@@ -19818,7 +20109,7 @@
         <v>1111</v>
       </c>
       <c r="L113" s="25" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="M113" s="25" t="s">
         <v>822</v>
@@ -19832,7 +20123,7 @@
     </row>
     <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="23" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B114" s="24" t="s">
         <v>838</v>
@@ -19845,7 +20136,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E114" s="26" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F114" s="24" t="s">
         <v>922</v>
@@ -19854,22 +20145,22 @@
         <v>6</v>
       </c>
       <c r="H114" s="25" t="s">
+        <v>1498</v>
+      </c>
+      <c r="I114" s="25" t="s">
         <v>1499</v>
-      </c>
-      <c r="I114" s="25" t="s">
-        <v>1500</v>
       </c>
       <c r="J114" s="24" t="n">
         <v>90</v>
       </c>
       <c r="K114" s="25" t="s">
+        <v>1500</v>
+      </c>
+      <c r="L114" s="25" t="s">
         <v>1501</v>
       </c>
-      <c r="L114" s="25" t="s">
+      <c r="M114" s="25" t="s">
         <v>1502</v>
-      </c>
-      <c r="M114" s="25" t="s">
-        <v>1503</v>
       </c>
       <c r="N114" s="24" t="s">
         <v>191</v>
@@ -19880,7 +20171,7 @@
     </row>
     <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="23" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B115" s="24" t="s">
         <v>830</v>
@@ -19893,7 +20184,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E115" s="26" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F115" s="24" t="s">
         <v>922</v>
@@ -19905,19 +20196,19 @@
         <v>1020</v>
       </c>
       <c r="I115" s="25" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="J115" s="24" t="n">
         <v>30</v>
       </c>
       <c r="K115" s="25" t="s">
+        <v>1506</v>
+      </c>
+      <c r="L115" s="25" t="s">
         <v>1507</v>
       </c>
-      <c r="L115" s="25" t="s">
+      <c r="M115" s="25" t="s">
         <v>1508</v>
-      </c>
-      <c r="M115" s="25" t="s">
-        <v>1509</v>
       </c>
       <c r="N115" s="24" t="s">
         <v>191</v>
@@ -19928,7 +20219,7 @@
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="13" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B116" s="27" t="s">
         <v>830</v>
@@ -19941,7 +20232,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F116" s="27" t="s">
         <v>201</v>
@@ -19959,13 +20250,13 @@
         <v>480</v>
       </c>
       <c r="K116" s="28" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L116" s="28" t="s">
         <v>1512</v>
       </c>
-      <c r="L116" s="28" t="s">
+      <c r="M116" s="28" t="s">
         <v>1513</v>
-      </c>
-      <c r="M116" s="28" t="s">
-        <v>1514</v>
       </c>
       <c r="N116" s="27" t="s">
         <v>191</v>
@@ -19976,7 +20267,7 @@
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="23" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B117" s="24" t="s">
         <v>850</v>
@@ -19989,7 +20280,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E117" s="26" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F117" s="24" t="s">
         <v>922</v>
@@ -20001,19 +20292,19 @@
         <v>1020</v>
       </c>
       <c r="I117" s="25" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="J117" s="24" t="n">
         <v>240</v>
       </c>
       <c r="K117" s="25" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L117" s="25" t="s">
         <v>1518</v>
       </c>
-      <c r="L117" s="25" t="s">
+      <c r="M117" s="25" t="s">
         <v>1519</v>
-      </c>
-      <c r="M117" s="25" t="s">
-        <v>1520</v>
       </c>
       <c r="N117" s="24" t="s">
         <v>191</v>
@@ -20024,7 +20315,7 @@
     </row>
     <row r="118" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="13" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B118" s="27" t="s">
         <v>855</v>
@@ -20037,7 +20328,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F118" s="27" t="s">
         <v>201</v>
@@ -20046,7 +20337,7 @@
         <v>48</v>
       </c>
       <c r="H118" s="28" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="I118" s="28" t="s">
         <v>924</v>
@@ -20055,13 +20346,13 @@
         <v>90</v>
       </c>
       <c r="K118" s="28" t="s">
+        <v>1523</v>
+      </c>
+      <c r="L118" s="28" t="s">
         <v>1524</v>
       </c>
-      <c r="L118" s="28" t="s">
+      <c r="M118" s="28" t="s">
         <v>1525</v>
-      </c>
-      <c r="M118" s="28" t="s">
-        <v>1526</v>
       </c>
       <c r="N118" s="27" t="s">
         <v>224</v>
@@ -20072,7 +20363,7 @@
     </row>
     <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="23" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B119" s="24" t="s">
         <v>862</v>
@@ -20085,7 +20376,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E119" s="26" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F119" s="24" t="s">
         <v>922</v>
@@ -20097,19 +20388,19 @@
         <v>1020</v>
       </c>
       <c r="I119" s="25" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J119" s="24" t="n">
         <v>20</v>
       </c>
       <c r="K119" s="25" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="L119" s="25" t="s">
+        <v>1529</v>
+      </c>
+      <c r="M119" s="25" t="s">
         <v>1530</v>
-      </c>
-      <c r="M119" s="25" t="s">
-        <v>1531</v>
       </c>
       <c r="N119" s="24" t="s">
         <v>191</v>
@@ -20120,7 +20411,7 @@
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="23" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B120" s="24" t="s">
         <v>866</v>
@@ -20133,7 +20424,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E120" s="26" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="F120" s="24" t="s">
         <v>922</v>
@@ -20145,19 +20436,19 @@
         <v>1020</v>
       </c>
       <c r="I120" s="25" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J120" s="24" t="n">
         <v>15</v>
       </c>
       <c r="K120" s="25" t="s">
+        <v>1533</v>
+      </c>
+      <c r="L120" s="25" t="s">
         <v>1534</v>
       </c>
-      <c r="L120" s="25" t="s">
+      <c r="M120" s="25" t="s">
         <v>1535</v>
-      </c>
-      <c r="M120" s="25" t="s">
-        <v>1536</v>
       </c>
       <c r="N120" s="24" t="s">
         <v>191</v>
@@ -20168,7 +20459,7 @@
     </row>
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="23" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B121" s="24" t="s">
         <v>610</v>
@@ -20181,7 +20472,7 @@
         <v>Energie</v>
       </c>
       <c r="E121" s="26" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="F121" s="24" t="s">
         <v>922</v>
@@ -20193,19 +20484,19 @@
         <v>1020</v>
       </c>
       <c r="I121" s="25" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="J121" s="24" t="n">
         <v>30</v>
       </c>
       <c r="K121" s="25" t="s">
+        <v>1539</v>
+      </c>
+      <c r="L121" s="25" t="s">
         <v>1540</v>
       </c>
-      <c r="L121" s="25" t="s">
+      <c r="M121" s="25" t="s">
         <v>1541</v>
-      </c>
-      <c r="M121" s="25" t="s">
-        <v>1542</v>
       </c>
       <c r="N121" s="24" t="s">
         <v>191</v>
@@ -20216,7 +20507,7 @@
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="23" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B122" s="24" t="s">
         <v>294</v>
@@ -20241,7 +20532,7 @@
         <v>966</v>
       </c>
       <c r="I122" s="25" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="J122" s="24" t="n">
         <v>10</v>
@@ -20250,10 +20541,10 @@
         <v>1028</v>
       </c>
       <c r="L122" s="25" t="s">
+        <v>1543</v>
+      </c>
+      <c r="M122" s="25" t="s">
         <v>1544</v>
-      </c>
-      <c r="M122" s="25" t="s">
-        <v>1545</v>
       </c>
       <c r="N122" s="24" t="s">
         <v>191</v>
@@ -20264,7 +20555,7 @@
     </row>
     <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="17" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B123" s="16" t="s">
         <v>294</v>
@@ -20277,7 +20568,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="F123" s="16" t="s">
         <v>201</v>
@@ -20289,7 +20580,7 @@
         <v>169</v>
       </c>
       <c r="I123" s="19" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="J123" s="16" t="n">
         <v>90</v>
@@ -20298,10 +20589,10 @@
         <v>297</v>
       </c>
       <c r="L123" s="19" t="s">
+        <v>1548</v>
+      </c>
+      <c r="M123" s="19" t="s">
         <v>1549</v>
-      </c>
-      <c r="M123" s="19" t="s">
-        <v>1550</v>
       </c>
       <c r="N123" s="17" t="s">
         <v>97</v>
@@ -20312,7 +20603,7 @@
     </row>
     <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="23" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B124" s="24" t="s">
         <v>294</v>
@@ -20325,7 +20616,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="F124" s="24" t="s">
         <v>922</v>
@@ -20337,19 +20628,19 @@
         <v>1020</v>
       </c>
       <c r="I124" s="25" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="J124" s="24" t="n">
         <v>15</v>
       </c>
       <c r="K124" s="25" t="s">
+        <v>1552</v>
+      </c>
+      <c r="L124" s="25" t="s">
         <v>1553</v>
       </c>
-      <c r="L124" s="25" t="s">
+      <c r="M124" s="25" t="s">
         <v>1554</v>
-      </c>
-      <c r="M124" s="25" t="s">
-        <v>1555</v>
       </c>
       <c r="N124" s="24" t="s">
         <v>191</v>
@@ -20360,7 +20651,7 @@
     </row>
     <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="23" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B125" s="24" t="s">
         <v>299</v>
@@ -20373,7 +20664,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E125" s="26" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="F125" s="24" t="s">
         <v>922</v>
@@ -20382,22 +20673,22 @@
         <v>1</v>
       </c>
       <c r="H125" s="25" t="s">
+        <v>1557</v>
+      </c>
+      <c r="I125" s="25" t="s">
         <v>1558</v>
-      </c>
-      <c r="I125" s="25" t="s">
-        <v>1559</v>
       </c>
       <c r="J125" s="24" t="n">
         <v>10</v>
       </c>
       <c r="K125" s="25" t="s">
+        <v>1559</v>
+      </c>
+      <c r="L125" s="25" t="s">
         <v>1560</v>
       </c>
-      <c r="L125" s="25" t="s">
+      <c r="M125" s="25" t="s">
         <v>1561</v>
-      </c>
-      <c r="M125" s="25" t="s">
-        <v>1562</v>
       </c>
       <c r="N125" s="24" t="s">
         <v>191</v>
@@ -20408,7 +20699,7 @@
     </row>
     <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="17" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B126" s="16" t="s">
         <v>306</v>
@@ -20421,7 +20712,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E126" s="18" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="F126" s="16" t="s">
         <v>201</v>
@@ -20439,13 +20730,13 @@
         <v>60</v>
       </c>
       <c r="K126" s="19" t="s">
+        <v>1564</v>
+      </c>
+      <c r="L126" s="19" t="s">
         <v>1565</v>
       </c>
-      <c r="L126" s="19" t="s">
+      <c r="M126" s="19" t="s">
         <v>1566</v>
-      </c>
-      <c r="M126" s="19" t="s">
-        <v>1567</v>
       </c>
       <c r="N126" s="17" t="s">
         <v>97</v>
@@ -20456,7 +20747,7 @@
     </row>
     <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="17" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B127" s="16" t="s">
         <v>182</v>
@@ -20469,7 +20760,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E127" s="18" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="F127" s="16" t="s">
         <v>201</v>
@@ -20487,13 +20778,13 @@
         <v>120</v>
       </c>
       <c r="K127" s="19" t="s">
+        <v>1569</v>
+      </c>
+      <c r="L127" s="19" t="s">
         <v>1570</v>
       </c>
-      <c r="L127" s="19" t="s">
+      <c r="M127" s="19" t="s">
         <v>1571</v>
-      </c>
-      <c r="M127" s="19" t="s">
-        <v>1572</v>
       </c>
       <c r="N127" s="17" t="s">
         <v>97</v>
@@ -20504,7 +20795,7 @@
     </row>
     <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="23" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B128" s="24" t="s">
         <v>206</v>
@@ -20517,7 +20808,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E128" s="26" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="F128" s="24" t="s">
         <v>922</v>
@@ -20535,13 +20826,13 @@
         <v>20</v>
       </c>
       <c r="K128" s="25" t="s">
+        <v>1574</v>
+      </c>
+      <c r="L128" s="25" t="s">
         <v>1575</v>
       </c>
-      <c r="L128" s="25" t="s">
+      <c r="M128" s="25" t="s">
         <v>1576</v>
-      </c>
-      <c r="M128" s="25" t="s">
-        <v>1577</v>
       </c>
       <c r="N128" s="24" t="s">
         <v>191</v>
@@ -20552,7 +20843,7 @@
     </row>
     <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="17" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B129" s="16" t="s">
         <v>232</v>
@@ -20565,7 +20856,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E129" s="18" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F129" s="16" t="s">
         <v>201</v>
@@ -20574,10 +20865,10 @@
         <v>60</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="I129" s="19" t="s">
-        <v>1383</v>
+        <v>1362</v>
       </c>
       <c r="J129" s="16" t="n">
         <v>60</v>
@@ -20586,10 +20877,10 @@
         <v>237</v>
       </c>
       <c r="L129" s="19" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M129" s="19" t="s">
         <v>1581</v>
-      </c>
-      <c r="M129" s="19" t="s">
-        <v>1582</v>
       </c>
       <c r="N129" s="17" t="s">
         <v>97</v>
@@ -20600,7 +20891,7 @@
     </row>
     <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="23" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B130" s="24" t="s">
         <v>244</v>
@@ -20613,7 +20904,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E130" s="26" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F130" s="24" t="s">
         <v>922</v>
@@ -20631,13 +20922,13 @@
         <v>5</v>
       </c>
       <c r="K130" s="25" t="s">
+        <v>1584</v>
+      </c>
+      <c r="L130" s="25" t="s">
         <v>1585</v>
       </c>
-      <c r="L130" s="25" t="s">
+      <c r="M130" s="25" t="s">
         <v>1586</v>
-      </c>
-      <c r="M130" s="25" t="s">
-        <v>1587</v>
       </c>
       <c r="N130" s="24" t="s">
         <v>191</v>
@@ -20648,7 +20939,7 @@
     </row>
     <row r="131" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="17" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B131" s="16" t="s">
         <v>264</v>
@@ -20661,7 +20952,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E131" s="18" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="F131" s="16" t="s">
         <v>201</v>
@@ -20679,13 +20970,13 @@
         <v>60</v>
       </c>
       <c r="K131" s="19" t="s">
+        <v>1589</v>
+      </c>
+      <c r="L131" s="19" t="s">
         <v>1590</v>
       </c>
-      <c r="L131" s="19" t="s">
+      <c r="M131" s="19" t="s">
         <v>1591</v>
-      </c>
-      <c r="M131" s="19" t="s">
-        <v>1592</v>
       </c>
       <c r="N131" s="17" t="s">
         <v>97</v>
@@ -20696,7 +20987,7 @@
     </row>
     <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="13" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B132" s="27" t="s">
         <v>279</v>
@@ -20709,7 +21000,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F132" s="27" t="s">
         <v>201</v>
@@ -20727,13 +21018,13 @@
         <v>45</v>
       </c>
       <c r="K132" s="28" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L132" s="28" t="s">
         <v>1595</v>
       </c>
-      <c r="L132" s="28" t="s">
+      <c r="M132" s="28" t="s">
         <v>1596</v>
-      </c>
-      <c r="M132" s="28" t="s">
-        <v>1597</v>
       </c>
       <c r="N132" s="27" t="s">
         <v>191</v>
@@ -20744,7 +21035,7 @@
     </row>
     <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="13" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B133" s="27" t="s">
         <v>346</v>
@@ -20757,7 +21048,7 @@
         <v>Chauffage &amp; climatisation</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F133" s="27" t="s">
         <v>201</v>
@@ -20775,13 +21066,13 @@
         <v>45</v>
       </c>
       <c r="K133" s="28" t="s">
+        <v>1599</v>
+      </c>
+      <c r="L133" s="28" t="s">
         <v>1600</v>
       </c>
-      <c r="L133" s="28" t="s">
+      <c r="M133" s="28" t="s">
         <v>1601</v>
-      </c>
-      <c r="M133" s="28" t="s">
-        <v>1602</v>
       </c>
       <c r="N133" s="27" t="s">
         <v>191</v>
@@ -20792,7 +21083,7 @@
     </row>
     <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="23" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>375</v>
@@ -20805,7 +21096,7 @@
         <v>Cuisine</v>
       </c>
       <c r="E134" s="26" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F134" s="24" t="s">
         <v>922</v>
@@ -20826,10 +21117,10 @@
         <v>1262</v>
       </c>
       <c r="L134" s="25" t="s">
+        <v>1604</v>
+      </c>
+      <c r="M134" s="25" t="s">
         <v>1605</v>
-      </c>
-      <c r="M134" s="25" t="s">
-        <v>1606</v>
       </c>
       <c r="N134" s="24" t="s">
         <v>191</v>
@@ -20840,7 +21131,7 @@
     </row>
     <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="23" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B135" s="24" t="s">
         <v>404</v>
@@ -20853,7 +21144,7 @@
         <v>Buanderie</v>
       </c>
       <c r="E135" s="26" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F135" s="24" t="s">
         <v>922</v>
@@ -20862,7 +21153,7 @@
         <v>3</v>
       </c>
       <c r="H135" s="25" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="I135" s="25" t="s">
         <v>924</v>
@@ -20871,13 +21162,13 @@
         <v>30</v>
       </c>
       <c r="K135" s="25" t="s">
+        <v>1609</v>
+      </c>
+      <c r="L135" s="25" t="s">
         <v>1610</v>
       </c>
-      <c r="L135" s="25" t="s">
+      <c r="M135" s="25" t="s">
         <v>1611</v>
-      </c>
-      <c r="M135" s="25" t="s">
-        <v>1612</v>
       </c>
       <c r="N135" s="24" t="s">
         <v>191</v>
@@ -20888,7 +21179,7 @@
     </row>
     <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="23" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>416</v>
@@ -20901,7 +21192,7 @@
         <v>Cuisine</v>
       </c>
       <c r="E136" s="26" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F136" s="24" t="s">
         <v>922</v>
@@ -20919,13 +21210,13 @@
         <v>15</v>
       </c>
       <c r="K136" s="25" t="s">
+        <v>1614</v>
+      </c>
+      <c r="L136" s="25" t="s">
         <v>1615</v>
       </c>
-      <c r="L136" s="25" t="s">
+      <c r="M136" s="25" t="s">
         <v>1616</v>
-      </c>
-      <c r="M136" s="25" t="s">
-        <v>1617</v>
       </c>
       <c r="N136" s="24" t="s">
         <v>191</v>
@@ -20936,7 +21227,7 @@
     </row>
     <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="23" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B137" s="24" t="s">
         <v>441</v>
@@ -20949,7 +21240,7 @@
         <v>Cuisine</v>
       </c>
       <c r="E137" s="26" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="F137" s="24" t="s">
         <v>922</v>
@@ -20970,10 +21261,10 @@
         <v>1022</v>
       </c>
       <c r="L137" s="25" t="s">
+        <v>1619</v>
+      </c>
+      <c r="M137" s="25" t="s">
         <v>1620</v>
-      </c>
-      <c r="M137" s="25" t="s">
-        <v>1621</v>
       </c>
       <c r="N137" s="24" t="s">
         <v>191</v>
@@ -20984,7 +21275,7 @@
     </row>
     <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="23" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B138" s="24" t="s">
         <v>468</v>
@@ -20997,7 +21288,7 @@
         <v>Petit electromenager</v>
       </c>
       <c r="E138" s="26" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F138" s="24" t="s">
         <v>922</v>
@@ -21006,7 +21297,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="25" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="I138" s="25" t="s">
         <v>924</v>
@@ -21015,13 +21306,13 @@
         <v>10</v>
       </c>
       <c r="K138" s="25" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L138" s="25" t="s">
         <v>1625</v>
       </c>
-      <c r="L138" s="25" t="s">
+      <c r="M138" s="25" t="s">
         <v>1626</v>
-      </c>
-      <c r="M138" s="25" t="s">
-        <v>1627</v>
       </c>
       <c r="N138" s="24" t="s">
         <v>191</v>
@@ -21032,7 +21323,7 @@
     </row>
     <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="23" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B139" s="24" t="s">
         <v>476</v>
@@ -21045,7 +21336,7 @@
         <v>Petit electromenager</v>
       </c>
       <c r="E139" s="26" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F139" s="24" t="s">
         <v>922</v>
@@ -21054,7 +21345,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="25" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="I139" s="25" t="s">
         <v>942</v>
@@ -21063,13 +21354,13 @@
         <v>10</v>
       </c>
       <c r="K139" s="25" t="s">
+        <v>1629</v>
+      </c>
+      <c r="L139" s="25" t="s">
         <v>1630</v>
       </c>
-      <c r="L139" s="25" t="s">
+      <c r="M139" s="25" t="s">
         <v>1631</v>
-      </c>
-      <c r="M139" s="25" t="s">
-        <v>1632</v>
       </c>
       <c r="N139" s="24" t="s">
         <v>191</v>
@@ -21080,7 +21371,7 @@
     </row>
     <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="23" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B140" s="24" t="s">
         <v>481</v>
@@ -21093,7 +21384,7 @@
         <v>Buanderie</v>
       </c>
       <c r="E140" s="26" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="F140" s="24" t="s">
         <v>922</v>
@@ -21111,13 +21402,13 @@
         <v>20</v>
       </c>
       <c r="K140" s="25" t="s">
+        <v>1634</v>
+      </c>
+      <c r="L140" s="25" t="s">
         <v>1635</v>
       </c>
-      <c r="L140" s="25" t="s">
+      <c r="M140" s="25" t="s">
         <v>1636</v>
-      </c>
-      <c r="M140" s="25" t="s">
-        <v>1637</v>
       </c>
       <c r="N140" s="24" t="s">
         <v>191</v>
@@ -21128,7 +21419,7 @@
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="23" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B141" s="24" t="s">
         <v>494</v>
@@ -21141,7 +21432,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E141" s="26" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="F141" s="24" t="s">
         <v>922</v>
@@ -21159,13 +21450,13 @@
         <v>5</v>
       </c>
       <c r="K141" s="25" t="s">
+        <v>1639</v>
+      </c>
+      <c r="L141" s="25" t="s">
         <v>1640</v>
       </c>
-      <c r="L141" s="25" t="s">
+      <c r="M141" s="25" t="s">
         <v>1641</v>
-      </c>
-      <c r="M141" s="25" t="s">
-        <v>1642</v>
       </c>
       <c r="N141" s="24" t="s">
         <v>191</v>
@@ -21176,7 +21467,7 @@
     </row>
     <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="17" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B142" s="16" t="s">
         <v>517</v>
@@ -21189,7 +21480,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E142" s="18" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="F142" s="16" t="s">
         <v>922</v>
@@ -21198,7 +21489,7 @@
         <v>120</v>
       </c>
       <c r="H142" s="19" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="I142" s="19" t="s">
         <v>1081</v>
@@ -21207,13 +21498,13 @@
         <v>60</v>
       </c>
       <c r="K142" s="19" t="s">
+        <v>1645</v>
+      </c>
+      <c r="L142" s="19" t="s">
         <v>1646</v>
       </c>
-      <c r="L142" s="19" t="s">
+      <c r="M142" s="19" t="s">
         <v>1647</v>
-      </c>
-      <c r="M142" s="19" t="s">
-        <v>1648</v>
       </c>
       <c r="N142" s="17" t="s">
         <v>97</v>
@@ -21224,7 +21515,7 @@
     </row>
     <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="23" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B143" s="24" t="s">
         <v>535</v>
@@ -21237,7 +21528,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E143" s="26" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="F143" s="24" t="s">
         <v>922</v>
@@ -21258,10 +21549,10 @@
         <v>931</v>
       </c>
       <c r="L143" s="25" t="s">
+        <v>1650</v>
+      </c>
+      <c r="M143" s="25" t="s">
         <v>1651</v>
-      </c>
-      <c r="M143" s="25" t="s">
-        <v>1652</v>
       </c>
       <c r="N143" s="24" t="s">
         <v>191</v>
@@ -21272,7 +21563,7 @@
     </row>
     <row r="144" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="13" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B144" s="27" t="s">
         <v>541</v>
@@ -21285,7 +21576,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F144" s="27" t="s">
         <v>201</v>
@@ -21297,7 +21588,7 @@
         <v>169</v>
       </c>
       <c r="I144" s="28" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="J144" s="27" t="n">
         <v>30</v>
@@ -21306,10 +21597,10 @@
         <v>111</v>
       </c>
       <c r="L144" s="28" t="s">
+        <v>1655</v>
+      </c>
+      <c r="M144" s="28" t="s">
         <v>1656</v>
-      </c>
-      <c r="M144" s="28" t="s">
-        <v>1657</v>
       </c>
       <c r="N144" s="27" t="s">
         <v>191</v>
@@ -21320,7 +21611,7 @@
     </row>
     <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="13" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B145" s="27" t="s">
         <v>577</v>
@@ -21333,7 +21624,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="F145" s="27" t="s">
         <v>201</v>
@@ -21342,7 +21633,7 @@
         <v>30</v>
       </c>
       <c r="H145" s="28" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="I145" s="28" t="s">
         <v>924</v>
@@ -21351,13 +21642,13 @@
         <v>90</v>
       </c>
       <c r="K145" s="28" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L145" s="28" t="s">
         <v>1661</v>
       </c>
-      <c r="L145" s="28" t="s">
+      <c r="M145" s="28" t="s">
         <v>1662</v>
-      </c>
-      <c r="M145" s="28" t="s">
-        <v>1663</v>
       </c>
       <c r="N145" s="27" t="s">
         <v>191</v>
@@ -21368,7 +21659,7 @@
     </row>
     <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="13" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="B146" s="27" t="s">
         <v>596</v>
@@ -21381,7 +21672,7 @@
         <v>Energie</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="F146" s="27" t="s">
         <v>201</v>
@@ -21402,10 +21693,10 @@
         <v>111</v>
       </c>
       <c r="L146" s="28" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M146" s="28" t="s">
         <v>1666</v>
-      </c>
-      <c r="M146" s="28" t="s">
-        <v>1667</v>
       </c>
       <c r="N146" s="27" t="s">
         <v>191</v>
@@ -21416,7 +21707,7 @@
     </row>
     <row r="147" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="17" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B147" s="16" t="s">
         <v>620</v>
@@ -21429,7 +21720,7 @@
         <v>Energie</v>
       </c>
       <c r="E147" s="18" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="F147" s="16" t="s">
         <v>201</v>
@@ -21438,10 +21729,10 @@
         <v>36</v>
       </c>
       <c r="H147" s="19" t="s">
+        <v>1669</v>
+      </c>
+      <c r="I147" s="19" t="s">
         <v>1670</v>
-      </c>
-      <c r="I147" s="19" t="s">
-        <v>1671</v>
       </c>
       <c r="J147" s="16" t="n">
         <v>90</v>
@@ -21450,10 +21741,10 @@
         <v>625</v>
       </c>
       <c r="L147" s="19" t="s">
+        <v>1671</v>
+      </c>
+      <c r="M147" s="19" t="s">
         <v>1672</v>
-      </c>
-      <c r="M147" s="19" t="s">
-        <v>1673</v>
       </c>
       <c r="N147" s="17" t="s">
         <v>97</v>
@@ -21464,7 +21755,7 @@
     </row>
     <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="13" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="B148" s="27" t="s">
         <v>655</v>
@@ -21477,7 +21768,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="F148" s="27" t="s">
         <v>201</v>
@@ -21495,13 +21786,13 @@
         <v>15</v>
       </c>
       <c r="K148" s="28" t="s">
+        <v>1675</v>
+      </c>
+      <c r="L148" s="28" t="s">
         <v>1676</v>
       </c>
-      <c r="L148" s="28" t="s">
+      <c r="M148" s="28" t="s">
         <v>1677</v>
-      </c>
-      <c r="M148" s="28" t="s">
-        <v>1678</v>
       </c>
       <c r="N148" s="27" t="s">
         <v>224</v>
@@ -21512,7 +21803,7 @@
     </row>
     <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="23" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B149" s="24" t="s">
         <v>672</v>
@@ -21525,7 +21816,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E149" s="26" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="F149" s="24" t="s">
         <v>922</v>
@@ -21543,13 +21834,13 @@
         <v>20</v>
       </c>
       <c r="K149" s="25" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="L149" s="25" t="s">
+        <v>1680</v>
+      </c>
+      <c r="M149" s="25" t="s">
         <v>1681</v>
-      </c>
-      <c r="M149" s="25" t="s">
-        <v>1682</v>
       </c>
       <c r="N149" s="24" t="s">
         <v>191</v>
@@ -21560,7 +21851,7 @@
     </row>
     <row r="150" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="23" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B150" s="24" t="s">
         <v>678</v>
@@ -21573,7 +21864,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E150" s="26" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="F150" s="24" t="s">
         <v>922</v>
@@ -21591,13 +21882,13 @@
         <v>15</v>
       </c>
       <c r="K150" s="25" t="s">
+        <v>1684</v>
+      </c>
+      <c r="L150" s="25" t="s">
         <v>1685</v>
       </c>
-      <c r="L150" s="25" t="s">
+      <c r="M150" s="25" t="s">
         <v>1686</v>
-      </c>
-      <c r="M150" s="25" t="s">
-        <v>1687</v>
       </c>
       <c r="N150" s="24" t="s">
         <v>191</v>
@@ -21608,7 +21899,7 @@
     </row>
     <row r="151" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="23" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B151" s="24" t="s">
         <v>727</v>
@@ -21621,7 +21912,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E151" s="26" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="F151" s="24" t="s">
         <v>922</v>
@@ -21633,19 +21924,19 @@
         <v>1020</v>
       </c>
       <c r="I151" s="25" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="J151" s="24" t="n">
         <v>45</v>
       </c>
       <c r="K151" s="25" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L151" s="25" t="s">
         <v>1690</v>
       </c>
-      <c r="L151" s="25" t="s">
+      <c r="M151" s="25" t="s">
         <v>1691</v>
-      </c>
-      <c r="M151" s="25" t="s">
-        <v>1692</v>
       </c>
       <c r="N151" s="24" t="s">
         <v>191</v>
@@ -21656,7 +21947,7 @@
     </row>
     <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="17" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B152" s="16" t="s">
         <v>765</v>
@@ -21669,7 +21960,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E152" s="18" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="F152" s="16" t="s">
         <v>201</v>
@@ -21681,7 +21972,7 @@
         <v>169</v>
       </c>
       <c r="I152" s="19" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="J152" s="16" t="n">
         <v>60</v>
@@ -21690,10 +21981,10 @@
         <v>111</v>
       </c>
       <c r="L152" s="19" t="s">
+        <v>1695</v>
+      </c>
+      <c r="M152" s="19" t="s">
         <v>1696</v>
-      </c>
-      <c r="M152" s="19" t="s">
-        <v>1697</v>
       </c>
       <c r="N152" s="17" t="s">
         <v>97</v>
@@ -21704,7 +21995,7 @@
     </row>
     <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="23" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B153" s="24" t="s">
         <v>769</v>
@@ -21717,7 +22008,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E153" s="26" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F153" s="24" t="s">
         <v>922</v>
@@ -21726,22 +22017,22 @@
         <v>1</v>
       </c>
       <c r="H153" s="25" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="I153" s="25" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="J153" s="24" t="n">
         <v>15</v>
       </c>
       <c r="K153" s="25" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L153" s="25" t="s">
         <v>1701</v>
       </c>
-      <c r="L153" s="25" t="s">
+      <c r="M153" s="25" t="s">
         <v>1702</v>
-      </c>
-      <c r="M153" s="25" t="s">
-        <v>1703</v>
       </c>
       <c r="N153" s="24" t="s">
         <v>191</v>
@@ -21752,7 +22043,7 @@
     </row>
     <row r="154" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="23" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B154" s="24" t="s">
         <v>803</v>
@@ -21765,7 +22056,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E154" s="26" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="F154" s="24" t="s">
         <v>922</v>
@@ -21777,19 +22068,19 @@
         <v>1020</v>
       </c>
       <c r="I154" s="25" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="J154" s="24" t="n">
         <v>45</v>
       </c>
       <c r="K154" s="25" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L154" s="25" t="s">
         <v>1707</v>
       </c>
-      <c r="L154" s="25" t="s">
+      <c r="M154" s="25" t="s">
         <v>1708</v>
-      </c>
-      <c r="M154" s="25" t="s">
-        <v>1709</v>
       </c>
       <c r="N154" s="24" t="s">
         <v>191</v>
@@ -21800,7 +22091,7 @@
     </row>
     <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="23" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B155" s="24" t="s">
         <v>825</v>
@@ -21813,7 +22104,7 @@
         <v>Jardin &amp; piscine</v>
       </c>
       <c r="E155" s="26" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="F155" s="24" t="s">
         <v>922</v>
@@ -21822,22 +22113,22 @@
         <v>30</v>
       </c>
       <c r="H155" s="25" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="I155" s="25" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="J155" s="24" t="n">
         <v>240</v>
       </c>
       <c r="K155" s="25" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L155" s="25" t="s">
         <v>1713</v>
       </c>
-      <c r="L155" s="25" t="s">
+      <c r="M155" s="25" t="s">
         <v>1714</v>
-      </c>
-      <c r="M155" s="25" t="s">
-        <v>1715</v>
       </c>
       <c r="N155" s="24" t="s">
         <v>191</v>
@@ -21848,7 +22139,7 @@
     </row>
     <row r="156" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="23" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B156" s="24" t="s">
         <v>843</v>
@@ -21861,7 +22152,7 @@
         <v>Maison &amp; securite</v>
       </c>
       <c r="E156" s="26" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="F156" s="24" t="s">
         <v>922</v>
@@ -21873,19 +22164,19 @@
         <v>1020</v>
       </c>
       <c r="I156" s="25" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="J156" s="24" t="n">
         <v>30</v>
       </c>
       <c r="K156" s="25" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="L156" s="25" t="s">
+        <v>1718</v>
+      </c>
+      <c r="M156" s="25" t="s">
         <v>1719</v>
-      </c>
-      <c r="M156" s="25" t="s">
-        <v>1720</v>
       </c>
       <c r="N156" s="24" t="s">
         <v>224</v>
@@ -21896,7 +22187,7 @@
     </row>
     <row r="157" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="17" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B157" s="16" t="s">
         <v>870</v>
@@ -21909,7 +22200,7 @@
         <v>Vehicules</v>
       </c>
       <c r="E157" s="18" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="F157" s="16" t="s">
         <v>201</v>
@@ -21918,19 +22209,19 @@
         <v>24</v>
       </c>
       <c r="H157" s="19" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="I157" s="19" t="s">
-        <v>1383</v>
+        <v>1362</v>
       </c>
       <c r="J157" s="16" t="n">
         <v>60</v>
       </c>
       <c r="K157" s="19" t="s">
+        <v>1723</v>
+      </c>
+      <c r="L157" s="19" t="s">
         <v>1724</v>
-      </c>
-      <c r="L157" s="19" t="s">
-        <v>1725</v>
       </c>
       <c r="M157" s="19" t="s">
         <v>877</v>
@@ -21944,7 +22235,7 @@
     </row>
     <row r="158" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="17" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B158" s="16" t="s">
         <v>881</v>
@@ -21957,7 +22248,7 @@
         <v>Vehicules</v>
       </c>
       <c r="E158" s="18" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="F158" s="16" t="s">
         <v>201</v>
@@ -21966,19 +22257,19 @@
         <v>36</v>
       </c>
       <c r="H158" s="19" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="I158" s="19" t="s">
-        <v>1383</v>
+        <v>1362</v>
       </c>
       <c r="J158" s="16" t="n">
         <v>45</v>
       </c>
       <c r="K158" s="19" t="s">
+        <v>1728</v>
+      </c>
+      <c r="L158" s="19" t="s">
         <v>1729</v>
-      </c>
-      <c r="L158" s="19" t="s">
-        <v>1730</v>
       </c>
       <c r="M158" s="19" t="s">
         <v>887</v>
@@ -21992,7 +22283,7 @@
     </row>
     <row r="159" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="13" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B159" s="27" t="s">
         <v>889</v>
@@ -22005,7 +22296,7 @@
         <v>Vehicules</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="F159" s="27" t="s">
         <v>201</v>
@@ -22023,13 +22314,13 @@
         <v>60</v>
       </c>
       <c r="K159" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="L159" s="28" t="s">
         <v>1733</v>
       </c>
-      <c r="L159" s="28" t="s">
+      <c r="M159" s="28" t="s">
         <v>1734</v>
-      </c>
-      <c r="M159" s="28" t="s">
-        <v>1735</v>
       </c>
       <c r="N159" s="27" t="s">
         <v>191</v>
@@ -22056,7 +22347,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:L81"/>
+  <dimension ref="A2:M87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -22069,17 +22360,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22087,36 +22378,39 @@
         <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>1738</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>1739</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>1740</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>1741</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>1742</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>1743</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>1744</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>1745</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>1746</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="L5" s="9" t="s">
         <v>1747</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>1748</v>
       </c>
     </row>
@@ -22157,6 +22451,9 @@
       <c r="L6" s="21" t="s">
         <v>1755</v>
       </c>
+      <c r="M6" s="21" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
@@ -22195,6 +22492,9 @@
       <c r="L7" s="21" t="s">
         <v>1758</v>
       </c>
+      <c r="M7" s="21" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
@@ -22233,6 +22533,9 @@
       <c r="L8" s="21" t="s">
         <v>1761</v>
       </c>
+      <c r="M8" s="21" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
@@ -22271,6 +22574,9 @@
       <c r="L9" s="21" t="s">
         <v>1764</v>
       </c>
+      <c r="M9" s="21" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
@@ -22309,6 +22615,9 @@
       <c r="L10" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M10" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
@@ -22347,6 +22656,9 @@
       <c r="L11" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M11" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
@@ -22385,6 +22697,9 @@
       <c r="L12" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M12" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
@@ -22423,6 +22738,9 @@
       <c r="L13" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M13" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
@@ -22461,6 +22779,9 @@
       <c r="L14" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M14" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
@@ -22499,6 +22820,9 @@
       <c r="L15" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M15" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
@@ -22537,6 +22861,9 @@
       <c r="L16" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M16" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
@@ -22575,6 +22902,9 @@
       <c r="L17" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M17" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
@@ -22613,6 +22943,9 @@
       <c r="L18" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M18" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
@@ -22651,6 +22984,9 @@
       <c r="L19" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M19" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
@@ -22689,6 +23025,9 @@
       <c r="L20" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M20" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
@@ -22727,6 +23066,9 @@
       <c r="L21" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M21" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
@@ -22765,6 +23107,9 @@
       <c r="L22" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M22" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
@@ -22803,6 +23148,9 @@
       <c r="L23" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M23" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
@@ -22841,6 +23189,9 @@
       <c r="L24" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M24" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
@@ -22879,6 +23230,9 @@
       <c r="L25" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M25" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
@@ -22917,6 +23271,9 @@
       <c r="L26" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M26" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
@@ -22955,6 +23312,9 @@
       <c r="L27" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M27" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
@@ -22993,6 +23353,9 @@
       <c r="L28" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M28" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
@@ -23031,6 +23394,9 @@
       <c r="L29" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M29" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
@@ -23069,6 +23435,9 @@
       <c r="L30" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M30" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
@@ -23107,6 +23476,9 @@
       <c r="L31" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M31" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
@@ -23145,6 +23517,9 @@
       <c r="L32" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M32" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
@@ -23183,6 +23558,9 @@
       <c r="L33" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M33" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
@@ -23221,6 +23599,9 @@
       <c r="L34" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M34" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
@@ -23259,6 +23640,9 @@
       <c r="L35" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M35" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
@@ -23283,7 +23667,7 @@
         <v>1814</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>1815</v>
+        <v>153</v>
       </c>
       <c r="I36" s="19" t="s">
         <v>153</v>
@@ -23295,6 +23679,9 @@
         <v>153</v>
       </c>
       <c r="L36" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M36" s="19" t="s">
         <v>153</v>
       </c>
     </row>
@@ -23335,6 +23722,9 @@
       <c r="L37" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M37" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
@@ -23362,7 +23752,7 @@
         <v>153</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="J38" s="19" t="s">
         <v>153</v>
@@ -23371,12 +23761,15 @@
         <v>153</v>
       </c>
       <c r="L38" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M38" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>1766</v>
@@ -23385,7 +23778,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E39" s="16" t="s">
         <v>1752</v>
@@ -23411,10 +23804,13 @@
       <c r="L39" s="19" t="s">
         <v>153</v>
       </c>
+      <c r="M39" s="19" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>1766</v>
@@ -23423,19 +23819,19 @@
         <v>7</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>1752</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="G40" s="19" t="s">
         <v>548</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>1820</v>
+        <v>153</v>
       </c>
       <c r="I40" s="19" t="s">
         <v>153</v>
@@ -23447,12 +23843,15 @@
         <v>153</v>
       </c>
       <c r="L40" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M40" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>1766</v>
@@ -23461,19 +23860,19 @@
         <v>7</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>1752</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="G41" s="19" t="s">
         <v>559</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>1820</v>
+        <v>153</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>153</v>
@@ -23485,12 +23884,15 @@
         <v>153</v>
       </c>
       <c r="L41" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M41" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>1766</v>
@@ -23499,7 +23901,7 @@
         <v>7</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E42" s="16" t="s">
         <v>1752</v>
@@ -23514,7 +23916,7 @@
         <v>153</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="J42" s="19" t="s">
         <v>153</v>
@@ -23523,12 +23925,15 @@
         <v>153</v>
       </c>
       <c r="L42" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M42" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>1766</v>
@@ -23537,36 +23942,39 @@
         <v>8</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E43" s="16" t="s">
         <v>1752</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>97</v>
+        <v>1823</v>
       </c>
       <c r="G43" s="19" t="s">
         <v>734</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>1825</v>
+        <v>153</v>
       </c>
       <c r="I43" s="19" t="s">
         <v>153</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>775</v>
+        <v>153</v>
       </c>
       <c r="K43" s="19" t="s">
         <v>153</v>
       </c>
       <c r="L43" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M43" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>1766</v>
@@ -23575,16 +23983,16 @@
         <v>8</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>1752</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>191</v>
+        <v>1824</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>153</v>
+        <v>1825</v>
       </c>
       <c r="H44" s="19" t="s">
         <v>153</v>
@@ -23599,12 +24007,15 @@
         <v>153</v>
       </c>
       <c r="L44" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M44" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>1766</v>
@@ -23613,16 +24024,16 @@
         <v>8</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E45" s="16" t="s">
         <v>1752</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>1789</v>
+        <v>1826</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>153</v>
+        <v>734</v>
       </c>
       <c r="H45" s="19" t="s">
         <v>153</v>
@@ -23639,35 +24050,38 @@
       <c r="L45" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M45" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>1752</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>97</v>
+        <v>1827</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>517</v>
+        <v>734</v>
       </c>
       <c r="H46" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="I46" s="19" t="s">
         <v>1828</v>
       </c>
-      <c r="I46" s="19" t="s">
-        <v>153</v>
-      </c>
       <c r="J46" s="19" t="s">
         <v>153</v>
       </c>
@@ -23677,19 +24091,22 @@
       <c r="L46" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M46" s="19" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C47" s="16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>1752</v>
@@ -23715,19 +24132,22 @@
       <c r="L47" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M47" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>1752</v>
@@ -23753,124 +24173,136 @@
       <c r="L48" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M48" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="16" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D49" s="18" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J49" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L49" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M49" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16" t="s">
         <v>1830</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>1793</v>
-      </c>
-      <c r="F49" s="18" t="s">
-        <v>1831</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>870</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>1832</v>
-      </c>
-      <c r="I49" s="19" t="s">
-        <v>1833</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="K49" s="19" t="s">
-        <v>1834</v>
-      </c>
-      <c r="L49" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
-        <v>1829</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" s="18" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L50" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M50" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="16" t="s">
         <v>1830</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>1793</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>1835</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>881</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>1832</v>
-      </c>
-      <c r="I50" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="K50" s="19" t="s">
-        <v>1834</v>
-      </c>
-      <c r="L50" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
-        <v>1829</v>
       </c>
       <c r="B51" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>1793</v>
+        <v>1752</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>1836</v>
+        <v>1789</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>889</v>
+        <v>153</v>
       </c>
       <c r="H51" s="19" t="s">
         <v>153</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>1788</v>
+        <v>153</v>
       </c>
       <c r="J51" s="19" t="s">
         <v>153</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>1834</v>
+        <v>153</v>
       </c>
       <c r="L51" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M51" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="16" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="B52" s="16" t="s">
         <v>1766</v>
@@ -23879,36 +24311,39 @@
         <v>10</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="E52" s="16" t="s">
         <v>1793</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>1022</v>
+        <v>1834</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>153</v>
+        <v>870</v>
       </c>
       <c r="H52" s="19" t="s">
         <v>153</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>153</v>
+        <v>1835</v>
       </c>
       <c r="J52" s="19" t="s">
         <v>153</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="L52" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M52" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="16" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>1766</v>
@@ -23917,16 +24352,16 @@
         <v>10</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="E53" s="16" t="s">
         <v>1793</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>1789</v>
+        <v>1837</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>153</v>
+        <v>881</v>
       </c>
       <c r="H53" s="19" t="s">
         <v>153</v>
@@ -23938,74 +24373,80 @@
         <v>153</v>
       </c>
       <c r="K53" s="19" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="L53" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M53" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D54" s="18" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F54" s="18" t="s">
         <v>1838</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>1839</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>1840</v>
-      </c>
       <c r="G54" s="19" t="s">
-        <v>636</v>
+        <v>889</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>1841</v>
+        <v>153</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>1842</v>
+        <v>1788</v>
       </c>
       <c r="J54" s="19" t="s">
         <v>153</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>153</v>
+        <v>1836</v>
       </c>
       <c r="L54" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M54" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
-        <v>1843</v>
+        <v>1832</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>1844</v>
+        <v>1833</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>1845</v>
+        <v>1793</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>1846</v>
+        <v>1022</v>
       </c>
       <c r="G55" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>1847</v>
+        <v>153</v>
       </c>
       <c r="I55" s="19" t="s">
         <v>153</v>
@@ -24014,36 +24455,39 @@
         <v>153</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>153</v>
+        <v>1836</v>
       </c>
       <c r="L55" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M55" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="16" t="s">
-        <v>1848</v>
+        <v>1832</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C56" s="16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>1849</v>
+        <v>1833</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>1845</v>
+        <v>1793</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>1850</v>
+        <v>1789</v>
       </c>
       <c r="G56" s="19" t="s">
         <v>153</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>1851</v>
+        <v>153</v>
       </c>
       <c r="I56" s="19" t="s">
         <v>153</v>
@@ -24052,39 +24496,42 @@
         <v>153</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>153</v>
+        <v>1836</v>
       </c>
       <c r="L56" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M56" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="16" t="s">
-        <v>1852</v>
+        <v>1839</v>
       </c>
       <c r="B57" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>1853</v>
+        <v>1840</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>1845</v>
+        <v>1752</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>1854</v>
+        <v>97</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>153</v>
+        <v>636</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>1855</v>
+        <v>153</v>
       </c>
       <c r="I57" s="19" t="s">
-        <v>153</v>
+        <v>1841</v>
       </c>
       <c r="J57" s="19" t="s">
         <v>153</v>
@@ -24095,34 +24542,37 @@
       <c r="L57" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M57" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="16" t="s">
-        <v>1856</v>
+        <v>1839</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>1857</v>
+        <v>1840</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>1845</v>
+        <v>1752</v>
       </c>
       <c r="F58" s="18" t="s">
-        <v>1858</v>
+        <v>191</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>153</v>
+        <v>636</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>1859</v>
+        <v>153</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>153</v>
+        <v>1842</v>
       </c>
       <c r="J58" s="19" t="s">
         <v>153</v>
@@ -24133,294 +24583,318 @@
       <c r="L58" s="19" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M58" s="19" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="16" t="s">
-        <v>1860</v>
+        <v>1839</v>
       </c>
       <c r="B59" s="16" t="s">
         <v>1766</v>
       </c>
       <c r="C59" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>636</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>1844</v>
+      </c>
+      <c r="J59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L59" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M59" s="19" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>1849</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H60" s="19" t="s">
+        <v>1850</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J60" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L60" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M60" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="16" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H61" s="19" t="s">
+        <v>1854</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J61" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L61" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M61" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="16" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>1857</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>1858</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J62" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L62" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M62" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="16" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>1861</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J63" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L63" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M63" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="16" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C64" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="D59" s="18" t="s">
-        <v>1861</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>1845</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>1862</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>1863</v>
-      </c>
-      <c r="I59" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="J59" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="K59" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="L59" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="24" t="s">
+      <c r="D64" s="18" t="s">
         <v>1864</v>
       </c>
-      <c r="B60" s="24" t="s">
+      <c r="E64" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F64" s="18" t="s">
         <v>1865</v>
       </c>
-      <c r="C60" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D60" s="26" t="s">
+      <c r="G64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H64" s="19" t="s">
         <v>1866</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="I64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M64" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="16" t="s">
         <v>1867</v>
       </c>
-      <c r="F60" s="26" t="s">
+      <c r="B65" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D65" s="18" t="s">
         <v>1868</v>
       </c>
-      <c r="G60" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="H60" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I60" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K60" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L60" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="24" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C61" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E61" s="24" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F61" s="26" t="s">
+      <c r="E65" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F65" s="18" t="s">
         <v>1869</v>
       </c>
-      <c r="G61" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="H61" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I61" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J61" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K61" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L61" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="24" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C62" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F62" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="G62" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="H62" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I62" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K62" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L62" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="24" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C63" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D63" s="26" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E63" s="24" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F63" s="26" t="s">
+      <c r="G65" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H65" s="19" t="s">
         <v>1870</v>
       </c>
-      <c r="G63" s="25" t="s">
-        <v>391</v>
-      </c>
-      <c r="H63" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I63" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J63" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K63" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L63" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="24" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C64" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E64" s="24" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F64" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="G64" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="H64" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I64" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J64" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K64" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L64" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="24" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B65" s="24" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C65" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D65" s="26" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E65" s="24" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F65" s="26" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G65" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="H65" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I65" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K65" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L65" s="25" t="s">
+      <c r="I65" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J65" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L65" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M65" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C66" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>416</v>
+        <v>352</v>
       </c>
       <c r="H66" s="25" t="s">
         <v>153</v>
@@ -24435,30 +24909,33 @@
         <v>153</v>
       </c>
       <c r="L66" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M66" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C67" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="H67" s="25" t="s">
         <v>153</v>
@@ -24473,30 +24950,33 @@
         <v>153</v>
       </c>
       <c r="L67" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M67" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C68" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>1874</v>
+        <v>384</v>
       </c>
       <c r="G68" s="25" t="s">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="H68" s="25" t="s">
         <v>153</v>
@@ -24511,30 +24991,33 @@
         <v>153</v>
       </c>
       <c r="L68" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M68" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C69" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="G69" s="25" t="s">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="H69" s="25" t="s">
         <v>153</v>
@@ -24549,30 +25032,33 @@
         <v>153</v>
       </c>
       <c r="L69" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M69" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C70" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>1876</v>
+        <v>398</v>
       </c>
       <c r="G70" s="25" t="s">
-        <v>453</v>
+        <v>397</v>
       </c>
       <c r="H70" s="25" t="s">
         <v>153</v>
@@ -24587,30 +25073,33 @@
         <v>153</v>
       </c>
       <c r="L70" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M70" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C71" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>461</v>
+        <v>1878</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="H71" s="25" t="s">
         <v>153</v>
@@ -24625,36 +25114,39 @@
         <v>153</v>
       </c>
       <c r="L71" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M71" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C72" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>316</v>
+        <v>416</v>
       </c>
       <c r="H72" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I72" s="25" t="s">
-        <v>1878</v>
+        <v>153</v>
       </c>
       <c r="J72" s="25" t="s">
         <v>153</v>
@@ -24663,30 +25155,33 @@
         <v>153</v>
       </c>
       <c r="L72" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M72" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C73" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E73" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>289</v>
+        <v>1880</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="H73" s="25" t="s">
         <v>153</v>
@@ -24701,36 +25196,39 @@
         <v>153</v>
       </c>
       <c r="L73" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M73" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C74" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>647</v>
+        <v>441</v>
       </c>
       <c r="H74" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I74" s="25" t="s">
-        <v>1880</v>
+        <v>153</v>
       </c>
       <c r="J74" s="25" t="s">
         <v>153</v>
@@ -24739,30 +25237,33 @@
         <v>153</v>
       </c>
       <c r="L74" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M74" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C75" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>714</v>
+        <v>1882</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>713</v>
+        <v>446</v>
       </c>
       <c r="H75" s="25" t="s">
         <v>153</v>
@@ -24777,30 +25278,33 @@
         <v>153</v>
       </c>
       <c r="L75" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M75" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C76" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="G76" s="25" t="s">
-        <v>694</v>
+        <v>453</v>
       </c>
       <c r="H76" s="25" t="s">
         <v>153</v>
@@ -24815,30 +25319,33 @@
         <v>153</v>
       </c>
       <c r="L76" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M76" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C77" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>1882</v>
+        <v>461</v>
       </c>
       <c r="G77" s="25" t="s">
-        <v>789</v>
+        <v>460</v>
       </c>
       <c r="H77" s="25" t="s">
         <v>153</v>
@@ -24853,36 +25360,39 @@
         <v>153</v>
       </c>
       <c r="L77" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M77" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C78" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>799</v>
+        <v>1884</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>798</v>
+        <v>316</v>
       </c>
       <c r="H78" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I78" s="25" t="s">
-        <v>153</v>
+        <v>1885</v>
       </c>
       <c r="J78" s="25" t="s">
         <v>153</v>
@@ -24891,36 +25401,39 @@
         <v>153</v>
       </c>
       <c r="L78" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M78" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B79" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C79" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>1883</v>
+        <v>289</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>1884</v>
+        <v>288</v>
       </c>
       <c r="H79" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I79" s="25" t="s">
-        <v>1885</v>
+        <v>153</v>
       </c>
       <c r="J79" s="25" t="s">
         <v>153</v>
@@ -24929,36 +25442,39 @@
         <v>153</v>
       </c>
       <c r="L79" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M79" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C80" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F80" s="26" t="s">
         <v>1886</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>603</v>
+        <v>647</v>
       </c>
       <c r="H80" s="25" t="s">
         <v>153</v>
       </c>
       <c r="I80" s="25" t="s">
-        <v>153</v>
+        <v>1887</v>
       </c>
       <c r="J80" s="25" t="s">
         <v>153</v>
@@ -24967,49 +25483,301 @@
         <v>153</v>
       </c>
       <c r="L80" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M80" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="24" t="s">
-        <v>1864</v>
+        <v>1871</v>
       </c>
       <c r="B81" s="24" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C81" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>1866</v>
+        <v>1873</v>
       </c>
       <c r="E81" s="24" t="s">
-        <v>1867</v>
+        <v>1874</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>1887</v>
+        <v>714</v>
       </c>
       <c r="G81" s="25" t="s">
+        <v>713</v>
+      </c>
+      <c r="H81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L81" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M81" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="24" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C82" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E82" s="24" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F82" s="26" t="s">
+        <v>1888</v>
+      </c>
+      <c r="G82" s="25" t="s">
+        <v>694</v>
+      </c>
+      <c r="H82" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I82" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J82" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K82" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L82" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M82" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="24" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C83" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D83" s="26" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E83" s="24" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F83" s="26" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G83" s="25" t="s">
+        <v>789</v>
+      </c>
+      <c r="H83" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I83" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J83" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K83" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L83" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M83" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="24" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C84" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E84" s="24" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F84" s="26" t="s">
+        <v>799</v>
+      </c>
+      <c r="G84" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="H84" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I84" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J84" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K84" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L84" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M84" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="24" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C85" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E85" s="24" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>1890</v>
+      </c>
+      <c r="G85" s="25" t="s">
+        <v>1891</v>
+      </c>
+      <c r="H85" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I85" s="25" t="s">
+        <v>1892</v>
+      </c>
+      <c r="J85" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K85" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L85" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M85" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="24" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B86" s="24" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C86" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E86" s="24" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F86" s="26" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G86" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="H86" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I86" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J86" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K86" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L86" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M86" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="24" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C87" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D87" s="26" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E87" s="24" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F87" s="26" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G87" s="25" t="s">
         <v>838</v>
       </c>
-      <c r="H81" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I81" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J81" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K81" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L81" s="25" t="s">
+      <c r="H87" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I87" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J87" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="K87" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L87" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="M87" s="25" t="s">
         <v>153</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L81"/>
+  <autoFilter ref="A5:M87"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -25022,6 +25790,896 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:G41"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>1900</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>913</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>913</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>934</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>934</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>946</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>946</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>970</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>970</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>986</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>986</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>990</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>990</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>639</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>639</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="29" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="29" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>735</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="29" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="29" t="s">
+        <v>997</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>997</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:G41"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -25042,349 +26700,349 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1888</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>1889</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>1890</v>
+        <v>1986</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1891</v>
+        <v>1987</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1892</v>
+        <v>1988</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1893</v>
+        <v>1989</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1894</v>
+        <v>1990</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1895</v>
+        <v>1991</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1896</v>
+        <v>1992</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1897</v>
+        <v>1993</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1898</v>
+        <v>1994</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>1899</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1900</v>
+        <v>1996</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1901</v>
+        <v>1997</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1902</v>
+        <v>1998</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>1903</v>
+        <v>1999</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1904</v>
+        <v>2000</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>1905</v>
+        <v>2001</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>1906</v>
+        <v>2002</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>1907</v>
+        <v>2003</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>1908</v>
+        <v>2004</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>1909</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1910</v>
+        <v>2006</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1910</v>
+        <v>2006</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1911</v>
+        <v>2007</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1912</v>
+        <v>2008</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1913</v>
+        <v>2009</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>1915</v>
+        <v>2011</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>1916</v>
+        <v>2012</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>1917</v>
+        <v>2013</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>1909</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1918</v>
+        <v>2014</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>1918</v>
+        <v>2014</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1919</v>
+        <v>2015</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>1920</v>
+        <v>2016</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>1921</v>
+        <v>2017</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>1922</v>
+        <v>2018</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>1923</v>
+        <v>2019</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>1924</v>
+        <v>2020</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>1909</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1925</v>
+        <v>2021</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>1925</v>
+        <v>2021</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1926</v>
+        <v>2022</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1927</v>
+        <v>2023</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1928</v>
+        <v>2024</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>1929</v>
+        <v>2025</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>1930</v>
+        <v>2026</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>1931</v>
+        <v>2027</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>1909</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1932</v>
+        <v>2028</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>1932</v>
+        <v>2028</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1926</v>
+        <v>2022</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>1933</v>
+        <v>2029</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1934</v>
+        <v>2030</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>1935</v>
+        <v>2031</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>153</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>1936</v>
+        <v>2032</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>1909</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1937</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>1938</v>
+        <v>2034</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1939</v>
+        <v>2035</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1940</v>
+        <v>2036</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1941</v>
+        <v>2037</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>1942</v>
+        <v>2038</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>1943</v>
+        <v>2039</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>1944</v>
+        <v>2040</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>1945</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1946</v>
+        <v>2042</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>1947</v>
+        <v>2043</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1939</v>
+        <v>2035</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>1948</v>
+        <v>2044</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>1949</v>
+        <v>2045</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>1942</v>
+        <v>2038</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>1950</v>
+        <v>2046</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>1951</v>
+        <v>2047</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>1952</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1953</v>
+        <v>2049</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>1954</v>
+        <v>2050</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1939</v>
+        <v>2035</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>1955</v>
+        <v>2051</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>1956</v>
+        <v>2052</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>1957</v>
+        <v>2053</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>1958</v>
+        <v>2054</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>1959</v>
+        <v>2055</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>1960</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1961</v>
+        <v>2057</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>1962</v>
+        <v>2058</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1963</v>
+        <v>2059</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>1964</v>
+        <v>2060</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>1965</v>
+        <v>2061</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>1966</v>
+        <v>2062</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>1967</v>
+        <v>2063</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>1968</v>
+        <v>2064</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>1969</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1970</v>
+        <v>2066</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>1971</v>
+        <v>2067</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1972</v>
+        <v>2068</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>1973</v>
+        <v>2069</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>1974</v>
+        <v>2070</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>153</v>
@@ -25393,36 +27051,36 @@
         <v>181</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>1975</v>
+        <v>2071</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>1976</v>
+        <v>2072</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>1977</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1978</v>
+        <v>2074</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>1979</v>
+        <v>2075</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1939</v>
+        <v>2035</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>1980</v>
+        <v>2076</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>153</v>
@@ -25431,30 +27089,30 @@
         <v>153</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1981</v>
+        <v>2077</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>1982</v>
+        <v>2078</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1939</v>
+        <v>2035</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>1980</v>
+        <v>2076</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>153</v>
@@ -25463,30 +27121,30 @@
         <v>153</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1983</v>
+        <v>2079</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1984</v>
+        <v>2080</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1939</v>
+        <v>2035</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>1980</v>
+        <v>2076</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>153</v>
@@ -25495,30 +27153,30 @@
         <v>153</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1985</v>
+        <v>2081</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>1986</v>
+        <v>2082</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1987</v>
+        <v>2083</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>1988</v>
+        <v>2084</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>153</v>
@@ -25527,59 +27185,59 @@
         <v>153</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1989</v>
+        <v>2085</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>1990</v>
+        <v>2086</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1991</v>
+        <v>2087</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>1992</v>
+        <v>2088</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>1993</v>
+        <v>2089</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>153</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1994</v>
+        <v>2090</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>1995</v>
+        <v>2091</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1996</v>
+        <v>2092</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>304</v>
@@ -25591,7 +27249,7 @@
         <v>153</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25599,22 +27257,22 @@
         <v>44</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>1997</v>
+        <v>2093</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>1998</v>
+        <v>2094</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>1999</v>
+        <v>2095</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>153</v>
@@ -25623,7 +27281,7 @@
         <v>153</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
     </row>
   </sheetData>
@@ -25639,7 +27297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -25663,12 +27321,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2000</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2001</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25676,172 +27334,172 @@
         <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2002</v>
+        <v>2098</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2003</v>
+        <v>2099</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2004</v>
+        <v>2100</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>2005</v>
+        <v>2101</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>2006</v>
+        <v>2102</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>2007</v>
+        <v>2103</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>2008</v>
+        <v>2104</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1898</v>
+        <v>1994</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>2009</v>
+        <v>2105</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>2010</v>
+        <v>2106</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>2011</v>
+        <v>2107</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>2012</v>
+        <v>2108</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>2013</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>2014</v>
+        <v>2110</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>2015</v>
+        <v>2111</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>2016</v>
+        <v>2112</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>2017</v>
+        <v>2113</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>915</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>2018</v>
+        <v>2114</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>2019</v>
+        <v>2115</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>2020</v>
+        <v>2116</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>2021</v>
+        <v>2117</v>
       </c>
       <c r="J6" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>2022</v>
+        <v>2118</v>
       </c>
       <c r="L6" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>2023</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>2024</v>
+        <v>2120</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>2025</v>
+        <v>2121</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>2026</v>
+        <v>2122</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>2027</v>
+        <v>2123</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>2028</v>
+        <v>2124</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>2029</v>
+        <v>2125</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>2030</v>
+        <v>2126</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>2031</v>
+        <v>2127</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>2032</v>
+        <v>2128</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>2033</v>
+        <v>2129</v>
       </c>
       <c r="K7" s="28" t="s">
-        <v>2034</v>
+        <v>2130</v>
       </c>
       <c r="L7" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>2035</v>
+        <v>2131</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>2036</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>2037</v>
+        <v>2133</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>2038</v>
+        <v>2134</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>2039</v>
+        <v>2135</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>2040</v>
+        <v>2136</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>2041</v>
+        <v>2137</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>2042</v>
+        <v>2138</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>112</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>2043</v>
+        <v>2139</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>2032</v>
+        <v>2128</v>
       </c>
       <c r="J8" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>2044</v>
+        <v>2140</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>2045</v>
+        <v>2141</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>153</v>
@@ -25849,31 +27507,31 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>2046</v>
+        <v>2142</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>2047</v>
+        <v>2143</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>2048</v>
+        <v>2144</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>2049</v>
+        <v>2145</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>2050</v>
+        <v>2146</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>2051</v>
+        <v>2147</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>112</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>2052</v>
+        <v>2148</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>2053</v>
+        <v>2149</v>
       </c>
       <c r="J9" s="28" t="s">
         <v>153</v>
@@ -25888,36 +27546,36 @@
         <v>153</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>2054</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>2055</v>
+        <v>2151</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>2056</v>
+        <v>2152</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>2057</v>
+        <v>2153</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>2058</v>
+        <v>2154</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>2059</v>
+        <v>2155</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>2060</v>
+        <v>2156</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>2061</v>
+        <v>2157</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>2062</v>
+        <v>2158</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>2053</v>
+        <v>2149</v>
       </c>
       <c r="J10" s="28" t="s">
         <v>153</v>
@@ -25932,39 +27590,39 @@
         <v>153</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>2063</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>2064</v>
+        <v>2160</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>2065</v>
+        <v>2161</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>2066</v>
+        <v>2162</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>2067</v>
+        <v>2163</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>2068</v>
+        <v>2164</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>2069</v>
+        <v>2165</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>2070</v>
+        <v>2166</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>2071</v>
+        <v>2167</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>2072</v>
+        <v>2168</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>2073</v>
+        <v>2169</v>
       </c>
       <c r="K11" s="28" t="s">
         <v>153</v>
@@ -25976,48 +27634,48 @@
         <v>153</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>2074</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>2075</v>
+        <v>2171</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>2076</v>
+        <v>2172</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>2077</v>
+        <v>2173</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>2078</v>
+        <v>2174</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>2079</v>
+        <v>2175</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>2080</v>
+        <v>2176</v>
       </c>
       <c r="G12" s="15" t="s">
         <v>642</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>2081</v>
+        <v>2177</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>2082</v>
+        <v>2178</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>2083</v>
+        <v>2179</v>
       </c>
       <c r="L12" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>2084</v>
+        <v>2180</v>
       </c>
       <c r="N12" s="28" t="s">
         <v>153</v>
@@ -26025,43 +27683,43 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>2085</v>
+        <v>2181</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>2086</v>
+        <v>2182</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>2087</v>
+        <v>2183</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>2088</v>
+        <v>2184</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>2089</v>
+        <v>2185</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>2090</v>
+        <v>2186</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>2091</v>
+        <v>2187</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>2092</v>
+        <v>2188</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>2093</v>
+        <v>2189</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>2094</v>
+        <v>2190</v>
       </c>
       <c r="K13" s="28" t="s">
         <v>153</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>2095</v>
+        <v>2191</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>2096</v>
+        <v>2192</v>
       </c>
       <c r="N13" s="28" t="s">
         <v>153</v>
@@ -26069,31 +27727,31 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>2097</v>
+        <v>2193</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>2098</v>
+        <v>2194</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>2099</v>
+        <v>2195</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>2100</v>
+        <v>2196</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>2101</v>
+        <v>2197</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>2090</v>
+        <v>2186</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>2102</v>
+        <v>2198</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>2103</v>
+        <v>2199</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>2104</v>
+        <v>2200</v>
       </c>
       <c r="J14" s="28" t="s">
         <v>153</v>
@@ -26108,39 +27766,39 @@
         <v>153</v>
       </c>
       <c r="N14" s="28" t="s">
-        <v>2105</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>2106</v>
+        <v>2202</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>2107</v>
+        <v>2203</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>2108</v>
+        <v>2204</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>2109</v>
+        <v>2205</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>2110</v>
+        <v>2206</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>2090</v>
+        <v>2186</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>2111</v>
+        <v>2207</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>2112</v>
+        <v>2208</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>2113</v>
+        <v>2209</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>2114</v>
+        <v>2210</v>
       </c>
       <c r="K15" s="28" t="s">
         <v>153</v>
@@ -26152,36 +27810,36 @@
         <v>153</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>2115</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>2116</v>
+        <v>2212</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2117</v>
+        <v>2213</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2118</v>
+        <v>2214</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>2119</v>
+        <v>2215</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>2120</v>
+        <v>2216</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>2121</v>
+        <v>2217</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>2122</v>
+        <v>2218</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>2123</v>
+        <v>2219</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>153</v>
@@ -26190,42 +27848,42 @@
         <v>153</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>2124</v>
+        <v>2220</v>
       </c>
       <c r="M16" s="28" t="s">
         <v>153</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>2125</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>2126</v>
+        <v>2222</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>2127</v>
+        <v>2223</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>2128</v>
+        <v>2224</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>2129</v>
+        <v>2225</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>2119</v>
+        <v>2215</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>2120</v>
+        <v>2216</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>2121</v>
+        <v>2217</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>2130</v>
+        <v>2226</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>2123</v>
+        <v>2219</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>153</v>
@@ -26234,42 +27892,42 @@
         <v>153</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>2124</v>
+        <v>2220</v>
       </c>
       <c r="M17" s="28" t="s">
         <v>153</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>2125</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>2131</v>
+        <v>2227</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>2132</v>
+        <v>2228</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2133</v>
+        <v>2229</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2134</v>
+        <v>2230</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>2135</v>
+        <v>2231</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>2060</v>
+        <v>2156</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>2136</v>
+        <v>2232</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>2137</v>
+        <v>2233</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>2138</v>
+        <v>2234</v>
       </c>
       <c r="J18" s="28" t="s">
         <v>153</v>
@@ -26278,54 +27936,54 @@
         <v>153</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>2139</v>
+        <v>2235</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>2140</v>
+        <v>2236</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>2141</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>2142</v>
+        <v>2238</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>2143</v>
+        <v>2239</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2144</v>
+        <v>2240</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2145</v>
+        <v>2241</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>2146</v>
+        <v>2242</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>2042</v>
+        <v>2138</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>2147</v>
+        <v>2243</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>2148</v>
+        <v>2244</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>2149</v>
+        <v>2245</v>
       </c>
       <c r="J19" s="28" t="s">
         <v>153</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>2150</v>
+        <v>2246</v>
       </c>
       <c r="L19" s="28" t="s">
         <v>153</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>2151</v>
+        <v>2247</v>
       </c>
       <c r="N19" s="28" t="s">
         <v>153</v>
@@ -26333,31 +27991,31 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>2152</v>
+        <v>2248</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>2153</v>
+        <v>2249</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2154</v>
+        <v>2250</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2155</v>
+        <v>2251</v>
       </c>
       <c r="E20" s="15" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>2156</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>2060</v>
-      </c>
       <c r="G20" s="15" t="s">
-        <v>2157</v>
+        <v>2253</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>2158</v>
+        <v>2254</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>2159</v>
+        <v>2255</v>
       </c>
       <c r="J20" s="28" t="s">
         <v>153</v>
@@ -26366,42 +28024,42 @@
         <v>153</v>
       </c>
       <c r="L20" s="28" t="s">
-        <v>2160</v>
+        <v>2256</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>2161</v>
+        <v>2257</v>
       </c>
       <c r="N20" s="28" t="s">
-        <v>2162</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>2163</v>
+        <v>2259</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>2164</v>
+        <v>2260</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2165</v>
+        <v>2261</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>2166</v>
+        <v>2262</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>2167</v>
+        <v>2263</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>2090</v>
+        <v>2186</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>847</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>2168</v>
+        <v>2264</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>2169</v>
+        <v>2265</v>
       </c>
       <c r="J21" s="28" t="s">
         <v>153</v>
@@ -26416,36 +28074,36 @@
         <v>153</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>2170</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>2171</v>
+        <v>2267</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>2172</v>
+        <v>2268</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2173</v>
+        <v>2269</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2174</v>
+        <v>2270</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>2175</v>
+        <v>2271</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>2090</v>
+        <v>2186</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>2176</v>
+        <v>2272</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>2177</v>
+        <v>2273</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>2178</v>
+        <v>2274</v>
       </c>
       <c r="J22" s="28" t="s">
         <v>153</v>
@@ -26457,39 +28115,39 @@
         <v>153</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>2179</v>
+        <v>2275</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>2180</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>2181</v>
+        <v>2277</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>2182</v>
+        <v>2278</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2183</v>
+        <v>2279</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>2184</v>
+        <v>2280</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>2185</v>
+        <v>2281</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>2186</v>
+        <v>2282</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>227</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>2187</v>
+        <v>2283</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>2178</v>
+        <v>2274</v>
       </c>
       <c r="J23" s="28" t="s">
         <v>153</v>
@@ -26498,10 +28156,10 @@
         <v>153</v>
       </c>
       <c r="L23" s="28" t="s">
-        <v>2188</v>
+        <v>2284</v>
       </c>
       <c r="M23" s="28" t="s">
-        <v>2189</v>
+        <v>2285</v>
       </c>
       <c r="N23" s="28" t="s">
         <v>153</v>
@@ -26509,31 +28167,31 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>2190</v>
+        <v>2286</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>2191</v>
+        <v>2287</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2192</v>
+        <v>2288</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>2193</v>
+        <v>2289</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>2194</v>
+        <v>2290</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>2090</v>
+        <v>2186</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>2195</v>
+        <v>2291</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>2196</v>
+        <v>2292</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>2197</v>
+        <v>2293</v>
       </c>
       <c r="J24" s="28" t="s">
         <v>153</v>
@@ -26545,42 +28203,42 @@
         <v>153</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>2198</v>
+        <v>2294</v>
       </c>
       <c r="N24" s="28" t="s">
-        <v>2199</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>2200</v>
+        <v>2296</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>2201</v>
+        <v>2297</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2202</v>
+        <v>2298</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>872</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>2203</v>
+        <v>2299</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>2204</v>
+        <v>2300</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>875</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>2205</v>
+        <v>2301</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>2206</v>
+        <v>2302</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>2207</v>
+        <v>2303</v>
       </c>
       <c r="K25" s="28" t="s">
         <v>153</v>
@@ -26592,27 +28250,27 @@
         <v>153</v>
       </c>
       <c r="N25" s="28" t="s">
-        <v>2208</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>2209</v>
+        <v>2305</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>2210</v>
+        <v>2306</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2211</v>
+        <v>2307</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>2212</v>
+        <v>2308</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>2213</v>
+        <v>2309</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>2204</v>
+        <v>2300</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>875</v>
@@ -26621,10 +28279,10 @@
         <v>887</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>2214</v>
+        <v>2310</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>2207</v>
+        <v>2303</v>
       </c>
       <c r="K26" s="28" t="s">
         <v>153</v>
@@ -26652,7 +28310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -26668,26 +28326,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2215</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2216</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>2217</v>
+        <v>2313</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>2218</v>
+        <v>1897</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2219</v>
+        <v>2314</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2220</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26695,7 +28353,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>2221</v>
+        <v>2316</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>41</v>
@@ -26707,7 +28365,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>2222</v>
+        <v>2317</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>42</v>
@@ -26719,7 +28377,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>2223</v>
+        <v>2318</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>43</v>
@@ -26731,7 +28389,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>2224</v>
+        <v>2319</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>44</v>
@@ -26743,13 +28401,13 @@
         <v>35</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>2225</v>
+        <v>2320</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>45</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>2226</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26757,7 +28415,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>2227</v>
+        <v>2322</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>46</v>
@@ -26769,7 +28427,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>2228</v>
+        <v>2323</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>47</v>
@@ -26781,7 +28439,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>2229</v>
+        <v>2324</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>48</v>
@@ -26793,13 +28451,13 @@
         <v>35</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>2230</v>
+        <v>2325</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>2231</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26807,191 +28465,191 @@
         <v>35</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>2232</v>
+        <v>2327</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2226</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>2233</v>
+        <v>2328</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>2234</v>
+        <v>2329</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2235</v>
+        <v>2330</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2236</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>2233</v>
+        <v>2328</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>2237</v>
+        <v>2332</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>2238</v>
+        <v>2333</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>2239</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>2233</v>
+        <v>2328</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>2240</v>
+        <v>2335</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2241</v>
+        <v>2336</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2242</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>2243</v>
+        <v>2338</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>2244</v>
+        <v>2339</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2245</v>
+        <v>2340</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2246</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>2243</v>
+        <v>2338</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>2247</v>
+        <v>2342</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>2248</v>
+        <v>2343</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2249</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>2243</v>
+        <v>2338</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>2250</v>
+        <v>2345</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2251</v>
+        <v>2346</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>2252</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>2243</v>
+        <v>2338</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>2253</v>
+        <v>2348</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2254</v>
+        <v>2349</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2255</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>2256</v>
+        <v>2351</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>2257</v>
+        <v>2352</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2258</v>
+        <v>2353</v>
       </c>
       <c r="D23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>2256</v>
+        <v>2351</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>2259</v>
+        <v>2354</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2260</v>
+        <v>2355</v>
       </c>
       <c r="D24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>2256</v>
+        <v>2351</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>2261</v>
+        <v>2356</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>2262</v>
+        <v>2357</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>2263</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>2256</v>
+        <v>2351</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>2264</v>
+        <v>2359</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2265</v>
+        <v>2360</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>2266</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>2256</v>
+        <v>2351</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>2267</v>
+        <v>2362</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>2268</v>
+        <v>2363</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>2269</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>2256</v>
+        <v>2351</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>2270</v>
+        <v>2365</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>2271</v>
+        <v>2366</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>2272</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26999,13 +28657,13 @@
         <v>53</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>2273</v>
+        <v>2368</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>56</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>2274</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27013,13 +28671,13 @@
         <v>53</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2275</v>
+        <v>2370</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>2276</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27027,317 +28685,317 @@
         <v>53</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>2277</v>
+        <v>2372</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>60</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>2278</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>2280</v>
+        <v>2375</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>112</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>2281</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>2282</v>
+        <v>2377</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>2283</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>2284</v>
+        <v>2379</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>2285</v>
+        <v>2380</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>2286</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>2287</v>
+        <v>2382</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>227</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>2288</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>2289</v>
+        <v>2384</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>2290</v>
+        <v>2385</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>2291</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>2292</v>
+        <v>2387</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>581</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>2293</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>2279</v>
+        <v>2374</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>2294</v>
+        <v>2389</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>779</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>2295</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>2296</v>
+        <v>2391</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>2297</v>
+        <v>2392</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>2298</v>
+        <v>2393</v>
       </c>
       <c r="D39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>2296</v>
+        <v>2391</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>2299</v>
+        <v>2394</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>2300</v>
+        <v>2395</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>2301</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>2296</v>
+        <v>2391</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>2302</v>
+        <v>2397</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>2303</v>
+        <v>2398</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>2304</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>2296</v>
+        <v>2391</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>2305</v>
+        <v>2400</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>2306</v>
+        <v>2401</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>2307</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>2308</v>
+        <v>2403</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>2309</v>
+        <v>2404</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>2310</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>2308</v>
+        <v>2403</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>2311</v>
+        <v>2406</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>2312</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>2308</v>
+        <v>2403</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>2313</v>
+        <v>2408</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>74</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>2314</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>2308</v>
+        <v>2403</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>2315</v>
+        <v>2410</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>75</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>2316</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>2308</v>
+        <v>2403</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>2317</v>
+        <v>2412</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>2318</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>2319</v>
+        <v>2414</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>2320</v>
+        <v>2415</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>2321</v>
+        <v>2416</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>2322</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>2319</v>
+        <v>2414</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>2323</v>
+        <v>2418</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>1969</v>
+        <v>2065</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>2324</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>2319</v>
+        <v>2414</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>2325</v>
+        <v>2420</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1914</v>
+        <v>2010</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>2326</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>2327</v>
+        <v>2422</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>2328</v>
+        <v>2423</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>2329</v>
+        <v>2424</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>2330</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>2327</v>
+        <v>2422</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>2331</v>
+        <v>2426</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>2332</v>
+        <v>2427</v>
       </c>
       <c r="D52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>2327</v>
+        <v>2422</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>2333</v>
+        <v>2428</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>2334</v>
+        <v>2429</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>2335</v>
+        <v>2430</v>
       </c>
     </row>
   </sheetData>

--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">Questionnaire d'accueil : premiere utilisation et nouveau lieu</t>
   </si>
   <si>
-    <t xml:space="preserve">Une ligne = une reponse possible. Chaque obligation a sa propre question de date (onglet Questions de date, seed/date_questions.json), qui nomme l'appareil et l'intervention. Réponses graduées avec le vrai délai de l'obligation : mois et année → calcul normal ; « Il y a moins de {délai} », sans date précise → à confirmer (orange) ; « Il y a plus de {délai} » → en retard (rouge) ; « Jamais » ou « Je ne sais pas » → en retard, prioritaire. Les dates se choisissent dans deux listes (mois en toutes lettres, année) et s'affichent « septembre 2026 », jamais avec un jour.</t>
+    <t xml:space="preserve">Une ligne = une reponse possible. Chaque obligation a sa propre question de date (onglet Questions de date, seed/date_questions.json), qui nomme l'appareil et l'intervention. Réponses graduées avec le vrai délai de l'obligation : mois et année → calcul normal ; « Il y a moins de {délai} », sans date précise → à confirmer (orange) ; « Il y a plus de {délai} » → en retard (rouge) ; « Jamais ou je ne sais pas », un seul bouton en dernière position → en retard, prioritaire. Les dates se choisissent dans deux listes (mois en toutes lettres, année) et s'affichent « septembre 2026 », jamais avec un jour.</t>
   </si>
   <si>
     <t xml:space="preserve">Bloc</t>
@@ -5588,7 +5588,7 @@
     <t xml:space="preserve">Pour chaque obligation créée</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaque obligation a sa propre question de date (onglet Questions de date, seed/date_questions.json), qui nomme l'appareil et l'intervention. Réponses graduées avec le vrai délai de l'obligation : mois et année → calcul normal ; « Il y a moins de {délai} », sans date précise → à confirmer (orange) ; « Il y a plus de {délai} » → en retard (rouge) ; « Jamais » ou « Je ne sais pas » → en retard, prioritaire. Les dates se choisissent dans deux listes (mois en toutes lettres, année) et s'affichent « septembre 2026 », jamais avec un jour.</t>
+    <t xml:space="preserve">Chaque obligation a sa propre question de date (onglet Questions de date, seed/date_questions.json), qui nomme l'appareil et l'intervention. Réponses graduées avec le vrai délai de l'obligation : mois et année → calcul normal ; « Il y a moins de {délai} », sans date précise → à confirmer (orange) ; « Il y a plus de {délai} » → en retard (rouge) ; « Jamais ou je ne sais pas », un seul bouton en dernière position → en retard, prioritaire. Les dates se choisissent dans deux listes (mois en toutes lettres, année) et s'affichent « septembre 2026 », jamais avec un jour.</t>
   </si>
   <si>
     <t xml:space="preserve">REGLE-02</t>
@@ -5600,7 +5600,7 @@
     <t xml:space="preserve">Pour chaque question d'obligation</t>
   </si>
   <si>
-    <t xml:space="preserve">« Je ne sais pas » ne bloque jamais la progression : la réponse ajoute un point « à vérifier » sur l'écran d'accueil, avec l'aide associée pour trouver la réponse. Même règle pour les questions de suivi. À l'écran, c'est un choix discret, sous les autres.</t>
+    <t xml:space="preserve">« Je ne sais pas » ne bloque jamais la progression : la réponse ajoute un point « à vérifier » sur l'écran d'accueil, avec l'aide associée pour trouver la réponse. Même règle pour les questions de suivi. À l'écran, c'est un bouton comme les autres, en dernière position.</t>
   </si>
   <si>
     <t xml:space="preserve">REGLE-03</t>
@@ -5726,7 +5726,7 @@
     <t xml:space="preserve">Une question de date par obligation, avec le vrai delai legal</t>
   </si>
   <si>
-    <t xml:space="preserve">Mois gradue : mois et annee | Il y a moins de {delai} | Il y a plus de {delai} | Jamais | Je ne sais pas. Affichage des dates : septembre 2026.</t>
+    <t xml:space="preserve">Mois gradue : mois et annee | Il y a moins de {delai} | Il y a plus de {delai} | Jamais ou je ne sais pas (un seul bouton, en dernier). Affichage des dates : septembre 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Cle</t>
@@ -24628,7 +24628,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="16" t="s">
         <v>1846</v>
       </c>
@@ -24669,7 +24669,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="16" t="s">
         <v>1851</v>
       </c>

--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -17237,7 +17237,7 @@
         <v>56</v>
       </c>
       <c r="P47" s="23" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="Q47" s="24" t="n">
         <v>15</v>
@@ -17399,7 +17399,7 @@
         <v>56</v>
       </c>
       <c r="P50" s="23" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="Q50" s="24" t="n">
         <v>30</v>
@@ -22043,7 +22043,7 @@
         <v>56</v>
       </c>
       <c r="P136" s="23" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="Q136" s="24" t="n">
         <v>15</v>

--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -5954,7 +5954,7 @@
     <t xml:space="preserve">Péremption</t>
   </si>
   <si>
-    <t xml:space="preserve">Mois et année, ou « Je ne trouve pas la date » (à confirmer). La date donnée devient l'échéance.</t>
+    <t xml:space="preserve">Mois et année, années futures proposées (la date de péremption est à venir), ou « Je ne trouve pas la date » (à confirmer). La date donnée devient l'échéance.</t>
   </si>
   <si>
     <t xml:space="preserve">Détecteur de fumée</t>
@@ -5966,7 +5966,7 @@
     <t xml:space="preserve">Fabrication</t>
   </si>
   <si>
-    <t xml:space="preserve">Explication affichée : un détecteur se remplace 10 ans après sa fabrication. Mois et année, ou « Je ne la trouve pas » (à confirmer). Échéance = date + 10 ans.</t>
+    <t xml:space="preserve">Deux cas, au choix de l'utilisateur : date de fabrication (échéance = date + 10 ans) ou date limite de remplacement, souvent imprimée « à remplacer avant … » (échéance = cette date). Mois et année ; années futures proposées pour la date limite. « Je ne la trouve pas » → à confirmer.</t>
   </si>
   <si>
     <t xml:space="preserve">Quand la voiture a-t-elle passé son dernier contrôle technique ?</t>
@@ -27480,7 +27480,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
         <v>1246</v>
       </c>
@@ -27503,7 +27503,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
         <v>1366</v>
       </c>

--- a/docs/referentiel_entretien_france.xlsx
+++ b/docs/referentiel_entretien_france.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="B2:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -680,7 +680,6 @@
     <col width="105" customWidth="1" style="31" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="32">
       <c r="B2" s="33" t="inlineStr">
         <is>
@@ -695,7 +694,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="42" customHeight="1" s="32">
       <c r="B5" s="35" t="inlineStr">
         <is>
@@ -804,7 +802,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="32">
       <c r="B15" s="35" t="inlineStr">
         <is>
@@ -848,7 +845,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="32">
       <c r="B20" s="35" t="inlineStr">
         <is>
@@ -1531,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R114"/>
+  <dimension ref="A2:R114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="31" min="1" max="1"/>
@@ -1551,7 +1547,6 @@
     <col width="44" customWidth="1" style="31" min="16" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="32">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -1566,7 +1561,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="41" t="inlineStr">
         <is>
@@ -11374,7 +11368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q163"/>
+  <dimension ref="A2:R163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="31" min="1" max="2"/>
@@ -11395,7 +11389,6 @@
     <col width="11" customWidth="1" style="31" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="32">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -11410,7 +11403,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="41" t="inlineStr">
         <is>
@@ -11495,6 +11487,11 @@
       <c r="Q5" s="41" t="inlineStr">
         <is>
           <t>Temps actif (min)</t>
+        </is>
+      </c>
+      <c r="R5" s="41" t="inlineStr">
+        <is>
+          <t>Risque affiche</t>
         </is>
       </c>
     </row>
@@ -11577,6 +11574,11 @@
       <c r="Q6" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="35.05" customHeight="1" s="32">
       <c r="A7" s="55" t="inlineStr">
@@ -11657,6 +11659,11 @@
       <c r="Q7" s="56" t="n">
         <v>3</v>
       </c>
+      <c r="R7" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="23.85" customHeight="1" s="32">
       <c r="A8" s="45" t="inlineStr">
@@ -11737,6 +11744,11 @@
       <c r="Q8" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="35.05" customHeight="1" s="32">
       <c r="A9" s="49" t="inlineStr">
@@ -11817,6 +11829,11 @@
       <c r="Q9" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="32">
       <c r="A10" s="55" t="inlineStr">
@@ -11897,6 +11914,11 @@
       <c r="Q10" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R10" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="32">
       <c r="A11" s="49" t="inlineStr">
@@ -11977,6 +11999,11 @@
       <c r="Q11" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23.85" customHeight="1" s="32">
       <c r="A12" s="55" t="inlineStr">
@@ -12057,6 +12084,11 @@
       <c r="Q12" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R12" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.85" customHeight="1" s="32">
       <c r="A13" s="55" t="inlineStr">
@@ -12137,6 +12169,11 @@
       <c r="Q13" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R13" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="35.05" customHeight="1" s="32">
       <c r="A14" s="55" t="inlineStr">
@@ -12217,6 +12254,11 @@
       <c r="Q14" s="56" t="n">
         <v>25</v>
       </c>
+      <c r="R14" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.85" customHeight="1" s="32">
       <c r="A15" s="49" t="inlineStr">
@@ -12297,6 +12339,11 @@
       <c r="Q15" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="32">
       <c r="A16" s="45" t="inlineStr">
@@ -12377,6 +12424,11 @@
       <c r="Q16" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.85" customHeight="1" s="32">
       <c r="A17" s="55" t="inlineStr">
@@ -12457,6 +12509,11 @@
       <c r="Q17" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R17" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.85" customHeight="1" s="32">
       <c r="A18" s="49" t="inlineStr">
@@ -12537,6 +12594,11 @@
       <c r="Q18" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R18" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="35.05" customHeight="1" s="32">
       <c r="A19" s="49" t="inlineStr">
@@ -12617,6 +12679,11 @@
       <c r="Q19" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R19" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="35.05" customHeight="1" s="32">
       <c r="A20" s="49" t="inlineStr">
@@ -12697,6 +12764,11 @@
       <c r="Q20" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R20" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.85" customHeight="1" s="32">
       <c r="A21" s="49" t="inlineStr">
@@ -12777,6 +12849,11 @@
       <c r="Q21" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R21" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="35.05" customHeight="1" s="32">
       <c r="A22" s="49" t="inlineStr">
@@ -12857,6 +12934,11 @@
       <c r="Q22" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R22" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="35.05" customHeight="1" s="32">
       <c r="A23" s="55" t="inlineStr">
@@ -12937,6 +13019,11 @@
       <c r="Q23" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R23" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.85" customHeight="1" s="32">
       <c r="A24" s="55" t="inlineStr">
@@ -13017,6 +13104,11 @@
       <c r="Q24" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R24" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.85" customHeight="1" s="32">
       <c r="A25" s="55" t="inlineStr">
@@ -13097,6 +13189,11 @@
       <c r="Q25" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R25" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.85" customHeight="1" s="32">
       <c r="A26" s="49" t="inlineStr">
@@ -13177,6 +13274,11 @@
       <c r="Q26" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R26" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="35.05" customHeight="1" s="32">
       <c r="A27" s="55" t="inlineStr">
@@ -13257,6 +13359,11 @@
       <c r="Q27" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R27" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.85" customHeight="1" s="32">
       <c r="A28" s="55" t="inlineStr">
@@ -13337,6 +13444,11 @@
       <c r="Q28" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R28" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.85" customHeight="1" s="32">
       <c r="A29" s="45" t="inlineStr">
@@ -13417,6 +13529,11 @@
       <c r="Q29" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R29" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.85" customHeight="1" s="32">
       <c r="A30" s="55" t="inlineStr">
@@ -13497,6 +13614,11 @@
       <c r="Q30" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R30" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.85" customHeight="1" s="32">
       <c r="A31" s="45" t="inlineStr">
@@ -13577,6 +13699,11 @@
       <c r="Q31" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R31" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="35.05" customHeight="1" s="32">
       <c r="A32" s="55" t="inlineStr">
@@ -13657,6 +13784,11 @@
       <c r="Q32" s="56" t="n">
         <v>2</v>
       </c>
+      <c r="R32" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="35.05" customHeight="1" s="32">
       <c r="A33" s="45" t="inlineStr">
@@ -13737,6 +13869,11 @@
       <c r="Q33" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R33" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.85" customHeight="1" s="32">
       <c r="A34" s="55" t="inlineStr">
@@ -13817,6 +13954,11 @@
       <c r="Q34" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R34" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.85" customHeight="1" s="32">
       <c r="A35" s="49" t="inlineStr">
@@ -13897,6 +14039,11 @@
       <c r="Q35" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R35" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23.85" customHeight="1" s="32">
       <c r="A36" s="55" t="inlineStr">
@@ -13977,6 +14124,11 @@
       <c r="Q36" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R36" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.85" customHeight="1" s="32">
       <c r="A37" s="45" t="inlineStr">
@@ -14057,6 +14209,11 @@
       <c r="Q37" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R37" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.85" customHeight="1" s="32">
       <c r="A38" s="55" t="inlineStr">
@@ -14137,6 +14294,11 @@
       <c r="Q38" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R38" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.85" customHeight="1" s="32">
       <c r="A39" s="55" t="inlineStr">
@@ -14217,6 +14379,11 @@
       <c r="Q39" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R39" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="35.05" customHeight="1" s="32">
       <c r="A40" s="55" t="inlineStr">
@@ -14297,6 +14464,11 @@
       <c r="Q40" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R40" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.85" customHeight="1" s="32">
       <c r="A41" s="45" t="inlineStr">
@@ -14377,6 +14549,11 @@
       <c r="Q41" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R41" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="23.85" customHeight="1" s="32">
       <c r="A42" s="55" t="inlineStr">
@@ -14457,6 +14634,11 @@
       <c r="Q42" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R42" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="23.85" customHeight="1" s="32">
       <c r="A43" s="55" t="inlineStr">
@@ -14537,6 +14719,11 @@
       <c r="Q43" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R43" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="23.85" customHeight="1" s="32">
       <c r="A44" s="55" t="inlineStr">
@@ -14617,6 +14804,11 @@
       <c r="Q44" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R44" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.85" customHeight="1" s="32">
       <c r="A45" s="55" t="inlineStr">
@@ -14697,6 +14889,11 @@
       <c r="Q45" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R45" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="23.85" customHeight="1" s="32">
       <c r="A46" s="55" t="inlineStr">
@@ -14777,6 +14974,11 @@
       <c r="Q46" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R46" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="23.85" customHeight="1" s="32">
       <c r="A47" s="55" t="inlineStr">
@@ -14857,6 +15059,11 @@
       <c r="Q47" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R47" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="23.85" customHeight="1" s="32">
       <c r="A48" s="55" t="inlineStr">
@@ -14937,6 +15144,11 @@
       <c r="Q48" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R48" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="23.85" customHeight="1" s="32">
       <c r="A49" s="55" t="inlineStr">
@@ -15017,6 +15229,11 @@
       <c r="Q49" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R49" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="35.05" customHeight="1" s="32">
       <c r="A50" s="55" t="inlineStr">
@@ -15097,6 +15314,11 @@
       <c r="Q50" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R50" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="23.85" customHeight="1" s="32">
       <c r="A51" s="55" t="inlineStr">
@@ -15177,6 +15399,11 @@
       <c r="Q51" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R51" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="23.85" customHeight="1" s="32">
       <c r="A52" s="55" t="inlineStr">
@@ -15257,6 +15484,11 @@
       <c r="Q52" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R52" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="23.85" customHeight="1" s="32">
       <c r="A53" s="55" t="inlineStr">
@@ -15337,6 +15569,11 @@
       <c r="Q53" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R53" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="23.85" customHeight="1" s="32">
       <c r="A54" s="55" t="inlineStr">
@@ -15417,6 +15654,11 @@
       <c r="Q54" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R54" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="23.85" customHeight="1" s="32">
       <c r="A55" s="55" t="inlineStr">
@@ -15497,6 +15739,11 @@
       <c r="Q55" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R55" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="23.85" customHeight="1" s="32">
       <c r="A56" s="55" t="inlineStr">
@@ -15577,6 +15824,11 @@
       <c r="Q56" s="56" t="n">
         <v>2</v>
       </c>
+      <c r="R56" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="23.85" customHeight="1" s="32">
       <c r="A57" s="55" t="inlineStr">
@@ -15657,6 +15909,11 @@
       <c r="Q57" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R57" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="23.85" customHeight="1" s="32">
       <c r="A58" s="55" t="inlineStr">
@@ -15737,6 +15994,11 @@
       <c r="Q58" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R58" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="23.85" customHeight="1" s="32">
       <c r="A59" s="55" t="inlineStr">
@@ -15817,6 +16079,11 @@
       <c r="Q59" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R59" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="23.85" customHeight="1" s="32">
       <c r="A60" s="55" t="inlineStr">
@@ -15897,6 +16164,11 @@
       <c r="Q60" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R60" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="23.85" customHeight="1" s="32">
       <c r="A61" s="55" t="inlineStr">
@@ -15977,6 +16249,11 @@
       <c r="Q61" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R61" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="23.85" customHeight="1" s="32">
       <c r="A62" s="55" t="inlineStr">
@@ -16057,6 +16334,11 @@
       <c r="Q62" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R62" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="23.85" customHeight="1" s="32">
       <c r="A63" s="55" t="inlineStr">
@@ -16137,6 +16419,11 @@
       <c r="Q63" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R63" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="23.85" customHeight="1" s="32">
       <c r="A64" s="55" t="inlineStr">
@@ -16217,6 +16504,11 @@
       <c r="Q64" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R64" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="35.05" customHeight="1" s="32">
       <c r="A65" s="49" t="inlineStr">
@@ -16297,6 +16589,11 @@
       <c r="Q65" s="48" t="n">
         <v>3</v>
       </c>
+      <c r="R65" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="23.85" customHeight="1" s="32">
       <c r="A66" s="55" t="inlineStr">
@@ -16377,6 +16674,11 @@
       <c r="Q66" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R66" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="23.85" customHeight="1" s="32">
       <c r="A67" s="55" t="inlineStr">
@@ -16457,6 +16759,11 @@
       <c r="Q67" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R67" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="23.85" customHeight="1" s="32">
       <c r="A68" s="55" t="inlineStr">
@@ -16537,6 +16844,11 @@
       <c r="Q68" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R68" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="23.85" customHeight="1" s="32">
       <c r="A69" s="55" t="inlineStr">
@@ -16617,6 +16929,11 @@
       <c r="Q69" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R69" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="23.85" customHeight="1" s="32">
       <c r="A70" s="55" t="inlineStr">
@@ -16697,6 +17014,11 @@
       <c r="Q70" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R70" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="32">
       <c r="A71" s="55" t="inlineStr">
@@ -16777,6 +17099,11 @@
       <c r="Q71" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R71" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="35.05" customHeight="1" s="32">
       <c r="A72" s="55" t="inlineStr">
@@ -16857,6 +17184,11 @@
       <c r="Q72" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R72" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="23.85" customHeight="1" s="32">
       <c r="A73" s="45" t="inlineStr">
@@ -16937,6 +17269,11 @@
       <c r="Q73" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R73" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="23.85" customHeight="1" s="32">
       <c r="A74" s="55" t="inlineStr">
@@ -17017,6 +17354,11 @@
       <c r="Q74" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R74" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="23.85" customHeight="1" s="32">
       <c r="A75" s="55" t="inlineStr">
@@ -17097,6 +17439,11 @@
       <c r="Q75" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R75" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="35.05" customHeight="1" s="32">
       <c r="A76" s="49" t="inlineStr">
@@ -17177,6 +17524,11 @@
       <c r="Q76" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R76" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="23.85" customHeight="1" s="32">
       <c r="A77" s="49" t="inlineStr">
@@ -17257,6 +17609,11 @@
       <c r="Q77" s="48" t="n">
         <v>60</v>
       </c>
+      <c r="R77" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="23.85" customHeight="1" s="32">
       <c r="A78" s="55" t="inlineStr">
@@ -17337,6 +17694,11 @@
       <c r="Q78" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R78" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="23.85" customHeight="1" s="32">
       <c r="A79" s="55" t="inlineStr">
@@ -17417,6 +17779,11 @@
       <c r="Q79" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R79" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="23.85" customHeight="1" s="32">
       <c r="A80" s="49" t="inlineStr">
@@ -17497,6 +17864,11 @@
       <c r="Q80" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R80" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="35.05" customHeight="1" s="32">
       <c r="A81" s="55" t="inlineStr">
@@ -17577,6 +17949,11 @@
       <c r="Q81" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R81" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="23.85" customHeight="1" s="32">
       <c r="A82" s="45" t="inlineStr">
@@ -17657,6 +18034,11 @@
       <c r="Q82" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R82" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="23.85" customHeight="1" s="32">
       <c r="A83" s="55" t="inlineStr">
@@ -17737,6 +18119,11 @@
       <c r="Q83" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R83" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="23.85" customHeight="1" s="32">
       <c r="A84" s="45" t="inlineStr">
@@ -17817,6 +18204,11 @@
       <c r="Q84" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R84" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="35.05" customHeight="1" s="32">
       <c r="A85" s="55" t="inlineStr">
@@ -17897,6 +18289,11 @@
       <c r="Q85" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R85" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="23.85" customHeight="1" s="32">
       <c r="A86" s="55" t="inlineStr">
@@ -17977,6 +18374,11 @@
       <c r="Q86" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R86" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="23.85" customHeight="1" s="32">
       <c r="A87" s="49" t="inlineStr">
@@ -18057,6 +18459,11 @@
       <c r="Q87" s="48" t="n">
         <v>2</v>
       </c>
+      <c r="R87" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="46.25" customHeight="1" s="32">
       <c r="A88" s="49" t="inlineStr">
@@ -18137,6 +18544,11 @@
       <c r="Q88" s="48" t="n">
         <v>15</v>
       </c>
+      <c r="R88" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="23.85" customHeight="1" s="32">
       <c r="A89" s="55" t="inlineStr">
@@ -18217,6 +18629,11 @@
       <c r="Q89" s="56" t="n">
         <v>2</v>
       </c>
+      <c r="R89" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="23.85" customHeight="1" s="32">
       <c r="A90" s="55" t="inlineStr">
@@ -18297,6 +18714,11 @@
       <c r="Q90" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R90" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="23.85" customHeight="1" s="32">
       <c r="A91" s="49" t="inlineStr">
@@ -18377,6 +18799,11 @@
       <c r="Q91" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R91" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="23.85" customHeight="1" s="32">
       <c r="A92" s="49" t="inlineStr">
@@ -18457,6 +18884,11 @@
       <c r="Q92" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R92" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="23.85" customHeight="1" s="32">
       <c r="A93" s="55" t="inlineStr">
@@ -18537,6 +18969,11 @@
       <c r="Q93" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R93" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="23.85" customHeight="1" s="32">
       <c r="A94" s="55" t="inlineStr">
@@ -18617,6 +19054,11 @@
       <c r="Q94" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R94" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="23.85" customHeight="1" s="32">
       <c r="A95" s="55" t="inlineStr">
@@ -18697,6 +19139,11 @@
       <c r="Q95" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R95" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="23.85" customHeight="1" s="32">
       <c r="A96" s="55" t="inlineStr">
@@ -18777,6 +19224,11 @@
       <c r="Q96" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R96" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="23.85" customHeight="1" s="32">
       <c r="A97" s="55" t="inlineStr">
@@ -18857,6 +19309,11 @@
       <c r="Q97" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R97" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="23.85" customHeight="1" s="32">
       <c r="A98" s="49" t="inlineStr">
@@ -18937,6 +19394,11 @@
       <c r="Q98" s="48" t="n">
         <v>10</v>
       </c>
+      <c r="R98" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="35.05" customHeight="1" s="32">
       <c r="A99" s="55" t="inlineStr">
@@ -19017,6 +19479,11 @@
       <c r="Q99" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R99" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="23.85" customHeight="1" s="32">
       <c r="A100" s="45" t="inlineStr">
@@ -19097,6 +19564,11 @@
       <c r="Q100" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R100" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="23.85" customHeight="1" s="32">
       <c r="A101" s="55" t="inlineStr">
@@ -19177,6 +19649,11 @@
       <c r="Q101" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R101" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="23.85" customHeight="1" s="32">
       <c r="A102" s="55" t="inlineStr">
@@ -19257,6 +19734,11 @@
       <c r="Q102" s="56" t="n">
         <v>120</v>
       </c>
+      <c r="R102" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="23.85" customHeight="1" s="32">
       <c r="A103" s="55" t="inlineStr">
@@ -19337,6 +19819,11 @@
       <c r="Q103" s="56" t="n">
         <v>90</v>
       </c>
+      <c r="R103" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="23.85" customHeight="1" s="32">
       <c r="A104" s="55" t="inlineStr">
@@ -19417,6 +19904,11 @@
       <c r="Q104" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R104" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="23.85" customHeight="1" s="32">
       <c r="A105" s="49" t="inlineStr">
@@ -19497,6 +19989,11 @@
       <c r="Q105" s="48" t="n">
         <v>5</v>
       </c>
+      <c r="R105" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="23.85" customHeight="1" s="32">
       <c r="A106" s="55" t="inlineStr">
@@ -19577,6 +20074,11 @@
       <c r="Q106" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R106" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="23.85" customHeight="1" s="32">
       <c r="A107" s="55" t="inlineStr">
@@ -19657,6 +20159,11 @@
       <c r="Q107" s="56" t="n">
         <v>60</v>
       </c>
+      <c r="R107" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="23.85" customHeight="1" s="32">
       <c r="A108" s="55" t="inlineStr">
@@ -19737,6 +20244,11 @@
       <c r="Q108" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R108" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="23.85" customHeight="1" s="32">
       <c r="A109" s="55" t="inlineStr">
@@ -19817,6 +20329,11 @@
       <c r="Q109" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R109" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="23.85" customHeight="1" s="32">
       <c r="A110" s="55" t="inlineStr">
@@ -19897,6 +20414,11 @@
       <c r="Q110" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R110" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="23.85" customHeight="1" s="32">
       <c r="A111" s="55" t="inlineStr">
@@ -19977,6 +20499,11 @@
       <c r="Q111" s="56" t="n">
         <v>60</v>
       </c>
+      <c r="R111" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="23.85" customHeight="1" s="32">
       <c r="A112" s="55" t="inlineStr">
@@ -20057,6 +20584,11 @@
       <c r="Q112" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R112" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="23.85" customHeight="1" s="32">
       <c r="A113" s="55" t="inlineStr">
@@ -20137,6 +20669,11 @@
       <c r="Q113" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R113" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="23.85" customHeight="1" s="32">
       <c r="A114" s="55" t="inlineStr">
@@ -20217,6 +20754,11 @@
       <c r="Q114" s="56" t="n">
         <v>90</v>
       </c>
+      <c r="R114" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="35.05" customHeight="1" s="32">
       <c r="A115" s="55" t="inlineStr">
@@ -20297,6 +20839,11 @@
       <c r="Q115" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R115" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="23.85" customHeight="1" s="32">
       <c r="A116" s="45" t="inlineStr">
@@ -20377,6 +20924,11 @@
       <c r="Q116" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R116" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="23.85" customHeight="1" s="32">
       <c r="A117" s="55" t="inlineStr">
@@ -20457,6 +21009,11 @@
       <c r="Q117" s="56" t="n">
         <v>180</v>
       </c>
+      <c r="R117" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="35.05" customHeight="1" s="32">
       <c r="A118" s="45" t="inlineStr">
@@ -20537,6 +21094,11 @@
       <c r="Q118" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R118" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="23.85" customHeight="1" s="32">
       <c r="A119" s="55" t="inlineStr">
@@ -20617,6 +21179,11 @@
       <c r="Q119" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R119" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="23.85" customHeight="1" s="32">
       <c r="A120" s="55" t="inlineStr">
@@ -20697,6 +21264,11 @@
       <c r="Q120" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R120" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="35.05" customHeight="1" s="32">
       <c r="A121" s="55" t="inlineStr">
@@ -20777,6 +21349,11 @@
       <c r="Q121" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R121" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="23.85" customHeight="1" s="32">
       <c r="A122" s="55" t="inlineStr">
@@ -20857,6 +21434,11 @@
       <c r="Q122" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R122" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="23.85" customHeight="1" s="32">
       <c r="A123" s="49" t="inlineStr">
@@ -20937,6 +21519,11 @@
       <c r="Q123" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R123" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="23.85" customHeight="1" s="32">
       <c r="A124" s="55" t="inlineStr">
@@ -21017,6 +21604,11 @@
       <c r="Q124" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R124" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="23.85" customHeight="1" s="32">
       <c r="A125" s="55" t="inlineStr">
@@ -21097,6 +21689,11 @@
       <c r="Q125" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R125" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="23.85" customHeight="1" s="32">
       <c r="A126" s="49" t="inlineStr">
@@ -21177,6 +21774,11 @@
       <c r="Q126" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R126" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="23.85" customHeight="1" s="32">
       <c r="A127" s="49" t="inlineStr">
@@ -21257,6 +21859,11 @@
       <c r="Q127" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R127" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="23.85" customHeight="1" s="32">
       <c r="A128" s="55" t="inlineStr">
@@ -21337,6 +21944,11 @@
       <c r="Q128" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R128" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="23.85" customHeight="1" s="32">
       <c r="A129" s="49" t="inlineStr">
@@ -21417,6 +22029,11 @@
       <c r="Q129" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R129" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="23.85" customHeight="1" s="32">
       <c r="A130" s="55" t="inlineStr">
@@ -21497,6 +22114,11 @@
       <c r="Q130" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R130" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="23.85" customHeight="1" s="32">
       <c r="A131" s="49" t="inlineStr">
@@ -21577,6 +22199,11 @@
       <c r="Q131" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R131" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="23.85" customHeight="1" s="32">
       <c r="A132" s="45" t="inlineStr">
@@ -21657,6 +22284,11 @@
       <c r="Q132" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R132" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="23.85" customHeight="1" s="32">
       <c r="A133" s="45" t="inlineStr">
@@ -21737,6 +22369,11 @@
       <c r="Q133" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R133" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="23.85" customHeight="1" s="32">
       <c r="A134" s="55" t="inlineStr">
@@ -21817,6 +22454,11 @@
       <c r="Q134" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R134" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="23.85" customHeight="1" s="32">
       <c r="A135" s="55" t="inlineStr">
@@ -21897,6 +22539,11 @@
       <c r="Q135" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R135" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="23.85" customHeight="1" s="32">
       <c r="A136" s="55" t="inlineStr">
@@ -21977,6 +22624,11 @@
       <c r="Q136" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R136" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="23.85" customHeight="1" s="32">
       <c r="A137" s="55" t="inlineStr">
@@ -22057,6 +22709,11 @@
       <c r="Q137" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R137" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="23.85" customHeight="1" s="32">
       <c r="A138" s="55" t="inlineStr">
@@ -22137,6 +22794,11 @@
       <c r="Q138" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R138" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="23.85" customHeight="1" s="32">
       <c r="A139" s="55" t="inlineStr">
@@ -22217,6 +22879,11 @@
       <c r="Q139" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R139" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="23.85" customHeight="1" s="32">
       <c r="A140" s="55" t="inlineStr">
@@ -22297,6 +22964,11 @@
       <c r="Q140" s="56" t="n">
         <v>10</v>
       </c>
+      <c r="R140" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="23.85" customHeight="1" s="32">
       <c r="A141" s="55" t="inlineStr">
@@ -22377,6 +23049,11 @@
       <c r="Q141" s="56" t="n">
         <v>5</v>
       </c>
+      <c r="R141" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="23.85" customHeight="1" s="32">
       <c r="A142" s="49" t="inlineStr">
@@ -22457,6 +23134,11 @@
       <c r="Q142" s="48" t="n">
         <v>60</v>
       </c>
+      <c r="R142" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="23.85" customHeight="1" s="32">
       <c r="A143" s="55" t="inlineStr">
@@ -22537,6 +23219,11 @@
       <c r="Q143" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R143" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="23.85" customHeight="1" s="32">
       <c r="A144" s="45" t="inlineStr">
@@ -22617,6 +23304,11 @@
       <c r="Q144" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R144" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="23.85" customHeight="1" s="32">
       <c r="A145" s="45" t="inlineStr">
@@ -22697,6 +23389,11 @@
       <c r="Q145" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R145" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="23.85" customHeight="1" s="32">
       <c r="A146" s="45" t="inlineStr">
@@ -22777,6 +23474,11 @@
       <c r="Q146" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R146" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="35.05" customHeight="1" s="32">
       <c r="A147" s="49" t="inlineStr">
@@ -22857,6 +23559,11 @@
       <c r="Q147" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R147" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="23.85" customHeight="1" s="32">
       <c r="A148" s="45" t="inlineStr">
@@ -22937,6 +23644,11 @@
       <c r="Q148" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R148" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="23.85" customHeight="1" s="32">
       <c r="A149" s="55" t="inlineStr">
@@ -23017,6 +23729,11 @@
       <c r="Q149" s="56" t="n">
         <v>20</v>
       </c>
+      <c r="R149" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="23.85" customHeight="1" s="32">
       <c r="A150" s="55" t="inlineStr">
@@ -23097,6 +23814,11 @@
       <c r="Q150" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R150" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="23.85" customHeight="1" s="32">
       <c r="A151" s="55" t="inlineStr">
@@ -23177,6 +23899,11 @@
       <c r="Q151" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R151" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="23.85" customHeight="1" s="32">
       <c r="A152" s="49" t="inlineStr">
@@ -23257,6 +23984,11 @@
       <c r="Q152" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R152" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="23.85" customHeight="1" s="32">
       <c r="A153" s="55" t="inlineStr">
@@ -23337,6 +24069,11 @@
       <c r="Q153" s="56" t="n">
         <v>15</v>
       </c>
+      <c r="R153" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="23.85" customHeight="1" s="32">
       <c r="A154" s="55" t="inlineStr">
@@ -23417,6 +24154,11 @@
       <c r="Q154" s="56" t="n">
         <v>45</v>
       </c>
+      <c r="R154" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="23.85" customHeight="1" s="32">
       <c r="A155" s="55" t="inlineStr">
@@ -23497,6 +24239,11 @@
       <c r="Q155" s="56" t="n">
         <v>180</v>
       </c>
+      <c r="R155" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="23.85" customHeight="1" s="32">
       <c r="A156" s="55" t="inlineStr">
@@ -23577,6 +24324,11 @@
       <c r="Q156" s="56" t="n">
         <v>30</v>
       </c>
+      <c r="R156" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="35.05" customHeight="1" s="32">
       <c r="A157" s="49" t="inlineStr">
@@ -23657,6 +24409,11 @@
       <c r="Q157" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R157" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="35.05" customHeight="1" s="32">
       <c r="A158" s="49" t="inlineStr">
@@ -23737,6 +24494,11 @@
       <c r="Q158" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R158" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="35.05" customHeight="1" s="32">
       <c r="A159" s="45" t="inlineStr">
@@ -23817,6 +24579,11 @@
       <c r="Q159" s="59" t="n">
         <v>0</v>
       </c>
+      <c r="R159" s="59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="49" t="inlineStr">
@@ -23897,6 +24664,11 @@
       <c r="Q160" s="48" t="n">
         <v>2</v>
       </c>
+      <c r="R160" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="49" t="inlineStr">
@@ -23977,6 +24749,11 @@
       <c r="Q161" s="48" t="n">
         <v>15</v>
       </c>
+      <c r="R161" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="49" t="inlineStr">
@@ -24057,6 +24834,11 @@
       <c r="Q162" s="48" t="n">
         <v>0</v>
       </c>
+      <c r="R162" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="49" t="inlineStr">
@@ -24116,7 +24898,7 @@
       </c>
       <c r="M163" s="51" t="inlineStr">
         <is>
-          <t>Un détecteur non conforme peut ne pas être reconnu par l'assureur</t>
+          <t>Un détecteur non conforme peut ne pas être reconnu par votre assureur</t>
         </is>
       </c>
       <c r="N163" s="49" t="inlineStr">
@@ -24136,6 +24918,11 @@
       </c>
       <c r="Q163" s="48" t="n">
         <v>5</v>
+      </c>
+      <c r="R163" s="48" t="inlineStr">
+        <is>
+          <t>Un détecteur non conforme peut ne pas être reconnu par votre assureur</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -24152,7 +24939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A2:N90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="31" min="1" max="1"/>
@@ -24168,7 +24955,6 @@
     <col width="30" customWidth="1" style="31" min="12" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="32">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -24183,7 +24969,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="41" t="inlineStr">
         <is>
@@ -30220,7 +31005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A2:I45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="31" min="1" max="2"/>
@@ -30231,7 +31016,6 @@
     <col width="60" customWidth="1" style="31" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="32">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -30246,7 +31030,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="41" t="inlineStr">
         <is>
@@ -30288,6 +31071,11 @@
           <t>Conseil si a confirmer</t>
         </is>
       </c>
+      <c r="I5" s="41" t="inlineStr">
+        <is>
+          <t>Conseil si en retard</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="32">
       <c r="A6" s="48" t="inlineStr">
@@ -30330,6 +31118,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I6" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="32">
       <c r="A7" s="48" t="inlineStr">
@@ -30372,6 +31165,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I7" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="32">
       <c r="A8" s="48" t="inlineStr">
@@ -30414,6 +31212,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I8" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="32">
       <c r="A9" s="48" t="inlineStr">
@@ -30456,6 +31259,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I9" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="32">
       <c r="A10" s="48" t="inlineStr">
@@ -30498,6 +31306,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I10" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="32">
       <c r="A11" s="48" t="inlineStr">
@@ -30540,6 +31353,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I11" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="32">
       <c r="A12" s="48" t="inlineStr">
@@ -30582,6 +31400,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I12" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.85" customHeight="1" s="32">
       <c r="A13" s="48" t="inlineStr">
@@ -30624,6 +31447,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I13" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="32">
       <c r="A14" s="48" t="inlineStr">
@@ -30666,6 +31494,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I14" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.85" customHeight="1" s="32">
       <c r="A15" s="48" t="inlineStr">
@@ -30708,6 +31541,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I15" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="32">
       <c r="A16" s="48" t="inlineStr">
@@ -30750,6 +31588,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I16" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.85" customHeight="1" s="32">
       <c r="A17" s="48" t="inlineStr">
@@ -30792,6 +31635,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I17" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.85" customHeight="1" s="32">
       <c r="A18" s="48" t="inlineStr">
@@ -30834,6 +31682,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I18" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.85" customHeight="1" s="32">
       <c r="A19" s="48" t="inlineStr">
@@ -30876,6 +31729,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I19" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.85" customHeight="1" s="32">
       <c r="A20" s="48" t="inlineStr">
@@ -30918,6 +31776,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I20" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.85" customHeight="1" s="32">
       <c r="A21" s="48" t="inlineStr">
@@ -30960,6 +31823,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I21" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.85" customHeight="1" s="32">
       <c r="A22" s="48" t="inlineStr">
@@ -31002,6 +31870,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I22" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="48" t="inlineStr">
@@ -31044,6 +31917,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I23" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.85" customHeight="1" s="32">
       <c r="A24" s="48" t="inlineStr">
@@ -31086,6 +31964,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I24" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.85" customHeight="1" s="32">
       <c r="A25" s="48" t="inlineStr">
@@ -31128,6 +32011,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I25" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.85" customHeight="1" s="32">
       <c r="A26" s="48" t="inlineStr">
@@ -31170,6 +32058,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I26" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="32">
       <c r="A27" s="48" t="inlineStr">
@@ -31212,6 +32105,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I27" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.85" customHeight="1" s="32">
       <c r="A28" s="48" t="inlineStr">
@@ -31254,6 +32152,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I28" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="32">
       <c r="A29" s="48" t="inlineStr">
@@ -31296,6 +32199,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I29" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="32">
       <c r="A30" s="48" t="inlineStr">
@@ -31338,6 +32246,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I30" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="32">
       <c r="A31" s="48" t="inlineStr">
@@ -31380,6 +32293,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I31" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="35.05" customHeight="1" s="32">
       <c r="A32" s="48" t="inlineStr">
@@ -31422,6 +32340,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I32" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="46.25" customHeight="1" s="32">
       <c r="A33" s="48" t="inlineStr">
@@ -31464,6 +32387,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I33" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.85" customHeight="1" s="32">
       <c r="A34" s="48" t="inlineStr">
@@ -31506,6 +32434,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I34" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.85" customHeight="1" s="32">
       <c r="A35" s="48" t="inlineStr">
@@ -31548,6 +32481,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I35" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23.85" customHeight="1" s="32">
       <c r="A36" s="48" t="inlineStr">
@@ -31590,6 +32528,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I36" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="32">
       <c r="A37" s="61" t="inlineStr">
@@ -31632,6 +32575,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I37" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="32">
       <c r="A38" s="61" t="inlineStr">
@@ -31674,6 +32622,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I38" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.85" customHeight="1" s="32">
       <c r="A39" s="61" t="inlineStr">
@@ -31716,6 +32669,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I39" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="32">
       <c r="A40" s="61" t="inlineStr">
@@ -31758,6 +32716,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I40" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.85" customHeight="1" s="32">
       <c r="A41" s="61" t="inlineStr">
@@ -31800,6 +32763,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I41" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="61" t="inlineStr">
@@ -31842,6 +32810,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I42" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="48" t="inlineStr">
@@ -31884,6 +32857,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I43" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="61" t="inlineStr">
@@ -31926,6 +32904,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I44" s="53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="48" t="inlineStr">
@@ -31966,6 +32949,11 @@
       <c r="H45" s="51" t="inlineStr">
         <is>
           <t>Regardez l'étiquette au dos du détecteur, ou le contrat de télésurveillance.</t>
+        </is>
+      </c>
+      <c r="I45" s="51" t="inlineStr">
+        <is>
+          <t>Remplacez le détecteur par un modèle conforme, ou contactez votre prestataire de télésurveillance.</t>
         </is>
       </c>
     </row>
@@ -32961,7 +33949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A2:N26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="31" min="1" max="1"/>
@@ -32978,7 +33966,6 @@
     <col width="40" customWidth="1" style="31" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="32">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -32993,7 +33980,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="41" t="inlineStr">
         <is>
